--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年度担当者物件表  20260127" sheetId="1" r:id="Rcaa4741ae488472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R2eeb60777d2b4645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R7e94b7f22a304238"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R7a47181b173b48ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Rc80b750430494b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R1aaef19a2e9047d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rc50e6944875c46c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R83755af76b134a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R4d76699beba34448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R561e3969b3db416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年度担当者物件表  20260127" sheetId="1" r:id="Rc86b62a2fcb34c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R361f6452d9c84f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R137b68ba1416446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rc5967cec631b4a2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R15b896d21d664328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R01c8bd1b423b458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rf22f1124dc794c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Rdcf5d705750c44ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R9b9d9d6ade6a41d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R22c3f8e6a7fb491d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4790,7 +4790,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="O57" t="str">
-        <x:v>金属-21</x:v>
+        <x:v>金属-22</x:v>
       </x:c>
       <x:c r="U57" t="s">
         <x:v>159</x:v>
@@ -4848,7 +4848,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="O59" t="str">
-        <x:v>金属-22</x:v>
+        <x:v>金属-21</x:v>
       </x:c>
       <x:c r="U59" t="s">
         <x:v>159</x:v>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年度担当者物件表  20260127" sheetId="1" r:id="Rc86b62a2fcb34c2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R361f6452d9c84f51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R137b68ba1416446a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rc5967cec631b4a2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R15b896d21d664328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R01c8bd1b423b458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rf22f1124dc794c22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Rdcf5d705750c44ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R9b9d9d6ade6a41d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R22c3f8e6a7fb491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年度担当者物件表  20260127" sheetId="1" r:id="R9183b7e1f6214320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R887b9c07c16b4913"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rc654317f894d4cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Re8e4230114304a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R764e9a3db4f24e8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rfc09a234cb604ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R7ea0794d42054c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Ra32891c8a4c34765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R217ace66ef324c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R574c131254424145"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6554,6 +6554,9 @@
       <x:c r="L116" t="s">
         <x:v>104</x:v>
       </x:c>
+      <x:c r="O116" t="str">
+        <x:v>金属-35</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="21" customHeight="1">
       <x:c r="A117" t="s">
@@ -6677,7 +6680,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="O121" t="str">
-        <x:v>金属-35</x:v>
+        <x:v>金属-36</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="21" customHeight="1">
@@ -6813,7 +6816,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="O126" t="str">
-        <x:v>金属-36</x:v>
+        <x:v>金属-37</x:v>
       </x:c>
       <x:c r="Q126" t="str">
         <x:v>ガラ-</x:v>
@@ -6917,7 +6920,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="O130" t="str">
-        <x:v>金属-37</x:v>
+        <x:v>金属-38</x:v>
       </x:c>
       <x:c r="S130" t="s">
         <x:v>191</x:v>
@@ -7065,7 +7068,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="O135" t="str">
-        <x:v>金属-38</x:v>
+        <x:v>金属-39</x:v>
       </x:c>
       <x:c r="P135" t="s">
         <x:v>29</x:v>
@@ -7221,7 +7224,7 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="O141" t="str">
-        <x:v>金属-39</x:v>
+        <x:v>金属-40</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="21" customHeight="1">
@@ -7303,7 +7306,7 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="O144" t="str">
-        <x:v>金属-40</x:v>
+        <x:v>金属-41</x:v>
       </x:c>
       <x:c r="U144" t="s">
         <x:v>126</x:v>
@@ -7335,7 +7338,7 @@
         <x:v>364</x:v>
       </x:c>
       <x:c r="O145" t="str">
-        <x:v>金属-41</x:v>
+        <x:v>金属-42</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="21" customHeight="1">
@@ -7436,7 +7439,7 @@
         <x:v>373</x:v>
       </x:c>
       <x:c r="O149" t="str">
-        <x:v>金属-42</x:v>
+        <x:v>金属-43</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="21" customHeight="1">
@@ -7647,7 +7650,7 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="O157" t="str">
-        <x:v>金属-43</x:v>
+        <x:v>金属-44</x:v>
       </x:c>
       <x:c r="Q157" t="str">
         <x:v>ガラ-</x:v>
@@ -7734,7 +7737,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="O160" t="str">
-        <x:v>金属-44</x:v>
+        <x:v>金属-45</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="21" customHeight="1">
@@ -7775,7 +7778,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="O161" t="str">
-        <x:v>金属-45</x:v>
+        <x:v>金属-46</x:v>
       </x:c>
       <x:c r="P161" t="s">
         <x:v>29</x:v>
@@ -7879,7 +7882,7 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="O165" t="str">
-        <x:v>金属-46</x:v>
+        <x:v>金属-47</x:v>
       </x:c>
       <x:c r="Q165" t="str">
         <x:v>ガラ-</x:v>
@@ -8102,7 +8105,7 @@
         <x:v>373</x:v>
       </x:c>
       <x:c r="O174" t="str">
-        <x:v>金属-48</x:v>
+        <x:v>金属-49</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="21" customHeight="1">
@@ -8189,7 +8192,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="O177" t="str">
-        <x:v>金属-47</x:v>
+        <x:v>金属-48</x:v>
       </x:c>
       <x:c r="Q177" t="str">
         <x:v>ガラ-</x:v>
@@ -8310,7 +8313,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="O182" t="str">
-        <x:v>金属-49</x:v>
+        <x:v>金属-50</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="21" customHeight="1">
@@ -8336,7 +8339,7 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="O183" t="str">
-        <x:v>金属-50</x:v>
+        <x:v>金属-51</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="21" customHeight="1">
@@ -8359,7 +8362,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="O184" t="str">
-        <x:v>金属-51</x:v>
+        <x:v>金属-52</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="21" customHeight="1">
@@ -9440,7 +9443,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="O226" t="str">
-        <x:v>金属-60</x:v>
+        <x:v>金属-61</x:v>
       </x:c>
       <x:c r="Q226" t="str">
         <x:v>ガラ-</x:v>
@@ -9521,7 +9524,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="O229" t="str">
-        <x:v>金属-59</x:v>
+        <x:v>金属-60</x:v>
       </x:c>
       <x:c r="Q229" t="str">
         <x:v>ガラ-</x:v>
@@ -9568,7 +9571,7 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="O230" t="str">
-        <x:v>金属-58</x:v>
+        <x:v>金属-59</x:v>
       </x:c>
       <x:c r="Q230" t="str">
         <x:v>ガラ-</x:v>
@@ -9594,7 +9597,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="O231" t="str">
-        <x:v>金属-61</x:v>
+        <x:v>金属-62</x:v>
       </x:c>
       <x:c r="S231" t="s">
         <x:v>550</x:v>
@@ -9678,7 +9681,7 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="O234" t="str">
-        <x:v>金属-54</x:v>
+        <x:v>金属-55</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="21" customHeight="1">
@@ -9730,7 +9733,7 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="O236" t="str">
-        <x:v>金属-56</x:v>
+        <x:v>金属-57</x:v>
       </x:c>
       <x:c r="Q236" t="str">
         <x:v>ガラ-</x:v>
@@ -9762,7 +9765,7 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="O237" t="str">
-        <x:v>金属-57</x:v>
+        <x:v>金属-58</x:v>
       </x:c>
       <x:c r="Q237" t="str">
         <x:v>ガラ-</x:v>
@@ -9791,7 +9794,7 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="O238" t="str">
-        <x:v>金属-55</x:v>
+        <x:v>金属-56</x:v>
       </x:c>
       <x:c r="Q238" t="str">
         <x:v>ガラ-</x:v>
@@ -9843,7 +9846,7 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="O240" t="str">
-        <x:v>金属-53</x:v>
+        <x:v>金属-54</x:v>
       </x:c>
       <x:c r="U240" t="s">
         <x:v>126</x:v>
@@ -9872,7 +9875,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="O241" t="str">
-        <x:v>金属-52</x:v>
+        <x:v>金属-53</x:v>
       </x:c>
       <x:c r="U241" t="s">
         <x:v>126</x:v>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年度担当者物件表  20260127" sheetId="1" r:id="R9183b7e1f6214320"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R887b9c07c16b4913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rc654317f894d4cb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Re8e4230114304a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R764e9a3db4f24e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rfc09a234cb604ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R7ea0794d42054c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Ra32891c8a4c34765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R217ace66ef324c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R574c131254424145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R7f93a872f6004df7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R60068292d8de46f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rb0eec0e3bc074804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R3ecc766f70744b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Rf997c94c31834f16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Re984608b9ff340bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R42d6e6f78aa04fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R4183e187a90b45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R61e047fbc2524744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rdad1a8268b8a4e2d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R7f93a872f6004df7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R60068292d8de46f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rb0eec0e3bc074804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R3ecc766f70744b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Rf997c94c31834f16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Re984608b9ff340bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R42d6e6f78aa04fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R4183e187a90b45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R61e047fbc2524744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rdad1a8268b8a4e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R8b5d37a9d2574ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rfe4ed397223b424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R6b72aa4ba2a1419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R83118f535fc54299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Rcf5597cd8d674ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R4e3af96f40484086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R8ae7e4f3ed46476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R94efe8a103234db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R358f4d276fad4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R22ea35f238224278"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -133,790 +133,790 @@
     <x:t xml:space="preserve">K-</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">K-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A-</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">イオンタウン可燃</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-7888</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">段紙・PET</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックスバリュ可燃</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22-1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">段紙・PET・アルミ・牛乳P</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">イオンタウン段紙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックス段紙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックスPETアルミ紙P</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PET アルミ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックス発泡</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">発泡</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WE CARS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22-8833</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">会社　商店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">関東電化ファインテック</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マンション</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">フォーティーナイン</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">違反ゴミのみ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">第1第3水曜日</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">介護</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">みんなの家</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-4165</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">なごみの家</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">H-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ジャルディーノブリリオ（大和リビング）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">金属第4水曜日</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">中華料理輝龍</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">名張育成会 こころのいろ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">卸団地</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">中電配電サポート</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">アイルライン問屋倉庫</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">鎌苅乳販</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-1930</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">内金</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23-5311</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">岩野屋</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-0236</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">官公庁</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">旧県民局（伊賀庁舎）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-8000</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">病院　薬</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">フラワー薬局四十九店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-1193</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">H-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">太陽作業所 ひらそる</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">コンビニ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">セブンイレブン四十九店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">H-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1/31~</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">桑町</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">太陽作業所</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ファーストウイン</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-3286</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マルベリーハイアット1.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">第1.3水</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">（株）新和工業社員寮</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">H-</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">6月8日～</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">可燃のみ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">銀座通り</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">買い物</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">クスリのアオキ伊賀上野店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">よい子のお家 ばしょう</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">国土省</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-3011</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ほっともっと桑町店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-3025</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">銀行</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">百五銀行　上野支店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23-7105</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ポットローズ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">大東建託パートナーズ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10/1~</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">堀川石油　銀座店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-4754</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">金属1.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ヘアカット</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NEVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">伊賀肉やまもと</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">立正佼成会</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ジェンティーレイガウエノ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">中川歯科</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">セブンイレブン伊賀忍者駅南店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">花市場</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">武田歯科</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">九庵</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-5859</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">9時半～</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">万川集海忍者体験施設</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">フラット立石（銀座）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">旧上野庁舎　SAKAKURABASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">近畿不動産</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">48-7779</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">第３週は金曜日</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">新聞</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">読売新聞　上野支局</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-5143</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">12時～</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">リエート</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">JEWRL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">森田クリニック</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22-2233</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">金属1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">エスペランサ薬局</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-5660</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">清水眼科</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23-0718</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">丸ノ内</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GEO　ゲオ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-7601</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">滋賀銀行</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-3326</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">検察庁</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-0492</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">裁判所</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ハイトメゾン丸之内</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">魚民</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-1788</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">石田サイクルビル</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">あすなろ薬局</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-9393</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">午前中</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">医療法人アクアクリニック</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-39</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">プラザあかもん</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">個別教室のトライ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">上野高校</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-2550</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">富々</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">備考欄</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">耕田090-6591-7086</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">パン工房　マームベランダ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">51-6996</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">11/10開始</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">三重ワークサービス</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-8037</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">カフェ碧（みどり）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-3001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">城北</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">服部歯科</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">感染ごみ回収不可</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ヒロタ薬局</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">48-6700</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1月8日開始</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ラム―</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">サンドラッグ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ポポラ-イーナ　Popora•Ina</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bワ-ルド</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">コメリ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-3310</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">西松屋</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-1885</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">プロマーケット</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">48-7310</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">はるやま</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22-1210</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10時までに</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ハミング</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">味神館</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23-5761</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">吉野家</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-5782</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ビッグエコー</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">23-2242</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ソフトバンク</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-1515</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ナリス化粧品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">王将</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-8863</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">セカンドストリート</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">小田</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">小川整備</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0120-481-532</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ライフテクノサービス</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ブラコウジ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">あゆみの</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ハートヒルⅢ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">創価学会</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-7571</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">おりがみ薬局</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">41-0240</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">セイムス伊賀小田店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">セブンイレブン平野北谷店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-0877</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">トゥルーハート</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">090-5616-3265神谷</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ポナール駒</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">積和トータルサポート神谷</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ハイツホワイトピジョン</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">鳩岡090-6084-3189</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">モンノーブル</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">洋服の青山</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-2950</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Crece クレス</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-4066</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">憩の里</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">48-7721</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">特別養護老人ホーム伊賀の街</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">41-1120</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">カットA</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">44-6138</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">堀川石油　小田店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24-2690</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Q's garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">K-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">白鳳通り</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">すき家</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">N-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0120-498-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">フレックスホテル</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">21-3111</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">N-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">イオンタウン可燃</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-7888</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">段紙・PET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックスバリュ可燃</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22-1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">段紙・PET・アルミ・牛乳P</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">イオンタウン段紙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックス段紙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックスPETアルミ紙P</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PET アルミ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックス発泡</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">発泡</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WE CARS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22-8833</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">会社　商店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">関東電化ファインテック</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マンション</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">フォーティーナイン</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">違反ゴミのみ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">第1第3水曜日</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">介護</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">みんなの家</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-4165</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">なごみの家</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">H-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ジャルディーノブリリオ（大和リビング）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">金属第4水曜日</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">中華料理輝龍</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">名張育成会 こころのいろ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">卸団地</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">中電配電サポート</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">アイルライン問屋倉庫</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">鎌苅乳販</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-1930</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">内金</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23-5311</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">岩野屋</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-0236</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">官公庁</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">旧県民局（伊賀庁舎）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-8000</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">病院　薬</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">フラワー薬局四十九店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-1193</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">H-4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">太陽作業所 ひらそる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">コンビニ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">セブンイレブン四十九店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">H-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1/31~</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">桑町</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">太陽作業所</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ファーストウイン</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-3286</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マルベリーハイアット1.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">第1.3水</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">（株）新和工業社員寮</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">H-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">6月8日～</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">可燃のみ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">銀座通り</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">買い物</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">クスリのアオキ伊賀上野店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">よい子のお家 ばしょう</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">国土省</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-3011</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ほっともっと桑町店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-3025</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">銀行</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">百五銀行　上野支店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23-7105</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ポットローズ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">大東建託パートナーズ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10/1~</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">堀川石油　銀座店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-4754</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">金属1.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ヘアカット</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NEVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">伊賀肉やまもと</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">立正佼成会</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ジェンティーレイガウエノ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">中川歯科</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">セブンイレブン伊賀忍者駅南店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">花市場</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">武田歯科</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">九庵</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-5859</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">9時半～</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">万川集海忍者体験施設</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">フラット立石（銀座）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-21</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">旧上野庁舎　SAKAKURABASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">近畿不動産</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">48-7779</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">第３週は金曜日</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">新聞</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">読売新聞　上野支局</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-5143</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">12時～</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">リエート</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">JEWRL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">森田クリニック</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22-2233</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">金属1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">エスペランサ薬局</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-5660</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">清水眼科</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23-0718</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">丸ノ内</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GEO　ゲオ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-7601</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">滋賀銀行</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-3326</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">検察庁</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-0492</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">裁判所</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ハイトメゾン丸之内</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">魚民</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-1788</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">石田サイクルビル</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">あすなろ薬局</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-9393</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">午前中</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">医療法人アクアクリニック</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-39</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">プラザあかもん</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">個別教室のトライ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">上野高校</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-2550</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">富々</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">備考欄</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">耕田090-6591-7086</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">パン工房　マームベランダ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">51-6996</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">11/10開始</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">三重ワークサービス</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-8037</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">カフェ碧（みどり）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-3001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">城北</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">服部歯科</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">感染ごみ回収不可</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ヒロタ薬局</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">48-6700</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1月8日開始</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ラム―</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">サンドラッグ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ポポラ-イーナ　Popora•Ina</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bワ-ルド</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">コメリ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-3310</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">西松屋</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-1885</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">プロマーケット</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">48-7310</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-24</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">はるやま</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22-1210</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10時までに</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ハミング</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">味神館</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23-5761</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">吉野家</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-5782</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ビッグエコー</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">23-2242</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ソフトバンク</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-1515</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ナリス化粧品</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">王将</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-8863</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">セカンドストリート</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">小田</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">小川整備</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0120-481-532</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ライフテクノサービス</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ブラコウジ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">あゆみの</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ハートヒルⅢ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">創価学会</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-7571</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">おりがみ薬局</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">41-0240</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">セイムス伊賀小田店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">セブンイレブン平野北谷店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-0877</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">トゥルーハート</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">090-5616-3265神谷</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ポナール駒</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">積和トータルサポート神谷</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ハイツホワイトピジョン</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">鳩岡090-6084-3189</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">モンノーブル</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-21</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">洋服の青山</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-2950</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Crece クレス</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-4066</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">憩の里</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">48-7721</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-27</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">特別養護老人ホーム伊賀の街</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">41-1120</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-28</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">カットA</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">44-6138</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">堀川石油　小田店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">24-2690</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q's garden</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">K-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">白鳳通り</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">すき家</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">N-24</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0120-498-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">フレックスホテル</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">21-3111</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">古本市場</x:t>
@@ -3373,17 +3373,17 @@
       <x:c r="I6" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J6" t="s">
+      <x:c r="J6" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="K6" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="K6" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="L6" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M6" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
@@ -3400,13 +3400,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G7" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="H7" t="s">
         <x:v>37</x:v>
@@ -3414,17 +3414,17 @@
       <x:c r="I7" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J7" t="s">
-        <x:v>38</x:v>
+      <x:c r="J7" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K7" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L7" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M7" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O7" t="str">
         <x:v>金属-1</x:v>
@@ -3433,7 +3433,7 @@
         <x:v>ガラ-</x:v>
       </x:c>
       <x:c r="S7" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
@@ -3450,13 +3450,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E8" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="F8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="H8" t="s">
         <x:v>37</x:v>
@@ -3464,17 +3464,17 @@
       <x:c r="I8" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J8" t="s">
-        <x:v>38</x:v>
+      <x:c r="J8" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K8" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L8" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M8" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>金属-2</x:v>
@@ -3483,7 +3483,7 @@
         <x:v>ガラ-</x:v>
       </x:c>
       <x:c r="S8" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
@@ -3500,7 +3500,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F9" t="s">
         <x:v>5</x:v>
@@ -3532,7 +3532,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F10" t="s">
         <x:v>5</x:v>
@@ -3564,22 +3564,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H11" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H11" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="J11" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L11" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M11" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
@@ -3596,19 +3596,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H12" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F12" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H12" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="J12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
@@ -3625,10 +3625,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G13" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="G13" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="H13" t="s">
         <x:v>37</x:v>
@@ -3636,11 +3636,11 @@
       <x:c r="I13" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J13" t="s">
-        <x:v>38</x:v>
+      <x:c r="J13" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K13" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L13" t="s">
         <x:v>26</x:v>
@@ -3654,7 +3654,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C14">
         <x:v>13</x:v>
@@ -3663,7 +3663,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L14" t="s">
         <x:v>26</x:v>
@@ -3674,7 +3674,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15">
         <x:v>14</x:v>
@@ -3683,19 +3683,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J15" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>金属-3</x:v>
       </x:c>
       <x:c r="S15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="U15" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="U15" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="21" customHeight="1">
@@ -3703,7 +3703,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C16">
         <x:v>15</x:v>
@@ -3712,10 +3712,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G16" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="G16" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="I16" t="s">
         <x:v>37</x:v>
@@ -3729,7 +3729,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C17">
         <x:v>16</x:v>
@@ -3738,10 +3738,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H17" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="H17" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="J17" t="s">
         <x:v>37</x:v>
@@ -3755,7 +3755,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18">
         <x:v>17</x:v>
@@ -3764,7 +3764,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I18" t="s">
         <x:v>37</x:v>
@@ -3774,7 +3774,7 @@
       </x:c>
       <x:c r="O18" t="str"/>
       <x:c r="S18" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
@@ -3791,7 +3791,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E19" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I19" t="s">
         <x:v>37</x:v>
@@ -3805,7 +3805,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C20">
         <x:v>19</x:v>
@@ -3814,7 +3814,7 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="E20" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I20" t="s">
         <x:v>37</x:v>
@@ -3825,10 +3825,10 @@
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21">
         <x:v>20</x:v>
@@ -3837,18 +3837,18 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E21" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K21" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="K21" t="s">
-        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C22">
         <x:v>21</x:v>
@@ -3857,7 +3857,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E22" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="L22" t="s">
         <x:v>26</x:v>
@@ -3865,10 +3865,10 @@
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
       <x:c r="A23" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23">
         <x:v>22</x:v>
@@ -3877,10 +3877,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E23" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G23" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="G23" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="I23" t="s">
         <x:v>37</x:v>
@@ -3897,10 +3897,10 @@
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
       <x:c r="A24" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24">
         <x:v>23</x:v>
@@ -3909,10 +3909,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E24" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G24" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="G24" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="L24" t="s">
         <x:v>26</x:v>
@@ -3923,10 +3923,10 @@
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
       <x:c r="A25" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C25">
         <x:v>24</x:v>
@@ -3935,10 +3935,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E25" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G25" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G25" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="L25" t="s">
         <x:v>26</x:v>
@@ -3946,10 +3946,10 @@
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
       <x:c r="A26" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C26">
         <x:v>25</x:v>
@@ -3958,10 +3958,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E26" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G26" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="G26" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="I26" t="s">
         <x:v>37</x:v>
@@ -3975,10 +3975,10 @@
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
       <x:c r="A27" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C27">
         <x:v>26</x:v>
@@ -3987,13 +3987,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="E27" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G27" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G27" t="s">
+      <x:c r="H27" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="H27" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="J27" t="s">
         <x:v>37</x:v>
@@ -4004,10 +4004,10 @@
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
       <x:c r="A28" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28">
         <x:v>27</x:v>
@@ -4016,7 +4016,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L28" t="s">
         <x:v>26</x:v>
@@ -4024,10 +4024,10 @@
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
       <x:c r="A29" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C29">
         <x:v>28</x:v>
@@ -4036,13 +4036,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F29" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H29" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="F29" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H29" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="I29" t="s">
         <x:v>37</x:v>
@@ -4051,13 +4051,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K29" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="L29" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M29" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>金属-5</x:v>
@@ -4066,15 +4066,15 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="S29" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="21" customHeight="1">
       <x:c r="A30" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C30">
         <x:v>29</x:v>
@@ -4083,7 +4083,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L30" t="s">
         <x:v>26</x:v>
@@ -4091,10 +4091,10 @@
     </x:row>
     <x:row r="31" ht="21" customHeight="1">
       <x:c r="A31" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C31">
         <x:v>30</x:v>
@@ -4103,10 +4103,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E31" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G31" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G31" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="I31" t="s">
         <x:v>37</x:v>
@@ -4114,10 +4114,10 @@
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
       <x:c r="A32" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C32">
         <x:v>31</x:v>
@@ -4126,27 +4126,27 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I32" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J32" t="s">
-        <x:v>38</x:v>
+      <x:c r="J32" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="O32" t="str">
         <x:v>金属-4</x:v>
       </x:c>
       <x:c r="U32" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="21" customHeight="1">
       <x:c r="A33" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C33">
         <x:v>32</x:v>
@@ -4155,27 +4155,27 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E33" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H33" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="H33" t="s">
+      <x:c r="K33" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="K33" t="s">
+      <x:c r="S33" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="S33" t="s">
+      <x:c r="U33" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="U33" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="21" customHeight="1">
       <x:c r="A34" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="B34" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="C34">
         <x:v>33</x:v>
@@ -4184,7 +4184,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F34" t="s">
         <x:v>5</x:v>
@@ -4195,11 +4195,11 @@
       <x:c r="I34" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J34" t="s">
-        <x:v>38</x:v>
+      <x:c r="J34" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K34" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="L34" t="s">
         <x:v>26</x:v>
@@ -4208,10 +4208,10 @@
     </x:row>
     <x:row r="35" ht="21" customHeight="1">
       <x:c r="A35" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C35">
         <x:v>34</x:v>
@@ -4220,7 +4220,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="L35" t="s">
         <x:v>26</x:v>
@@ -4228,10 +4228,10 @@
     </x:row>
     <x:row r="36" ht="21" customHeight="1">
       <x:c r="A36" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C36">
         <x:v>35</x:v>
@@ -4240,13 +4240,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E36" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G36" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G36" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="J36" t="s">
-        <x:v>38</x:v>
+      <x:c r="J36" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L36" t="s">
         <x:v>26</x:v>
@@ -4254,7 +4254,7 @@
     </x:row>
     <x:row r="37" ht="21" customHeight="1">
       <x:c r="A37" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B37" t="s">
         <x:v>32</x:v>
@@ -4266,13 +4266,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E37" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F37" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G37" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="F37" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G37" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="H37" t="s">
         <x:v>37</x:v>
@@ -4280,25 +4280,25 @@
       <x:c r="I37" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J37" t="s">
-        <x:v>38</x:v>
+      <x:c r="J37" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K37" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L37" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M37" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="21" customHeight="1">
       <x:c r="A38" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C38">
         <x:v>37</x:v>
@@ -4307,10 +4307,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E38" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G38" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="G38" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="L38" t="s">
         <x:v>26</x:v>
@@ -4318,10 +4318,10 @@
     </x:row>
     <x:row r="39" ht="21" customHeight="1">
       <x:c r="A39" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C39">
         <x:v>38</x:v>
@@ -4330,7 +4330,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E39" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I39" t="s">
         <x:v>37</x:v>
@@ -4340,15 +4340,15 @@
       </x:c>
       <x:c r="O39" t="str"/>
       <x:c r="S39" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="U39" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="U39" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="21" customHeight="1">
       <x:c r="A40" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B40" t="s">
         <x:v>27</x:v>
@@ -4360,27 +4360,27 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E40" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G40" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G40" t="s">
+      <x:c r="K40" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="K40" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="O40" t="str">
         <x:v>金属-19</x:v>
       </x:c>
       <x:c r="U40" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="21" customHeight="1">
       <x:c r="A41" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C41">
         <x:v>40</x:v>
@@ -4389,18 +4389,18 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="E41" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="J41" t="s">
-        <x:v>38</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="M41" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="21" customHeight="1">
       <x:c r="A42" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" t="s">
         <x:v>32</x:v>
@@ -4412,18 +4412,18 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E42" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K42" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="K42" t="s">
-        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="21" customHeight="1">
       <x:c r="A43" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C43">
         <x:v>42</x:v>
@@ -4432,7 +4432,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="E43" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L43" t="s">
         <x:v>26</x:v>
@@ -4440,10 +4440,10 @@
     </x:row>
     <x:row r="44" ht="21" customHeight="1">
       <x:c r="A44" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C44">
         <x:v>43</x:v>
@@ -4452,18 +4452,18 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E44" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="J44" t="s">
-        <x:v>38</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="21" customHeight="1">
       <x:c r="A45" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C45">
         <x:v>44</x:v>
@@ -4472,18 +4472,18 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E45" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="J45" t="s">
-        <x:v>38</x:v>
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="21" customHeight="1">
       <x:c r="A46" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C46">
         <x:v>45</x:v>
@@ -4492,28 +4492,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="E46" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F46" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H46" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I46" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J46" t="s">
-        <x:v>38</x:v>
+      <x:c r="J46" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K46" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="L46" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M46" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O46" t="str">
         <x:v>金属-20</x:v>
@@ -4524,10 +4524,10 @@
     </x:row>
     <x:row r="47" ht="21" customHeight="1">
       <x:c r="A47" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C47">
         <x:v>46</x:v>
@@ -4536,7 +4536,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E47" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H47" t="s">
         <x:v>37</x:v>
@@ -4547,10 +4547,10 @@
     </x:row>
     <x:row r="48" ht="21" customHeight="1">
       <x:c r="A48" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C48">
         <x:v>47</x:v>
@@ -4559,7 +4559,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E48" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L48" t="s">
         <x:v>26</x:v>
@@ -4567,7 +4567,7 @@
     </x:row>
     <x:row r="49" ht="21" customHeight="1">
       <x:c r="A49" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B49" t="s">
         <x:v>32</x:v>
@@ -4579,27 +4579,27 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="E49" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G49" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G49" t="s">
+      <x:c r="H49" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K49" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H49" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K49" t="s">
+      <x:c r="U49" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="U49" t="s">
-        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="21" customHeight="1">
       <x:c r="A50" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C50">
         <x:v>49</x:v>
@@ -4608,13 +4608,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E50" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H50" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J50" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J50" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L50" t="s">
         <x:v>26</x:v>
@@ -4622,10 +4622,10 @@
     </x:row>
     <x:row r="51" ht="21" customHeight="1">
       <x:c r="A51" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C51">
         <x:v>50</x:v>
@@ -4634,21 +4634,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E51" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H51" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K51" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="H51" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K51" t="s">
-        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="21" customHeight="1">
       <x:c r="A52" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C52">
         <x:v>51</x:v>
@@ -4657,16 +4657,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E52" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F52" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H52" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J52" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J52" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L52" t="s">
         <x:v>26</x:v>
@@ -4674,10 +4674,10 @@
     </x:row>
     <x:row r="53" ht="21" customHeight="1">
       <x:c r="A53" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C53">
         <x:v>52</x:v>
@@ -4686,24 +4686,24 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E53" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G53" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="G53" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="L53" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="S53" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="21" customHeight="1">
       <x:c r="A54" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C54">
         <x:v>53</x:v>
@@ -4712,21 +4712,21 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="E54" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G54" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="G54" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="I54" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="U54" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="21" customHeight="1">
       <x:c r="A55" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B55" t="s">
         <x:v>32</x:v>
@@ -4738,18 +4738,18 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E55" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H55" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K55" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="21" customHeight="1">
       <x:c r="A56" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B56" t="s">
         <x:v>32</x:v>
@@ -4761,18 +4761,18 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E56" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="K56" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="K56" t="s">
-        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="21" customHeight="1">
       <x:c r="A57" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C57">
         <x:v>56</x:v>
@@ -4781,10 +4781,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E57" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G57" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="G57" t="s">
-        <x:v>158</x:v>
       </x:c>
       <x:c r="L57" t="s">
         <x:v>26</x:v>
@@ -4793,15 +4793,15 @@
         <x:v>金属-22</x:v>
       </x:c>
       <x:c r="U57" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="21" customHeight="1">
       <x:c r="A58" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C58">
         <x:v>57</x:v>
@@ -4810,16 +4810,16 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E58" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G58" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="G58" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="H58" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J58" t="s">
-        <x:v>38</x:v>
+      <x:c r="J58" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L58" t="s">
         <x:v>26</x:v>
@@ -4827,10 +4827,10 @@
     </x:row>
     <x:row r="59" ht="21" customHeight="1">
       <x:c r="A59" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C59">
         <x:v>58</x:v>
@@ -4839,27 +4839,27 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E59" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G59" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G59" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="J59" t="s">
-        <x:v>38</x:v>
+      <x:c r="J59" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="O59" t="str">
         <x:v>金属-21</x:v>
       </x:c>
       <x:c r="U59" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="21" customHeight="1">
       <x:c r="A60" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C60">
         <x:v>59</x:v>
@@ -4868,16 +4868,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E60" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G60" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="G60" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="H60" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J60" t="s">
-        <x:v>38</x:v>
+      <x:c r="J60" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L60" t="s">
         <x:v>26</x:v>
@@ -4885,10 +4885,10 @@
     </x:row>
     <x:row r="61" ht="21" customHeight="1">
       <x:c r="A61" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C61">
         <x:v>60</x:v>
@@ -4897,10 +4897,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="E61" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G61" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="G61" t="s">
-        <x:v>168</x:v>
       </x:c>
       <x:c r="L61" t="s">
         <x:v>26</x:v>
@@ -4908,10 +4908,10 @@
     </x:row>
     <x:row r="62" ht="21" customHeight="1">
       <x:c r="A62" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C62">
         <x:v>61</x:v>
@@ -4920,13 +4920,13 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="E62" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F62" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G62" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="F62" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G62" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="L62" t="s">
         <x:v>26</x:v>
@@ -4937,10 +4937,10 @@
     </x:row>
     <x:row r="63" ht="21" customHeight="1">
       <x:c r="A63" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C63">
         <x:v>62</x:v>
@@ -4949,13 +4949,13 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E63" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F63" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G63" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="F63" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G63" t="s">
-        <x:v>172</x:v>
       </x:c>
       <x:c r="L63" t="s">
         <x:v>26</x:v>
@@ -4963,10 +4963,10 @@
     </x:row>
     <x:row r="64" ht="21" customHeight="1">
       <x:c r="A64" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C64">
         <x:v>63</x:v>
@@ -4975,15 +4975,15 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E64" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="J64" t="s">
-        <x:v>38</x:v>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="J64" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="21" customHeight="1">
       <x:c r="A65" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B65" t="s">
         <x:v>32</x:v>
@@ -4995,31 +4995,31 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="E65" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F65" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G65" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="F65" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G65" t="s">
-        <x:v>175</x:v>
-      </x:c>
       <x:c r="H65" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I65" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J65" t="s">
-        <x:v>38</x:v>
+      <x:c r="J65" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K65" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="L65" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="M65" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="Q65" t="str">
         <x:v>ガラ-</x:v>
@@ -5027,10 +5027,10 @@
     </x:row>
     <x:row r="66" ht="21" customHeight="1">
       <x:c r="A66" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C66">
         <x:v>65</x:v>
@@ -5039,7 +5039,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E66" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="I66" t="s">
         <x:v>37</x:v>
@@ -5047,10 +5047,10 @@
     </x:row>
     <x:row r="67" ht="21" customHeight="1">
       <x:c r="A67" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C67">
         <x:v>66</x:v>
@@ -5059,24 +5059,24 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="E67" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G67" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G67" t="s">
+      <x:c r="J67" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="U67" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="J67" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="U67" t="s">
-        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="21" customHeight="1">
       <x:c r="A68" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C68">
         <x:v>67</x:v>
@@ -5085,18 +5085,18 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E68" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K68" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="K68" t="s">
-        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="21" customHeight="1">
       <x:c r="A69" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C69">
         <x:v>68</x:v>
@@ -5105,18 +5105,18 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E69" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="J69" t="s">
-        <x:v>38</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="21" customHeight="1">
       <x:c r="A70" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C70">
         <x:v>69</x:v>
@@ -5125,22 +5125,22 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="E70" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="I70" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="L70" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="I70" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L70" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="O70" t="str"/>
     </x:row>
     <x:row r="71" ht="21" customHeight="1">
       <x:c r="A71" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C71">
         <x:v>70</x:v>
@@ -5149,13 +5149,13 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="E71" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G71" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="G71" t="s">
-        <x:v>187</x:v>
-      </x:c>
       <x:c r="I71" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="L71" t="s">
         <x:v>25</x:v>
@@ -5169,10 +5169,10 @@
     </x:row>
     <x:row r="72" ht="21" customHeight="1">
       <x:c r="A72" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C72">
         <x:v>71</x:v>
@@ -5181,27 +5181,27 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="E72" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G72" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G72" t="s">
+      <x:c r="I72" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="I72" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="L72" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="O72" t="str">
         <x:v>金属-25</x:v>
       </x:c>
       <x:c r="S72" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="21" customHeight="1">
       <x:c r="A73" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B73" t="s">
         <x:v>32</x:v>
@@ -5213,30 +5213,30 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="E73" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G73" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="G73" t="s">
+      <x:c r="I73" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="I73" t="s">
+      <x:c r="L73" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="S73" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="L73" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="S73" t="s">
-        <x:v>195</x:v>
-      </x:c>
       <x:c r="U73" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="21" customHeight="1">
       <x:c r="A74" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C74">
         <x:v>73</x:v>
@@ -5245,24 +5245,24 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="E74" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G74" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G74" t="s">
+      <x:c r="I74" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="I74" t="s">
-        <x:v>198</x:v>
-      </x:c>
       <x:c r="L74" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="U74" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="21" customHeight="1">
       <x:c r="A75" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B75" t="s">
         <x:v>32</x:v>
@@ -5274,24 +5274,24 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="E75" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G75" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G75" t="s">
+      <x:c r="I75" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="I75" t="s">
-        <x:v>201</x:v>
-      </x:c>
       <x:c r="L75" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="21" customHeight="1">
       <x:c r="A76" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C76">
         <x:v>75</x:v>
@@ -5300,21 +5300,21 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="E76" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="M76" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S76" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="M76" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="S76" t="s">
-        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="21" customHeight="1">
       <x:c r="A77" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C77">
         <x:v>76</x:v>
@@ -5323,27 +5323,27 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="E77" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G77" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G77" t="s">
+      <x:c r="I77" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="I77" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="L77" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="S77" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="U77" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="21" customHeight="1">
       <x:c r="A78" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B78" t="s">
         <x:v>32</x:v>
@@ -5355,7 +5355,7 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E78" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F78" t="s">
         <x:v>5</x:v>
@@ -5364,28 +5364,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="I78" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="J78" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="K78" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="J78" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="K78" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="L78" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M78" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O78" t="str"/>
     </x:row>
     <x:row r="79" ht="21" customHeight="1">
       <x:c r="A79" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C79">
         <x:v>78</x:v>
@@ -5394,13 +5394,13 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="E79" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H79" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J79" t="s">
-        <x:v>38</x:v>
+      <x:c r="J79" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L79" t="s">
         <x:v>37</x:v>
@@ -5408,7 +5408,7 @@
     </x:row>
     <x:row r="80" ht="21" customHeight="1">
       <x:c r="A80" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B80" t="s">
         <x:v>32</x:v>
@@ -5423,18 +5423,18 @@
         <x:v>K-FORCE　ひみつきち</x:v>
       </x:c>
       <x:c r="I80" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="L80" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="21" customHeight="1">
       <x:c r="A81" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C81">
         <x:v>80</x:v>
@@ -5443,21 +5443,21 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="E81" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="I81" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="I81" t="s">
-        <x:v>214</x:v>
-      </x:c>
       <x:c r="L81" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="21" customHeight="1">
       <x:c r="A82" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B82" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C82">
         <x:v>81</x:v>
@@ -5466,39 +5466,39 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="E82" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F82" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G82" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="F82" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G82" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="H82" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I82" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="J82" t="s">
-        <x:v>38</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="J82" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K82" t="s">
-        <x:v>218</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="L82" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M82" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="21" customHeight="1">
       <x:c r="A83" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B83" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C83">
         <x:v>82</x:v>
@@ -5507,19 +5507,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="E83" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F83" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G83" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="F83" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G83" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="H83" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J83" t="s">
-        <x:v>38</x:v>
+      <x:c r="J83" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L83" t="s">
         <x:v>37</x:v>
@@ -5527,10 +5527,10 @@
     </x:row>
     <x:row r="84" ht="21" customHeight="1">
       <x:c r="A84" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B84" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C84">
         <x:v>83</x:v>
@@ -5539,36 +5539,36 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E84" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G84" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="G84" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="H84" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I84" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="J84" t="s">
-        <x:v>38</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="J84" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K84" t="s">
-        <x:v>223</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="L84" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M84" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="21" customHeight="1">
       <x:c r="A85" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B85" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C85">
         <x:v>84</x:v>
@@ -5577,10 +5577,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E85" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G85" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="G85" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="H85" t="s">
         <x:v>37</x:v>
@@ -5589,12 +5589,12 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="U85" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="21" customHeight="1">
       <x:c r="A86" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B86" t="s">
         <x:v>32</x:v>
@@ -5606,16 +5606,16 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="E86" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G86" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="G86" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="H86" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J86" t="s">
-        <x:v>38</x:v>
+      <x:c r="J86" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L86" t="s">
         <x:v>37</x:v>
@@ -5627,7 +5627,7 @@
     </x:row>
     <x:row r="87" ht="21" customHeight="1">
       <x:c r="A87" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B87" t="s">
         <x:v>32</x:v>
@@ -5639,33 +5639,33 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E87" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G87" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="G87" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="H87" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I87" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="J87" t="s">
-        <x:v>38</x:v>
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J87" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K87" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="L87" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M87" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="21" customHeight="1">
       <x:c r="A88" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B88" t="s">
         <x:v>32</x:v>
@@ -5677,22 +5677,22 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E88" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G88" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="G88" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="H88" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I88" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="J88" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="J88" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K88" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="L88" t="s">
         <x:v>37</x:v>
@@ -5706,10 +5706,10 @@
     </x:row>
     <x:row r="89" ht="21" customHeight="1">
       <x:c r="A89" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C89">
         <x:v>88</x:v>
@@ -5718,19 +5718,19 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="E89" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G89" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="G89" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="H89" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I89" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K89" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="L89" t="s">
         <x:v>37</x:v>
@@ -5738,10 +5738,10 @@
     </x:row>
     <x:row r="90" ht="21" customHeight="1">
       <x:c r="A90" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B90" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C90">
         <x:v>89</x:v>
@@ -5750,19 +5750,19 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="E90" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H90" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I90" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="J90" t="s">
-        <x:v>38</x:v>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="J90" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K90" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L90" t="s">
         <x:v>37</x:v>
@@ -5770,7 +5770,7 @@
     </x:row>
     <x:row r="91" ht="21" customHeight="1">
       <x:c r="A91" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B91" t="s">
         <x:v>32</x:v>
@@ -5782,22 +5782,22 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="E91" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G91" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="G91" t="s">
-        <x:v>242</x:v>
       </x:c>
       <x:c r="H91" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I91" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J91" t="s">
-        <x:v>38</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K91" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="L91" t="s">
         <x:v>37</x:v>
@@ -5811,10 +5811,10 @@
     </x:row>
     <x:row r="92" ht="21" customHeight="1">
       <x:c r="A92" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B92" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C92">
         <x:v>91</x:v>
@@ -5823,13 +5823,13 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E92" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H92" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J92" t="s">
-        <x:v>38</x:v>
+      <x:c r="J92" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L92" t="s">
         <x:v>37</x:v>
@@ -5840,7 +5840,7 @@
     </x:row>
     <x:row r="93" ht="21" customHeight="1">
       <x:c r="A93" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B93" t="s">
         <x:v>27</x:v>
@@ -5852,27 +5852,27 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="E93" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G93" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="I93" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="L93" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="S93" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="21" customHeight="1">
       <x:c r="A94" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C94">
         <x:v>93</x:v>
@@ -5881,13 +5881,13 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="E94" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="F94" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="I94" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="L94" t="s">
         <x:v>37</x:v>
@@ -5895,7 +5895,7 @@
     </x:row>
     <x:row r="95" ht="21" customHeight="1">
       <x:c r="A95" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B95" t="s">
         <x:v>32</x:v>
@@ -5907,21 +5907,21 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="E95" t="s">
-        <x:v>249</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H95" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K95" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="21" customHeight="1">
       <x:c r="A96" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C96">
         <x:v>95</x:v>
@@ -5930,21 +5930,21 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="E96" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H96" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K96" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="21" customHeight="1">
       <x:c r="A97" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C97">
         <x:v>96</x:v>
@@ -5953,10 +5953,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="E97" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="I97" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="L97" t="s">
         <x:v>37</x:v>
@@ -5964,10 +5964,10 @@
     </x:row>
     <x:row r="98" ht="21" customHeight="1">
       <x:c r="A98" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C98">
         <x:v>97</x:v>
@@ -5976,24 +5976,24 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="E98" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F98" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G98" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="F98" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G98" t="s">
+      <x:c r="K98" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="K98" t="s">
-        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="21" customHeight="1">
       <x:c r="A99" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B99" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C99">
         <x:v>98</x:v>
@@ -6002,10 +6002,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="E99" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G99" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="G99" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="L99" t="s">
         <x:v>37</x:v>
@@ -6013,10 +6013,10 @@
     </x:row>
     <x:row r="100" ht="21" customHeight="1">
       <x:c r="A100" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B100" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C100">
         <x:v>99</x:v>
@@ -6025,13 +6025,13 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="E100" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H100" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J100" t="s">
-        <x:v>38</x:v>
+      <x:c r="J100" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L100" t="s">
         <x:v>37</x:v>
@@ -6039,10 +6039,10 @@
     </x:row>
     <x:row r="101" ht="21" customHeight="1">
       <x:c r="A101" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B101" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C101">
         <x:v>100</x:v>
@@ -6051,31 +6051,31 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="E101" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F101" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G101" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="F101" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G101" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="H101" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="I101" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="J101" t="s">
-        <x:v>38</x:v>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K101" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="L101" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M101" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O101" t="str">
         <x:v>金属-27</x:v>
@@ -6086,10 +6086,10 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B102" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C102">
         <x:v>101</x:v>
@@ -6098,24 +6098,24 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="E102" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G102" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="K102" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="G102" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="K102" t="s">
+      <x:c r="S102" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="S102" t="s">
-        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="21" customHeight="1">
       <x:c r="A103" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C103">
         <x:v>102</x:v>
@@ -6124,24 +6124,24 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="E103" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H103" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K103" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="S103" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="S103" t="s">
-        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="21" customHeight="1">
       <x:c r="A104" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C104">
         <x:v>103</x:v>
@@ -6150,30 +6150,30 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E104" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G104" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H104" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K104" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="O104" t="str">
         <x:v>金属-26</x:v>
       </x:c>
       <x:c r="S104" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="21" customHeight="1">
       <x:c r="A105" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C105">
         <x:v>104</x:v>
@@ -6182,21 +6182,21 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="E105" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="H105" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K105" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="21" customHeight="1">
       <x:c r="A106" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B106" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C106">
         <x:v>105</x:v>
@@ -6205,24 +6205,24 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="E106" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G106" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="G106" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="L106" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="U106" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="21" customHeight="1">
       <x:c r="A107" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B107" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C107">
         <x:v>106</x:v>
@@ -6231,24 +6231,24 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E107" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G107" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="G107" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="H107" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K107" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="21" customHeight="1">
       <x:c r="A108" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B108" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C108">
         <x:v>107</x:v>
@@ -6257,10 +6257,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="E108" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G108" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="G108" t="s">
-        <x:v>280</x:v>
       </x:c>
       <x:c r="H108" t="s">
         <x:v>37</x:v>
@@ -6268,25 +6268,25 @@
       <x:c r="I108" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J108" t="s">
-        <x:v>38</x:v>
+      <x:c r="J108" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K108" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="L108" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M108" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="21" customHeight="1">
       <x:c r="A109" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B109" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C109">
         <x:v>108</x:v>
@@ -6295,13 +6295,13 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="E109" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F109" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G109" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="F109" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G109" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="H109" t="s">
         <x:v>37</x:v>
@@ -6309,25 +6309,25 @@
       <x:c r="I109" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J109" t="s">
-        <x:v>38</x:v>
+      <x:c r="J109" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K109" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="L109" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="M109" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="21" customHeight="1">
       <x:c r="A110" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B110" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C110">
         <x:v>109</x:v>
@@ -6336,21 +6336,21 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="E110" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G110" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G110" t="s">
+      <x:c r="H110" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K110" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="H110" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K110" t="s">
-        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="21" customHeight="1">
       <x:c r="A111" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B111" t="s">
         <x:v>27</x:v>
@@ -6362,30 +6362,30 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="E111" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G111" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="G111" t="s">
+      <x:c r="H111" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K111" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="H111" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K111" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="O111" t="str">
         <x:v>金属-31</x:v>
       </x:c>
       <x:c r="U111" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="21" customHeight="1">
       <x:c r="A112" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B112" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C112">
         <x:v>111</x:v>
@@ -6394,18 +6394,18 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="E112" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H112" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K112" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="21" customHeight="1">
       <x:c r="A113" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B113" t="s">
         <x:v>32</x:v>
@@ -6417,31 +6417,31 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="E113" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F113" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G113" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H113" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I113" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="F113" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G113" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H113" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="I113" t="s">
+      <x:c r="J113" t="str">
+        <x:v>M-</x:v>
+      </x:c>
+      <x:c r="K113" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="J113" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="K113" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="L113" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="M113" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O113" t="str">
         <x:v>金属-33</x:v>
@@ -6450,12 +6450,12 @@
         <x:v>ガラ-</x:v>
       </x:c>
       <x:c r="S113" t="s">
-        <x:v>297</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="21" customHeight="1">
       <x:c r="A114" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B114" t="s">
         <x:v>32</x:v>
@@ -6467,19 +6467,19 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="E114" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G114" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="G114" t="s">
+      <x:c r="H114" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="H114" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="J114" t="s">
-        <x:v>38</x:v>
+      <x:c r="J114" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L114" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="O114" t="str">
         <x:v>金属-32</x:v>
@@ -6490,10 +6490,10 @@
     </x:row>
     <x:row r="115" ht="21" customHeight="1">
       <x:c r="A115" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B115" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C115">
         <x:v>114</x:v>
@@ -6511,19 +6511,19 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="H115" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I115" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="J115" t="s">
-        <x:v>38</x:v>
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K115" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="L115" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="O115" t="str">
         <x:v>金属-34</x:v>
@@ -6534,10 +6534,10 @@
     </x:row>
     <x:row r="116" ht="21" customHeight="1">
       <x:c r="A116" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B116" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C116">
         <x:v>115</x:v>
@@ -6549,10 +6549,10 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="I116" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="L116" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="O116" t="str">
         <x:v>金属-35</x:v>
@@ -6560,10 +6560,10 @@
     </x:row>
     <x:row r="117" ht="21" customHeight="1">
       <x:c r="A117" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B117" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C117">
         <x:v>116</x:v>
@@ -6574,17 +6574,17 @@
       <x:c r="E117" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="J117" t="s">
-        <x:v>38</x:v>
+      <x:c r="J117" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="O117" t="str"/>
     </x:row>
     <x:row r="118" ht="21" customHeight="1">
       <x:c r="A118" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B118" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C118">
         <x:v>117</x:v>
@@ -6599,15 +6599,15 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="I118" t="s">
-        <x:v>287</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="L118" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="21" customHeight="1">
       <x:c r="A119" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B119" t="s">
         <x:v>27</x:v>
@@ -6625,12 +6625,12 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="L119" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="21" customHeight="1">
       <x:c r="A120" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B120" t="s">
         <x:v>22</x:v>
@@ -6648,15 +6648,15 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="L120" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="21" customHeight="1">
       <x:c r="A121" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B121" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C121">
         <x:v>120</x:v>
@@ -6671,13 +6671,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="H121" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J121" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L121" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="O121" t="str">
         <x:v>金属-36</x:v>
@@ -6685,7 +6685,7 @@
     </x:row>
     <x:row r="122" ht="21" customHeight="1">
       <x:c r="A122" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B122" t="s">
         <x:v>32</x:v>
@@ -6703,13 +6703,13 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="H122" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J122" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L122" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="U122" t="s">
         <x:v>314</x:v>
@@ -6717,10 +6717,10 @@
     </x:row>
     <x:row r="123" ht="21" customHeight="1">
       <x:c r="A123" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B123" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C123">
         <x:v>122</x:v>
@@ -6738,15 +6738,15 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="L123" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="21" customHeight="1">
       <x:c r="A124" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B124" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C124">
         <x:v>123</x:v>
@@ -6761,15 +6761,15 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="L124" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="21" customHeight="1">
       <x:c r="A125" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B125" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C125">
         <x:v>124</x:v>
@@ -6784,12 +6784,12 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="L125" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="21" customHeight="1">
       <x:c r="A126" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B126" t="s">
         <x:v>32</x:v>
@@ -6807,13 +6807,13 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="H126" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J126" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J126" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L126" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="O126" t="str">
         <x:v>金属-37</x:v>
@@ -6824,10 +6824,10 @@
     </x:row>
     <x:row r="127" ht="21" customHeight="1">
       <x:c r="A127" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B127" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C127">
         <x:v>126</x:v>
@@ -6839,7 +6839,7 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="H127" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K127" t="s">
         <x:v>319</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="128" ht="21" customHeight="1">
       <x:c r="A128" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B128" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C128">
         <x:v>127</x:v>
@@ -6862,7 +6862,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="H128" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K128" t="s">
         <x:v>317</x:v>
@@ -6870,10 +6870,10 @@
     </x:row>
     <x:row r="129" ht="21" customHeight="1">
       <x:c r="A129" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B129" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C129">
         <x:v>128</x:v>
@@ -6885,7 +6885,7 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="H129" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K129" t="s">
         <x:v>309</x:v>
@@ -6896,10 +6896,10 @@
     </x:row>
     <x:row r="130" ht="21" customHeight="1">
       <x:c r="A130" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B130" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C130">
         <x:v>129</x:v>
@@ -6911,10 +6911,10 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="G130" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H130" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K130" t="s">
         <x:v>321</x:v>
@@ -6923,12 +6923,12 @@
         <x:v>金属-38</x:v>
       </x:c>
       <x:c r="S130" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="21" customHeight="1">
       <x:c r="A131" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B131" t="s">
         <x:v>32</x:v>
@@ -6949,30 +6949,30 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="H131" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I131" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="J131" t="s">
-        <x:v>38</x:v>
+      <x:c r="J131" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K131" t="s">
         <x:v>331</x:v>
       </x:c>
       <x:c r="L131" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="M131" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="21" customHeight="1">
       <x:c r="A132" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B132" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C132">
         <x:v>131</x:v>
@@ -6984,7 +6984,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="H132" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K132" t="s">
         <x:v>333</x:v>
@@ -6992,10 +6992,10 @@
     </x:row>
     <x:row r="133" ht="21" customHeight="1">
       <x:c r="A133" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B133" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C133">
         <x:v>132</x:v>
@@ -7015,7 +7015,7 @@
     </x:row>
     <x:row r="134" ht="21" customHeight="1">
       <x:c r="A134" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B134" t="s">
         <x:v>32</x:v>
@@ -7035,10 +7035,10 @@
     </x:row>
     <x:row r="135" ht="21" customHeight="1">
       <x:c r="A135" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B135" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C135">
         <x:v>134</x:v>
@@ -7053,7 +7053,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H135" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I135" t="s">
         <x:v>340</x:v>
@@ -7062,10 +7062,10 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="L135" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="M135" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="O135" t="str">
         <x:v>金属-39</x:v>
@@ -7076,10 +7076,10 @@
     </x:row>
     <x:row r="136" ht="21" customHeight="1">
       <x:c r="A136" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B136" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C136">
         <x:v>135</x:v>
@@ -7091,7 +7091,7 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="H136" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K136" t="s">
         <x:v>343</x:v>
@@ -7099,10 +7099,10 @@
     </x:row>
     <x:row r="137" ht="21" customHeight="1">
       <x:c r="A137" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C137">
         <x:v>136</x:v>
@@ -7117,7 +7117,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="H137" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K137" t="s">
         <x:v>346</x:v>
@@ -7125,10 +7125,10 @@
     </x:row>
     <x:row r="138" ht="21" customHeight="1">
       <x:c r="A138" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C138">
         <x:v>137</x:v>
@@ -7140,7 +7140,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="H138" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K138" t="s">
         <x:v>348</x:v>
@@ -7148,10 +7148,10 @@
     </x:row>
     <x:row r="139" ht="21" customHeight="1">
       <x:c r="A139" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C139">
         <x:v>138</x:v>
@@ -7169,15 +7169,15 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="L139" t="s">
-        <x:v>296</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="21" customHeight="1">
       <x:c r="A140" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B140" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C140">
         <x:v>139</x:v>
@@ -7189,7 +7189,7 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="H140" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K140" t="s">
         <x:v>352</x:v>
@@ -7197,10 +7197,10 @@
     </x:row>
     <x:row r="141" ht="21" customHeight="1">
       <x:c r="A141" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B141" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C141">
         <x:v>140</x:v>
@@ -7221,7 +7221,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="L141" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="O141" t="str">
         <x:v>金属-40</x:v>
@@ -7229,10 +7229,10 @@
     </x:row>
     <x:row r="142" ht="21" customHeight="1">
       <x:c r="A142" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B142" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C142">
         <x:v>141</x:v>
@@ -7244,7 +7244,7 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="H142" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K142" t="s">
         <x:v>340</x:v>
@@ -7252,10 +7252,10 @@
     </x:row>
     <x:row r="143" ht="21" customHeight="1">
       <x:c r="A143" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B143" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C143">
         <x:v>142</x:v>
@@ -7273,13 +7273,13 @@
         <x:v>357</x:v>
       </x:c>
       <x:c r="H143" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J143" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J143" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L143" t="s">
-        <x:v>287</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="O143" t="str"/>
     </x:row>
@@ -7309,7 +7309,7 @@
         <x:v>金属-41</x:v>
       </x:c>
       <x:c r="U144" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="21" customHeight="1">
@@ -7332,7 +7332,7 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="H145" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K145" t="s">
         <x:v>364</x:v>
@@ -7346,7 +7346,7 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="B146" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C146">
         <x:v>145</x:v>
@@ -7375,7 +7375,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B147" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C147">
         <x:v>146</x:v>
@@ -7398,7 +7398,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B148" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C148">
         <x:v>147</x:v>
@@ -7418,7 +7418,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B149" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C149">
         <x:v>148</x:v>
@@ -7433,7 +7433,7 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="H149" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K149" t="s">
         <x:v>373</x:v>
@@ -7447,7 +7447,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B150" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C150">
         <x:v>149</x:v>
@@ -7473,7 +7473,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B151" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C151">
         <x:v>150</x:v>
@@ -7522,7 +7522,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B153" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C153">
         <x:v>152</x:v>
@@ -7534,7 +7534,7 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="H153" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K153" t="s">
         <x:v>381</x:v>
@@ -7563,13 +7563,13 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="H154" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I154" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="J154" t="s">
-        <x:v>38</x:v>
+      <x:c r="J154" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K154" t="s">
         <x:v>384</x:v>
@@ -7578,7 +7578,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="M154" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="21" customHeight="1">
@@ -7586,7 +7586,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B155" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C155">
         <x:v>154</x:v>
@@ -7606,7 +7606,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B156" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C156">
         <x:v>155</x:v>
@@ -7621,10 +7621,10 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="H156" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J156" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J156" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L156" t="s">
         <x:v>319</x:v>
@@ -7635,7 +7635,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B157" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C157">
         <x:v>156</x:v>
@@ -7661,7 +7661,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B158" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C158">
         <x:v>157</x:v>
@@ -7676,7 +7676,7 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="H158" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K158" t="s">
         <x:v>392</x:v>
@@ -7687,7 +7687,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B159" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C159">
         <x:v>158</x:v>
@@ -7707,7 +7707,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B160" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C160">
         <x:v>159</x:v>
@@ -7722,13 +7722,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H160" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I160" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="J160" t="s">
-        <x:v>38</x:v>
+      <x:c r="J160" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K160" t="s">
         <x:v>395</x:v>
@@ -7745,7 +7745,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B161" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C161">
         <x:v>160</x:v>
@@ -7760,13 +7760,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H161" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I161" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="J161" t="s">
-        <x:v>38</x:v>
+      <x:c r="J161" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K161" t="s">
         <x:v>397</x:v>
@@ -7789,7 +7789,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B162" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C162">
         <x:v>161</x:v>
@@ -7815,7 +7815,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B163" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C163">
         <x:v>162</x:v>
@@ -7844,7 +7844,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B164" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C164">
         <x:v>163</x:v>
@@ -7864,7 +7864,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B165" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C165">
         <x:v>164</x:v>
@@ -7876,7 +7876,7 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="H165" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K165" t="s">
         <x:v>408</x:v>
@@ -7893,7 +7893,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B166" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C166">
         <x:v>165</x:v>
@@ -7916,7 +7916,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B167" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C167">
         <x:v>166</x:v>
@@ -7928,7 +7928,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="H167" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="L167" t="s">
         <x:v>343</x:v>
@@ -7939,7 +7939,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B168" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C168">
         <x:v>167</x:v>
@@ -7959,7 +7959,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B169" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C169">
         <x:v>168</x:v>
@@ -7985,7 +7985,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B170" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C170">
         <x:v>169</x:v>
@@ -7997,7 +7997,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="H170" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K170" t="s">
         <x:v>417</x:v>
@@ -8008,7 +8008,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B171" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C171">
         <x:v>170</x:v>
@@ -8020,7 +8020,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="H171" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K171" t="s">
         <x:v>419</x:v>
@@ -8032,7 +8032,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B172" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C172">
         <x:v>171</x:v>
@@ -8055,7 +8055,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B173" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C173">
         <x:v>172</x:v>
@@ -8096,10 +8096,10 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="H174" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="J174" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J174" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L174" t="s">
         <x:v>373</x:v>
@@ -8113,7 +8113,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B175" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C175">
         <x:v>174</x:v>
@@ -8133,7 +8133,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B176" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C176">
         <x:v>175</x:v>
@@ -8147,8 +8147,8 @@
       <x:c r="G176" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="J176" t="s">
-        <x:v>38</x:v>
+      <x:c r="J176" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="21" customHeight="1">
@@ -8174,13 +8174,13 @@
         <x:v>432</x:v>
       </x:c>
       <x:c r="H177" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I177" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="J177" t="s">
-        <x:v>38</x:v>
+      <x:c r="J177" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="K177" t="s">
         <x:v>433</x:v>
@@ -8203,7 +8203,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B178" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C178">
         <x:v>177</x:v>
@@ -8223,7 +8223,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B179" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C179">
         <x:v>178</x:v>
@@ -8246,7 +8246,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B180" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C180">
         <x:v>179</x:v>
@@ -8275,7 +8275,7 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B181" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C181">
         <x:v>180</x:v>
@@ -8286,8 +8286,8 @@
       <x:c r="E181" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="J181" t="s">
-        <x:v>38</x:v>
+      <x:c r="J181" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="21" customHeight="1">
@@ -8295,7 +8295,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B182" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C182">
         <x:v>181</x:v>
@@ -8321,7 +8321,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B183" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C183">
         <x:v>182</x:v>
@@ -8347,7 +8347,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B184" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C184">
         <x:v>183</x:v>
@@ -8358,8 +8358,8 @@
       <x:c r="E184" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="J184" t="s">
-        <x:v>38</x:v>
+      <x:c r="J184" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="O184" t="str">
         <x:v>金属-52</x:v>
@@ -8393,7 +8393,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B186" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C186">
         <x:v>185</x:v>
@@ -8410,8 +8410,8 @@
       <x:c r="G186" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="J186" t="s">
-        <x:v>38</x:v>
+      <x:c r="J186" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="M186" t="s">
         <x:v>398</x:v>
@@ -8436,8 +8436,8 @@
       <x:c r="G187" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="J187" t="s">
-        <x:v>38</x:v>
+      <x:c r="J187" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="M187" t="s">
         <x:v>398</x:v>
@@ -8451,7 +8451,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B188" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C188">
         <x:v>187</x:v>
@@ -8465,8 +8465,8 @@
       <x:c r="G188" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="J188" t="s">
-        <x:v>38</x:v>
+      <x:c r="J188" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="M188" t="s">
         <x:v>398</x:v>
@@ -8477,7 +8477,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B189" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C189">
         <x:v>188</x:v>
@@ -8530,7 +8530,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B191" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C191">
         <x:v>190</x:v>
@@ -8566,7 +8566,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B192" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C192">
         <x:v>191</x:v>
@@ -8589,7 +8589,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B193" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C193">
         <x:v>192</x:v>
@@ -8612,7 +8612,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B194" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C194">
         <x:v>193</x:v>
@@ -8638,7 +8638,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B195" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C195">
         <x:v>194</x:v>
@@ -8664,7 +8664,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B196" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C196">
         <x:v>195</x:v>
@@ -8684,7 +8684,7 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B197" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C197">
         <x:v>196</x:v>
@@ -8725,7 +8725,7 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B198" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C198">
         <x:v>197</x:v>
@@ -8763,7 +8763,7 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B199" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C199">
         <x:v>198</x:v>
@@ -8820,7 +8820,7 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B201" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C201">
         <x:v>200</x:v>
@@ -8843,7 +8843,7 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B202" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C202">
         <x:v>201</x:v>
@@ -8863,7 +8863,7 @@
         <x:v>484</x:v>
       </x:c>
       <x:c r="B203" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C203">
         <x:v>202</x:v>
@@ -8889,7 +8889,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B204" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C204">
         <x:v>203</x:v>
@@ -8909,7 +8909,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B205" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C205">
         <x:v>204</x:v>
@@ -8938,7 +8938,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B206" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C206">
         <x:v>205</x:v>
@@ -8967,7 +8967,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B207" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C207">
         <x:v>206</x:v>
@@ -8996,7 +8996,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B208" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C208">
         <x:v>207</x:v>
@@ -9016,7 +9016,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B209" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C209">
         <x:v>208</x:v>
@@ -9042,7 +9042,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B210" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C210">
         <x:v>209</x:v>
@@ -9065,7 +9065,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B211" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C211">
         <x:v>210</x:v>
@@ -9085,7 +9085,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B212" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C212">
         <x:v>211</x:v>
@@ -9108,7 +9108,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B213" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C213">
         <x:v>212</x:v>
@@ -9134,7 +9134,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B214" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C214">
         <x:v>213</x:v>
@@ -9160,7 +9160,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B215" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C215">
         <x:v>214</x:v>
@@ -9206,7 +9206,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B217" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C217">
         <x:v>216</x:v>
@@ -9226,7 +9226,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B218" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C218">
         <x:v>217</x:v>
@@ -9255,7 +9255,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B219" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C219">
         <x:v>218</x:v>
@@ -9278,7 +9278,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B220" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C220">
         <x:v>219</x:v>
@@ -9301,7 +9301,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B221" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C221">
         <x:v>220</x:v>
@@ -9327,7 +9327,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B222" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C222">
         <x:v>221</x:v>
@@ -9347,7 +9347,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B223" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C223">
         <x:v>222</x:v>
@@ -9480,7 +9480,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B228" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C228">
         <x:v>227</x:v>
@@ -9582,7 +9582,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B231" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C231">
         <x:v>230</x:v>
@@ -9608,7 +9608,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B232" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C232">
         <x:v>231</x:v>
@@ -9634,7 +9634,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B233" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C233">
         <x:v>232</x:v>
@@ -9646,7 +9646,7 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="G233" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="I233" t="s">
         <x:v>37</x:v>
@@ -9663,7 +9663,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B234" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C234">
         <x:v>233</x:v>
@@ -9689,7 +9689,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B235" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C235">
         <x:v>234</x:v>
@@ -9703,8 +9703,8 @@
       <x:c r="H235" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="J235" t="s">
-        <x:v>38</x:v>
+      <x:c r="J235" t="str">
+        <x:v>M-</x:v>
       </x:c>
       <x:c r="L235" t="s">
         <x:v>37</x:v>
@@ -9715,7 +9715,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B236" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C236">
         <x:v>235</x:v>
@@ -9744,7 +9744,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B237" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C237">
         <x:v>236</x:v>
@@ -9776,7 +9776,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B238" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C238">
         <x:v>237</x:v>
@@ -9805,7 +9805,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B239" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C239">
         <x:v>238</x:v>
@@ -9828,7 +9828,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B240" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C240">
         <x:v>239</x:v>
@@ -9849,7 +9849,7 @@
         <x:v>金属-54</x:v>
       </x:c>
       <x:c r="U240" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="21" customHeight="1">
@@ -9857,7 +9857,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B241" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C241">
         <x:v>240</x:v>
@@ -9878,7 +9878,7 @@
         <x:v>金属-53</x:v>
       </x:c>
       <x:c r="U241" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="21" customHeight="1">
@@ -9886,7 +9886,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B242" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C242">
         <x:v>241</x:v>
@@ -9901,7 +9901,7 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="H242" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="21" customHeight="1">
@@ -9924,7 +9924,7 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="H243" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J243" t="s">
         <x:v>37</x:v>
@@ -9938,7 +9938,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B244" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C244">
         <x:v>243</x:v>
@@ -9958,7 +9958,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B245" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C245">
         <x:v>244</x:v>
@@ -9981,7 +9981,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B246" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C246">
         <x:v>245</x:v>
@@ -10001,7 +10001,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B247" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C247">
         <x:v>246</x:v>
@@ -10019,7 +10019,7 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="H247" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I247" t="s">
         <x:v>37</x:v>
@@ -10028,7 +10028,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K247" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="L247" t="s">
         <x:v>26</x:v>
@@ -10051,7 +10051,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B248" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C248">
         <x:v>247</x:v>
@@ -10074,7 +10074,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B249" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C249">
         <x:v>248</x:v>
@@ -10092,7 +10092,7 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="H249" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I249" t="s">
         <x:v>37</x:v>
@@ -10101,7 +10101,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K249" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="L249" t="s">
         <x:v>26</x:v>
@@ -10124,7 +10124,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B250" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C250">
         <x:v>249</x:v>
@@ -10144,7 +10144,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B251" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C251">
         <x:v>250</x:v>
@@ -10170,7 +10170,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B252" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C252">
         <x:v>251</x:v>
@@ -10196,7 +10196,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B253" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C253">
         <x:v>252</x:v>
@@ -10228,7 +10228,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B254" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C254">
         <x:v>253</x:v>
@@ -10240,7 +10240,7 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="K254" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="21" customHeight="1">
@@ -10248,7 +10248,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B255" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C255">
         <x:v>254</x:v>
@@ -10268,7 +10268,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B256" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C256">
         <x:v>255</x:v>
@@ -10308,7 +10308,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B258" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C258">
         <x:v>257</x:v>
@@ -10331,7 +10331,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B259" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C259">
         <x:v>258</x:v>
@@ -10354,7 +10354,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B260" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C260">
         <x:v>259</x:v>
@@ -10377,7 +10377,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B261" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C261">
         <x:v>260</x:v>
@@ -10403,7 +10403,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B262" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C262">
         <x:v>261</x:v>
@@ -10426,7 +10426,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B263" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C263">
         <x:v>262</x:v>
@@ -10438,13 +10438,13 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="H263" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J263" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="K263" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="O263" t="str"/>
       <x:c r="S263" t="s">
@@ -10456,7 +10456,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B264" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C264">
         <x:v>263</x:v>
@@ -10476,7 +10476,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B265" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C265">
         <x:v>264</x:v>
@@ -10491,7 +10491,7 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="H265" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J265" t="s">
         <x:v>37</x:v>
@@ -10511,7 +10511,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B266" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C266">
         <x:v>265</x:v>
@@ -10534,7 +10534,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B267" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C267">
         <x:v>266</x:v>
@@ -10549,7 +10549,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="H267" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J267" t="s">
         <x:v>37</x:v>
@@ -10569,7 +10569,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B268" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C268">
         <x:v>267</x:v>
@@ -10584,7 +10584,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="H268" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J268" t="s">
         <x:v>37</x:v>
@@ -10599,7 +10599,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B269" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C269">
         <x:v>268</x:v>
@@ -10611,7 +10611,7 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="H269" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J269" t="s">
         <x:v>37</x:v>
@@ -10629,7 +10629,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B270" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C270">
         <x:v>269</x:v>
@@ -10678,7 +10678,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B272" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C272">
         <x:v>271</x:v>
@@ -10701,7 +10701,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B273" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C273">
         <x:v>272</x:v>
@@ -10733,7 +10733,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="H274" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I274" t="s">
         <x:v>37</x:v>
@@ -10742,7 +10742,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K274" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="L274" t="s">
         <x:v>26</x:v>
@@ -10762,7 +10762,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B275" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C275">
         <x:v>274</x:v>
@@ -10788,7 +10788,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B276" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C276">
         <x:v>275</x:v>
@@ -10826,7 +10826,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="K277" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="21" customHeight="1">
@@ -10834,7 +10834,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B278" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C278">
         <x:v>277</x:v>
@@ -10866,7 +10866,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B279" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C279">
         <x:v>278</x:v>
@@ -10889,7 +10889,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B280" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C280">
         <x:v>279</x:v>
@@ -10912,7 +10912,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B281" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C281">
         <x:v>280</x:v>
@@ -10938,7 +10938,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B282" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C282">
         <x:v>281</x:v>
@@ -10967,7 +10967,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B283" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C283">
         <x:v>282</x:v>
@@ -10993,7 +10993,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B284" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C284">
         <x:v>283</x:v>
@@ -11034,7 +11034,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M285" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="21" customHeight="1">
@@ -11042,7 +11042,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B286" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C286">
         <x:v>285</x:v>
@@ -11065,7 +11065,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B287" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C287">
         <x:v>286</x:v>
@@ -11085,7 +11085,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B288" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C288">
         <x:v>287</x:v>
@@ -11108,7 +11108,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B289" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C289">
         <x:v>288</x:v>
@@ -11123,10 +11123,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="H289" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K289" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="21" customHeight="1">
@@ -11134,7 +11134,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B290" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C290">
         <x:v>289</x:v>
@@ -11160,7 +11160,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B291" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C291">
         <x:v>290</x:v>
@@ -11183,7 +11183,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B292" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C292">
         <x:v>291</x:v>
@@ -11203,7 +11203,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B293" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C293">
         <x:v>292</x:v>
@@ -11247,7 +11247,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="K294" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="U294" t="s">
         <x:v>668</x:v>
@@ -11258,7 +11258,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B295" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C295">
         <x:v>294</x:v>
@@ -11388,7 +11388,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
         <x:v>829</x:v>
@@ -11539,10 +11539,10 @@
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>5</x:v>
@@ -11561,7 +11561,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
         <x:v>839</x:v>
@@ -11572,7 +11572,7 @@
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
         <x:v>839</x:v>
@@ -11594,7 +11594,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I10" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
         <x:v>840</x:v>
@@ -11605,10 +11605,10 @@
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
         <x:v>5</x:v>
@@ -11629,7 +11629,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I11" s="4" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
         <x:v>841</x:v>
@@ -11640,7 +11640,7 @@
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
         <x:v>842</x:v>
@@ -11675,7 +11675,7 @@
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
         <x:v>329</x:v>
@@ -11708,10 +11708,10 @@
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="4" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="s">
-        <x:v>294</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
         <x:v>5</x:v>
@@ -11743,7 +11743,7 @@
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
         <x:v>848</x:v>
@@ -11755,7 +11755,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
         <x:v>382</x:v>
@@ -11772,17 +11772,17 @@
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C16" s="5"/>
       <x:c r="D16" s="7">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F16" s="4" t="s">
         <x:v>849</x:v>
@@ -11799,10 +11799,10 @@
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
         <x:v>5</x:v>
@@ -11811,10 +11811,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E17" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F17" s="4" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G17" s="5"/>
       <x:c r="H17" s="7">
@@ -11826,17 +11826,17 @@
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C18" s="5"/>
       <x:c r="D18" s="7">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F18" s="4" t="s">
         <x:v>850</x:v>
@@ -11853,10 +11853,10 @@
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
       <x:c r="A19" s="4" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>216</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
         <x:v>5</x:v>
@@ -11882,10 +11882,10 @@
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
       <x:c r="A20" s="4" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="B20" s="4" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="C20" s="5"/>
       <x:c r="D20" s="7">
@@ -11903,7 +11903,7 @@
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
         <x:v>731</x:v>
@@ -12109,7 +12109,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="K3">
         <x:v>1</x:v>
@@ -12153,7 +12153,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="J4" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="K4">
         <x:v>1</x:v>
@@ -12176,7 +12176,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5">
         <x:v>1</x:v>
@@ -12979,7 +12979,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C24">
         <x:v>1</x:v>
@@ -13002,7 +13002,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C25">
         <x:v>1</x:v>
@@ -13025,7 +13025,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C26">
         <x:v>1</x:v>
@@ -13069,7 +13069,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C27">
         <x:v>1</x:v>
@@ -13113,7 +13113,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C28">
         <x:v>1</x:v>
@@ -13154,7 +13154,7 @@
     </x:row>
     <x:row r="29" ht="19.25" customHeight="1">
       <x:c r="A29" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B29" t="s">
         <x:v>712</x:v>
@@ -13198,10 +13198,10 @@
     </x:row>
     <x:row r="30" ht="19.25" customHeight="1">
       <x:c r="A30" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C30">
         <x:v>1</x:v>
@@ -13242,7 +13242,7 @@
     </x:row>
     <x:row r="31" ht="19.25" customHeight="1">
       <x:c r="A31" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B31" t="s">
         <x:v>713</x:v>
@@ -13286,10 +13286,10 @@
     </x:row>
     <x:row r="32" ht="19.25" customHeight="1">
       <x:c r="A32" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C32">
         <x:v>1</x:v>
@@ -13330,10 +13330,10 @@
     </x:row>
     <x:row r="33" ht="19.25" customHeight="1">
       <x:c r="A33" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C33">
         <x:v>1</x:v>
@@ -13374,7 +13374,7 @@
     </x:row>
     <x:row r="34" ht="19.25" customHeight="1">
       <x:c r="A34" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B34" t="s">
         <x:v>716</x:v>
@@ -13418,7 +13418,7 @@
     </x:row>
     <x:row r="35" ht="19.25" customHeight="1">
       <x:c r="A35" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B35" t="s">
         <x:v>718</x:v>
@@ -13614,7 +13614,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M2" t="s">
         <x:v>722</x:v>
@@ -13665,7 +13665,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF2" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG2" t="s">
         <x:v>685</x:v>
@@ -13718,10 +13718,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M3" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="O3">
         <x:v>1</x:v>
@@ -13769,7 +13769,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF3" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG3" t="s">
         <x:v>310</x:v>
@@ -13819,10 +13819,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M4" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="O4">
         <x:v>1</x:v>
@@ -13867,7 +13867,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF4" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG4" t="s">
         <x:v>322</x:v>
@@ -13917,10 +13917,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L5" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M5" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="O5">
         <x:v>1</x:v>
@@ -13965,7 +13965,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF5" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG5" t="s">
         <x:v>328</x:v>
@@ -14003,7 +14003,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L6" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M6" t="s">
         <x:v>712</x:v>
@@ -14039,7 +14039,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF6" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG6" t="s">
         <x:v>727</x:v>
@@ -14092,7 +14092,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L7" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M7" t="s">
         <x:v>728</x:v>
@@ -14193,7 +14193,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L8" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M8" t="s">
         <x:v>731</x:v>
@@ -14291,7 +14291,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L9" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M9" t="s">
         <x:v>733</x:v>
@@ -14540,10 +14540,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E12">
         <x:v>1</x:v>
@@ -14629,10 +14629,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E13">
         <x:v>1</x:v>
@@ -14727,10 +14727,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E14">
         <x:v>1</x:v>
@@ -14816,10 +14816,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E15">
         <x:v>1</x:v>
@@ -14902,10 +14902,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E16">
         <x:v>1</x:v>
@@ -15000,7 +15000,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C17" t="s">
         <x:v>743</x:v>
@@ -15098,10 +15098,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E18">
         <x:v>1</x:v>
@@ -15181,10 +15181,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E19">
         <x:v>1</x:v>
@@ -15270,10 +15270,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E20">
         <x:v>1</x:v>
@@ -15359,7 +15359,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C21" t="s">
         <x:v>745</x:v>
@@ -15451,7 +15451,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C22" t="s">
         <x:v>746</x:v>
@@ -15502,10 +15502,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="V22" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W22" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="Y22">
         <x:v>1</x:v>
@@ -15517,10 +15517,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AF22" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG22" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="AI22">
         <x:v>1</x:v>
@@ -15534,10 +15534,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E23">
         <x:v>1</x:v>
@@ -15585,10 +15585,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="V23" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W23" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="Y23">
         <x:v>1</x:v>
@@ -15609,7 +15609,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AF23" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG23" t="s">
         <x:v>722</x:v>
@@ -15638,7 +15638,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C24" t="s">
         <x:v>747</x:v>
@@ -15686,10 +15686,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V24" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W24" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="Y24">
         <x:v>1</x:v>
@@ -15698,10 +15698,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AF24" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG24" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="AI24">
         <x:v>1</x:v>
@@ -15724,7 +15724,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C25" t="s">
         <x:v>685</x:v>
@@ -15772,10 +15772,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="V25" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W25" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="Y25">
         <x:v>1</x:v>
@@ -15784,10 +15784,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="AF25" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG25" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="AI25">
         <x:v>1</x:v>
@@ -15810,7 +15810,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C26" t="s">
         <x:v>310</x:v>
@@ -15858,10 +15858,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="V26" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W26" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="Y26">
         <x:v>1</x:v>
@@ -15882,10 +15882,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AF26" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG26" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="AI26">
         <x:v>1</x:v>
@@ -15908,7 +15908,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C27" t="s">
         <x:v>322</x:v>
@@ -15956,7 +15956,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="V27" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W27" t="s">
         <x:v>743</x:v>
@@ -15980,7 +15980,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AF27" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG27" t="s">
         <x:v>712</x:v>
@@ -16006,7 +16006,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C28" t="s">
         <x:v>328</x:v>
@@ -16054,10 +16054,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="V28" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W28" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Y28">
         <x:v>1</x:v>
@@ -16078,7 +16078,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="AF28" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG28" t="s">
         <x:v>728</x:v>
@@ -16104,7 +16104,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C29" t="s">
         <x:v>727</x:v>
@@ -16155,10 +16155,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V29" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W29" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="Y29">
         <x:v>1</x:v>
@@ -16179,7 +16179,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="AF29" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG29" t="s">
         <x:v>731</x:v>
@@ -16256,10 +16256,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="V30" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W30" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="Y30">
         <x:v>1</x:v>
@@ -16280,7 +16280,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AF30" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG30" t="s">
         <x:v>733</x:v>
@@ -16339,7 +16339,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="V31" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W31" t="s">
         <x:v>745</x:v>
@@ -16440,7 +16440,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="V32" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W32" t="s">
         <x:v>746</x:v>
@@ -16541,10 +16541,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="V33" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W33" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="Y33">
         <x:v>1</x:v>
@@ -16591,10 +16591,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E34">
         <x:v>1</x:v>
@@ -16630,7 +16630,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="V34" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W34" t="s">
         <x:v>747</x:v>
@@ -16883,7 +16883,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M2" t="s">
         <x:v>722</x:v>
@@ -16939,10 +16939,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M3" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="O3">
         <x:v>1</x:v>
@@ -16989,10 +16989,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M4" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="O4">
         <x:v>1</x:v>
@@ -17039,10 +17039,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L5" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M5" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="O5">
         <x:v>1</x:v>
@@ -17077,7 +17077,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L6" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M6" t="s">
         <x:v>712</x:v>
@@ -17127,7 +17127,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L7" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M7" t="s">
         <x:v>728</x:v>
@@ -17180,7 +17180,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L8" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M8" t="s">
         <x:v>731</x:v>
@@ -17236,7 +17236,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L9" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M9" t="s">
         <x:v>733</x:v>
@@ -17350,10 +17350,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E12">
         <x:v>1</x:v>
@@ -17391,10 +17391,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E13">
         <x:v>1</x:v>
@@ -17441,10 +17441,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E14">
         <x:v>1</x:v>
@@ -17479,10 +17479,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E15">
         <x:v>1</x:v>
@@ -17517,10 +17517,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E16">
         <x:v>1</x:v>
@@ -17567,7 +17567,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C17" t="s">
         <x:v>743</x:v>
@@ -17617,10 +17617,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E18">
         <x:v>1</x:v>
@@ -17658,10 +17658,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E19">
         <x:v>1</x:v>
@@ -17699,10 +17699,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E20">
         <x:v>1</x:v>
@@ -17749,7 +17749,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C21" t="s">
         <x:v>745</x:v>
@@ -17802,7 +17802,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C22" t="s">
         <x:v>746</x:v>
@@ -17858,10 +17858,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E23">
         <x:v>1</x:v>
@@ -17908,7 +17908,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C24" t="s">
         <x:v>747</x:v>
@@ -17958,7 +17958,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C25" t="s">
         <x:v>685</x:v>
@@ -18008,7 +18008,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C26" t="s">
         <x:v>310</x:v>
@@ -18058,7 +18058,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C27" t="s">
         <x:v>322</x:v>
@@ -18108,7 +18108,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C28" t="s">
         <x:v>328</x:v>
@@ -18158,7 +18158,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C29" t="s">
         <x:v>727</x:v>
@@ -18399,10 +18399,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E34">
         <x:v>1</x:v>
@@ -18631,7 +18631,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M2" t="s">
         <x:v>722</x:v>
@@ -18682,7 +18682,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF2" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG2" t="s">
         <x:v>685</x:v>
@@ -18735,10 +18735,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M3" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="O3">
         <x:v>1</x:v>
@@ -18786,7 +18786,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF3" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG3" t="s">
         <x:v>310</x:v>
@@ -18836,10 +18836,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="L4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M4" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="O4">
         <x:v>1</x:v>
@@ -18884,7 +18884,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF4" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG4" t="s">
         <x:v>322</x:v>
@@ -18934,10 +18934,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L5" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M5" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="O5">
         <x:v>1</x:v>
@@ -18982,7 +18982,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AF5" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG5" t="s">
         <x:v>328</x:v>
@@ -19020,7 +19020,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="L6" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M6" t="s">
         <x:v>712</x:v>
@@ -19056,7 +19056,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF6" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="AG6" t="s">
         <x:v>727</x:v>
@@ -19109,7 +19109,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="L7" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M7" t="s">
         <x:v>728</x:v>
@@ -19210,7 +19210,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L8" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M8" t="s">
         <x:v>731</x:v>
@@ -19308,7 +19308,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="L9" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="M9" t="s">
         <x:v>733</x:v>
@@ -19557,10 +19557,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E12">
         <x:v>1</x:v>
@@ -19646,10 +19646,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E13">
         <x:v>1</x:v>
@@ -19744,10 +19744,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E14">
         <x:v>1</x:v>
@@ -19833,10 +19833,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E15">
         <x:v>1</x:v>
@@ -19919,10 +19919,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E16">
         <x:v>1</x:v>
@@ -20017,7 +20017,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C17" t="s">
         <x:v>743</x:v>
@@ -20115,10 +20115,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E18">
         <x:v>1</x:v>
@@ -20198,10 +20198,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E19">
         <x:v>1</x:v>
@@ -20287,10 +20287,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E20">
         <x:v>1</x:v>
@@ -20376,7 +20376,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C21" t="s">
         <x:v>745</x:v>
@@ -20468,7 +20468,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C22" t="s">
         <x:v>746</x:v>
@@ -20519,10 +20519,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="V22" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W22" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="Y22">
         <x:v>1</x:v>
@@ -20534,10 +20534,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AF22" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG22" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="AI22">
         <x:v>1</x:v>
@@ -20551,10 +20551,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E23">
         <x:v>1</x:v>
@@ -20602,10 +20602,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="V23" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W23" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="Y23">
         <x:v>1</x:v>
@@ -20626,7 +20626,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="AF23" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG23" t="s">
         <x:v>722</x:v>
@@ -20655,7 +20655,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C24" t="s">
         <x:v>747</x:v>
@@ -20703,10 +20703,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="V24" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W24" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="Y24">
         <x:v>1</x:v>
@@ -20715,10 +20715,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="AF24" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG24" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="AI24">
         <x:v>1</x:v>
@@ -20741,7 +20741,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C25" t="s">
         <x:v>685</x:v>
@@ -20789,10 +20789,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="V25" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W25" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="Y25">
         <x:v>1</x:v>
@@ -20801,10 +20801,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="AF25" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG25" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="AI25">
         <x:v>1</x:v>
@@ -20827,7 +20827,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C26" t="s">
         <x:v>310</x:v>
@@ -20875,10 +20875,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="V26" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W26" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="Y26">
         <x:v>1</x:v>
@@ -20899,10 +20899,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AF26" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG26" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="AI26">
         <x:v>1</x:v>
@@ -20925,7 +20925,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C27" t="s">
         <x:v>322</x:v>
@@ -20973,7 +20973,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="V27" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W27" t="s">
         <x:v>743</x:v>
@@ -20997,7 +20997,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="AF27" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG27" t="s">
         <x:v>712</x:v>
@@ -21023,7 +21023,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C28" t="s">
         <x:v>328</x:v>
@@ -21071,10 +21071,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="V28" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W28" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Y28">
         <x:v>1</x:v>
@@ -21095,7 +21095,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="AF28" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG28" t="s">
         <x:v>728</x:v>
@@ -21121,7 +21121,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C29" t="s">
         <x:v>727</x:v>
@@ -21172,10 +21172,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="V29" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W29" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="Y29">
         <x:v>1</x:v>
@@ -21196,7 +21196,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="AF29" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG29" t="s">
         <x:v>731</x:v>
@@ -21273,10 +21273,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="V30" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="W30" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="Y30">
         <x:v>1</x:v>
@@ -21297,7 +21297,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="AF30" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="AG30" t="s">
         <x:v>733</x:v>
@@ -21356,7 +21356,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="V31" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W31" t="s">
         <x:v>745</x:v>
@@ -21457,7 +21457,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="V32" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W32" t="s">
         <x:v>746</x:v>
@@ -21558,10 +21558,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="V33" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W33" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="Y33">
         <x:v>1</x:v>
@@ -21608,10 +21608,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E34">
         <x:v>1</x:v>
@@ -21647,7 +21647,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="V34" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="W34" t="s">
         <x:v>747</x:v>
@@ -21934,7 +21934,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="I5" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="J5" t="s">
         <x:v>725</x:v>
@@ -21954,13 +21954,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H6">
         <x:v>39</x:v>
       </x:c>
       <x:c r="I6" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="J6" t="s">
         <x:v>725</x:v>
@@ -21983,7 +21983,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="I7" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="J7" t="s">
         <x:v>754</x:v>
@@ -22009,7 +22009,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="I8" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
@@ -22037,13 +22037,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F10" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H10">
         <x:v>43</x:v>
       </x:c>
       <x:c r="I10" t="s">
-        <x:v>236</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
@@ -22057,13 +22057,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F11" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H11">
         <x:v>44</x:v>
       </x:c>
       <x:c r="I11" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
@@ -22077,13 +22077,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F12" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="I12" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
@@ -22106,7 +22106,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="I13" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
@@ -22120,13 +22120,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F14" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H14">
         <x:v>47</x:v>
       </x:c>
       <x:c r="I14" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
@@ -22169,7 +22169,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="I16" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="21" customHeight="1">
@@ -22215,7 +22215,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I18" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
@@ -22238,7 +22238,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="I19" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="J19" t="s">
         <x:v>725</x:v>
@@ -22307,7 +22307,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F22" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H22">
         <x:v>55</x:v>
@@ -22350,7 +22350,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F24" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="H24">
         <x:v>57</x:v>
@@ -22367,7 +22367,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C25" t="s">
         <x:v>725</x:v>
@@ -22536,7 +22536,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E33">
         <x:v>32</x:v>
@@ -22709,7 +22709,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D6" t="s">
         <x:v>725</x:v>
@@ -22801,10 +22801,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G10" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="I10" t="s">
         <x:v>725</x:v>
@@ -22827,10 +22827,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G11" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="H11" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="26.5" customHeight="1">
@@ -22942,7 +22942,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D16" t="s">
         <x:v>725</x:v>
@@ -22965,7 +22965,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="26.5" customHeight="1">
@@ -22976,7 +22976,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D18" t="s">
         <x:v>725</x:v>
@@ -22990,7 +22990,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="26.5" customHeight="1">
@@ -23015,7 +23015,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="26.5" customHeight="1">
@@ -23173,7 +23173,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18.75" customHeight="1">
@@ -23236,10 +23236,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D12" t="s">
         <x:v>723</x:v>
@@ -23250,10 +23250,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18.75" customHeight="1">
@@ -23261,10 +23261,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18.75" customHeight="1">
@@ -23272,10 +23272,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18.75" customHeight="1">
@@ -23283,7 +23283,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C16" t="s">
         <x:v>300</x:v>
@@ -23297,7 +23297,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C17" t="s">
         <x:v>685</x:v>
@@ -23308,7 +23308,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C18" t="s">
         <x:v>322</x:v>
@@ -23322,7 +23322,7 @@
         <x:v>ハミング</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18.75" customHeight="1">
@@ -23344,7 +23344,7 @@
         <x:v>ハミング</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18.75" customHeight="1">
@@ -23541,7 +23541,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C2">
         <x:v>245</x:v>
@@ -23556,7 +23556,7 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="H2" t="s">
-        <x:v>38</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="I2" t="s">
         <x:v>37</x:v>
@@ -23565,7 +23565,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>38</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="L2" t="s">
         <x:v>37</x:v>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="Raf15cb858f8c47d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Re3a41c346eb74efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R8cf8e9aff4f440ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R18751522507d4df8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Re2ca50566047406c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R2b125c5fb2d34da1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Reb968eff5ee74db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="Ra81c548538bf4a41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R4ef68c06ecd84028"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R676808eb10784a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R98982c6b66e74bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rf9cbba4c572746be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R4f7273046b7e4ef5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R5ad7395704a348f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R6d9d6e02d9c04179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R28663c0829ac413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rec4822fcc9b34495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R5334129fd96d4910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R703f3af5bcb44af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rc87883188d764462"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3420,7 +3420,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M7" t="str">
-        <x:v>内回り-2</x:v>
+        <x:v>内-2</x:v>
       </x:c>
       <x:c r="O7" t="str">
         <x:v>金属-1</x:v>
@@ -3470,7 +3470,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>内回り-1</x:v>
+        <x:v>内-1</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>金属-2</x:v>
@@ -4053,7 +4053,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>内回り-3</x:v>
+        <x:v>内-3</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>金属-5</x:v>
@@ -4286,7 +4286,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>内回り-6</x:v>
+        <x:v>内-6</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="21" customHeight="1">
@@ -4391,7 +4391,7 @@
         <x:v>M-</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>外回り-15</x:v>
+        <x:v>外-15</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="21" customHeight="1">
@@ -4509,7 +4509,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M46" t="str">
-        <x:v>内回り-7</x:v>
+        <x:v>内-7</x:v>
       </x:c>
       <x:c r="O46" t="str">
         <x:v>金属-20</x:v>
@@ -5015,7 +5015,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M65" t="str">
-        <x:v>内回り-8</x:v>
+        <x:v>内-8</x:v>
       </x:c>
       <x:c r="Q65" t="str">
         <x:v>ガラ-</x:v>
@@ -5299,7 +5299,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="M76" t="str">
-        <x:v>内回り-17</x:v>
+        <x:v>内-17</x:v>
       </x:c>
       <x:c r="S76" t="s">
         <x:v>202</x:v>
@@ -5372,7 +5372,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M78" t="str">
-        <x:v>内回り-18</x:v>
+        <x:v>内-18</x:v>
       </x:c>
       <x:c r="O78" t="str"/>
     </x:row>
@@ -5486,7 +5486,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M82" t="str">
-        <x:v>内回り-16</x:v>
+        <x:v>内-16</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="21" customHeight="1">
@@ -5521,7 +5521,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M83" t="str">
-        <x:v>内回り-14</x:v>
+        <x:v>内-14</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="21" customHeight="1">
@@ -5559,7 +5559,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M84" t="str">
-        <x:v>内回り-15</x:v>
+        <x:v>内-15</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="21" customHeight="1">
@@ -5659,7 +5659,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M87" t="str">
-        <x:v>内回り-13</x:v>
+        <x:v>内-13</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="21" customHeight="1">
@@ -6074,7 +6074,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M101" t="str">
-        <x:v>内回り-12</x:v>
+        <x:v>内-12</x:v>
       </x:c>
       <x:c r="O101" t="str">
         <x:v>金属-27</x:v>
@@ -6277,7 +6277,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M108" t="str">
-        <x:v>外回り-14</x:v>
+        <x:v>外-14</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="21" customHeight="1">
@@ -6318,7 +6318,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M109" t="str">
-        <x:v>外回り-13</x:v>
+        <x:v>外-13</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="21" customHeight="1">
@@ -6440,7 +6440,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="M113" t="str">
-        <x:v>内回り-11</x:v>
+        <x:v>内-11</x:v>
       </x:c>
       <x:c r="O113" t="str">
         <x:v>金属-33</x:v>
@@ -6963,7 +6963,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="M131" t="str">
-        <x:v>内回り-10</x:v>
+        <x:v>内-10</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="21" customHeight="1">
@@ -7064,7 +7064,7 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="M135" t="str">
-        <x:v>内回り-9</x:v>
+        <x:v>内-9</x:v>
       </x:c>
       <x:c r="O135" t="str">
         <x:v>金属-39</x:v>
@@ -7577,7 +7577,7 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="M154" t="str">
-        <x:v>外回り-12</x:v>
+        <x:v>外-12</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="21" customHeight="1">
@@ -7774,7 +7774,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="M161" t="str">
-        <x:v>外回り-11</x:v>
+        <x:v>外-11</x:v>
       </x:c>
       <x:c r="O161" t="str">
         <x:v>金属-46</x:v>
@@ -7973,7 +7973,7 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="M169" t="str">
-        <x:v>外回り-10</x:v>
+        <x:v>外-10</x:v>
       </x:c>
       <x:c r="U169" t="s">
         <x:v>413</x:v>
@@ -8188,7 +8188,7 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="M177" t="str">
-        <x:v>外回り-9</x:v>
+        <x:v>外-9</x:v>
       </x:c>
       <x:c r="O177" t="str">
         <x:v>金属-48</x:v>
@@ -8413,7 +8413,7 @@
         <x:v>M-</x:v>
       </x:c>
       <x:c r="M186" t="str">
-        <x:v>外回り-8</x:v>
+        <x:v>外-8</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="21" customHeight="1">
@@ -8439,7 +8439,7 @@
         <x:v>M-</x:v>
       </x:c>
       <x:c r="M187" t="str">
-        <x:v>外回り-7</x:v>
+        <x:v>外-7</x:v>
       </x:c>
       <x:c r="U187" t="s">
         <x:v>413</x:v>
@@ -8468,7 +8468,7 @@
         <x:v>M-</x:v>
       </x:c>
       <x:c r="M188" t="str">
-        <x:v>外回り-6</x:v>
+        <x:v>外-6</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="21" customHeight="1">
@@ -8716,7 +8716,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M197" t="str">
-        <x:v>内回り-4</x:v>
+        <x:v>内-4</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="21" customHeight="1">
@@ -8754,7 +8754,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M198" t="str">
-        <x:v>内回り-5</x:v>
+        <x:v>内-5</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="21" customHeight="1">
@@ -9567,7 +9567,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M230" t="str">
-        <x:v>内回り-19</x:v>
+        <x:v>内-19</x:v>
       </x:c>
       <x:c r="O230" t="str">
         <x:v>金属-59</x:v>
@@ -10033,7 +10033,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M247" t="str">
-        <x:v>外回り-5</x:v>
+        <x:v>外-5</x:v>
       </x:c>
       <x:c r="O247" t="str">
         <x:v>金属-14</x:v>
@@ -10106,7 +10106,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M249" t="str">
-        <x:v>外回り-4</x:v>
+        <x:v>外-4</x:v>
       </x:c>
       <x:c r="O249" t="str">
         <x:v>金属-15</x:v>
@@ -10747,7 +10747,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M274" t="str">
-        <x:v>外回り-2</x:v>
+        <x:v>外-2</x:v>
       </x:c>
       <x:c r="O274" t="str">
         <x:v>金属-7</x:v>
@@ -11033,7 +11033,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M285" t="str">
-        <x:v>外回り-3</x:v>
+        <x:v>外-3</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="21" customHeight="1">
@@ -11174,7 +11174,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="M291" t="str">
-        <x:v>外回り-1</x:v>
+        <x:v>外-1</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="21" customHeight="1">

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R98982c6b66e74bb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rf9cbba4c572746be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R4f7273046b7e4ef5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R5ad7395704a348f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R6d9d6e02d9c04179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R28663c0829ac413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rec4822fcc9b34495"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R5334129fd96d4910"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R703f3af5bcb44af0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rc87883188d764462"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R494c18ac973d424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R5a6fce78678a488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R2930d3233d764956"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R052295ae13664dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R56be17aea77241c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R36bac3821ff84f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R5c3acd7812f547d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R84ed7a50300a4b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="Rcb2c28d6fb5440f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rcef9583c9eec46cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10134,8 +10134,8 @@
       <x:c r="E250" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J250" t="s">
-        <x:v>37</x:v>
+      <x:c r="J250" t="str">
+        <x:v>M-</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="21" customHeight="1">

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R494c18ac973d424f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R5a6fce78678a488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R2930d3233d764956"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R052295ae13664dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R56be17aea77241c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R36bac3821ff84f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R5c3acd7812f547d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R84ed7a50300a4b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="Rcb2c28d6fb5440f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rcef9583c9eec46cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R1d07c582a4f24738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R65479d35ecc646be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R92e3a2b1b95441db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rc0eac0bd21834ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R713a1f6464024d7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R3a054b6a31c640cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Re54989bc5ed8400c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R055e1a7cffa446f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R003e549b51bd4f60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R63343ebc216545ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3510,8 +3510,8 @@
       <x:c r="L9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M9" t="s">
-        <x:v>15</x:v>
+      <x:c r="M9" t="str">
+        <x:v>段紙(土)-10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
@@ -4053,7 +4053,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>内-3</x:v>
+        <x:v>段紙(土)-2</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>金属-5</x:v>
@@ -4509,7 +4509,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M46" t="str">
-        <x:v>内-7</x:v>
+        <x:v>段紙(土)-6</x:v>
       </x:c>
       <x:c r="O46" t="str">
         <x:v>金属-20</x:v>
@@ -6074,7 +6074,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M101" t="str">
-        <x:v>内-12</x:v>
+        <x:v>段紙(土)-7</x:v>
       </x:c>
       <x:c r="O101" t="str">
         <x:v>金属-27</x:v>
@@ -7064,7 +7064,7 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="M135" t="str">
-        <x:v>内-9</x:v>
+        <x:v>段紙(土)-8</x:v>
       </x:c>
       <x:c r="O135" t="str">
         <x:v>金属-39</x:v>
@@ -7774,7 +7774,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="M161" t="str">
-        <x:v>外-11</x:v>
+        <x:v>段紙(土)-9</x:v>
       </x:c>
       <x:c r="O161" t="str">
         <x:v>金属-46</x:v>
@@ -10033,7 +10033,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M247" t="str">
-        <x:v>外-5</x:v>
+        <x:v>段紙(土)-3</x:v>
       </x:c>
       <x:c r="O247" t="str">
         <x:v>金属-14</x:v>
@@ -10106,7 +10106,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M249" t="str">
-        <x:v>外-4</x:v>
+        <x:v>段紙(土)-4</x:v>
       </x:c>
       <x:c r="O249" t="str">
         <x:v>金属-15</x:v>
@@ -10747,7 +10747,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M274" t="str">
-        <x:v>外-2</x:v>
+        <x:v>段紙(土)-5</x:v>
       </x:c>
       <x:c r="O274" t="str">
         <x:v>金属-7</x:v>
@@ -11280,6 +11280,76 @@
       <x:c r="U295" t="s">
         <x:v>670</x:v>
       </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" t="str">
+        <x:v>四十九</x:v>
+      </x:c>
+      <x:c r="B296" t="str">
+        <x:v>会社　商店</x:v>
+      </x:c>
+      <x:c r="C296" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D296" t="n">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="E296" t="str">
+        <x:v>会社の段ボール</x:v>
+      </x:c>
+      <x:c r="F296"/>
+      <x:c r="G296"/>
+      <x:c r="H296"/>
+      <x:c r="I296"/>
+      <x:c r="J296"/>
+      <x:c r="K296"/>
+      <x:c r="L296"/>
+      <x:c r="M296" t="str">
+        <x:v>段紙(土)-1</x:v>
+      </x:c>
+      <x:c r="N296"/>
+      <x:c r="O296"/>
+      <x:c r="P296"/>
+      <x:c r="Q296"/>
+      <x:c r="R296"/>
+      <x:c r="S296"/>
+      <x:c r="T296"/>
+      <x:c r="U296"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" t="str">
+        <x:v>四十九</x:v>
+      </x:c>
+      <x:c r="B297" t="str">
+        <x:v>飲食　食品</x:v>
+      </x:c>
+      <x:c r="C297" t="n">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D297" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="E297" t="str">
+        <x:v>イオン PET・アルミ</x:v>
+      </x:c>
+      <x:c r="F297"/>
+      <x:c r="G297"/>
+      <x:c r="H297"/>
+      <x:c r="I297"/>
+      <x:c r="J297"/>
+      <x:c r="K297"/>
+      <x:c r="L297"/>
+      <x:c r="M297" t="str">
+        <x:v>段紙(土)-11</x:v>
+      </x:c>
+      <x:c r="N297"/>
+      <x:c r="O297"/>
+      <x:c r="P297"/>
+      <x:c r="Q297"/>
+      <x:c r="R297"/>
+      <x:c r="S297"/>
+      <x:c r="T297"/>
+      <x:c r="U297"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R1d07c582a4f24738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R65479d35ecc646be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R92e3a2b1b95441db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rc0eac0bd21834ac4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R713a1f6464024d7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R3a054b6a31c640cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Re54989bc5ed8400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R055e1a7cffa446f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R003e549b51bd4f60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R63343ebc216545ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R09bdfd6011df473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rbbec8b3cd0584f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R5b6e47a685534e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Raa8f7a66d05442c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R1918551919394c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rd251b1a586ce48cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R8357e9ebbcb9481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R3d5a5f4bad5d4681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R9158d87bae48495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rd522b4031dfa4a5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3225,28 +3225,31 @@
       <x:c r="M1" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="N1" s="2" t="str">
+        <x:v>段紙(土)</x:v>
+      </x:c>
+      <x:c r="O1" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="s">
+      <x:c r="R1" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="s">
+      <x:c r="S1" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="s">
+      <x:c r="T1" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="T1" s="2" t="s">
+      <x:c r="U1" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="U1" s="2" t="s">
+      <x:c r="V1" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -3275,6 +3278,15 @@
       <x:c r="L2" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
+      <x:c r="R2"/>
+      <x:c r="S2"/>
+      <x:c r="T2"/>
+      <x:c r="U2"/>
+      <x:c r="V2"/>
     </x:row>
     <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" t="s">
@@ -3295,10 +3307,17 @@
       <x:c r="L3" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N3"/>
       <x:c r="O3" t="str"/>
-      <x:c r="P3" t="s">
+      <x:c r="P3"/>
+      <x:c r="Q3" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R3"/>
+      <x:c r="S3"/>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
     </x:row>
     <x:row r="4" ht="21" customHeight="1">
       <x:c r="A4" t="s">
@@ -3322,9 +3341,17 @@
       <x:c r="L4" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P4" t="s">
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+      <x:c r="P4"/>
+      <x:c r="Q4" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R4"/>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
+      <x:c r="U4"/>
+      <x:c r="V4"/>
     </x:row>
     <x:row r="5" ht="21" customHeight="1">
       <x:c r="A5" t="s">
@@ -3348,6 +3375,15 @@
       <x:c r="K5" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+      <x:c r="P5"/>
+      <x:c r="Q5"/>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
+      <x:c r="V5"/>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" t="s">
@@ -3381,6 +3417,15 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M6"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+      <x:c r="P6"/>
+      <x:c r="Q6"/>
+      <x:c r="R6"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
+      <x:c r="V6"/>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
       <x:c r="A7" t="s">
@@ -3422,15 +3467,21 @@
       <x:c r="M7" t="str">
         <x:v>内-2</x:v>
       </x:c>
-      <x:c r="O7" t="str">
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7" t="str">
         <x:v>金属-1</x:v>
       </x:c>
-      <x:c r="Q7" t="str">
+      <x:c r="Q7"/>
+      <x:c r="R7" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
-      <x:c r="S7" t="s">
+      <x:c r="S7"/>
+      <x:c r="T7" t="s">
         <x:v>42</x:v>
       </x:c>
+      <x:c r="U7"/>
+      <x:c r="V7"/>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
       <x:c r="A8" t="s">
@@ -3472,15 +3523,21 @@
       <x:c r="M8" t="str">
         <x:v>内-1</x:v>
       </x:c>
-      <x:c r="O8" t="str">
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+      <x:c r="P8" t="str">
         <x:v>金属-2</x:v>
       </x:c>
-      <x:c r="Q8" t="str">
+      <x:c r="Q8"/>
+      <x:c r="R8" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
-      <x:c r="S8" t="s">
+      <x:c r="S8"/>
+      <x:c r="T8" t="s">
         <x:v>46</x:v>
       </x:c>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
       <x:c r="A9" t="s">
@@ -3511,8 +3568,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="M9" t="str">
+        <x:v>段紙</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
         <x:v>段紙(土)-10</x:v>
       </x:c>
+      <x:c r="O9"/>
+      <x:c r="P9"/>
+      <x:c r="Q9"/>
+      <x:c r="R9"/>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
       <x:c r="A10" t="s">
@@ -3545,6 +3613,15 @@
       <x:c r="M10" t="s">
         <x:v>15</x:v>
       </x:c>
+      <x:c r="N10"/>
+      <x:c r="O10"/>
+      <x:c r="P10"/>
+      <x:c r="Q10"/>
+      <x:c r="R10"/>
+      <x:c r="S10"/>
+      <x:c r="T10"/>
+      <x:c r="U10"/>
+      <x:c r="V10"/>
     </x:row>
     <x:row r="11" ht="21" customHeight="1">
       <x:c r="A11" t="s">
@@ -3577,6 +3654,15 @@
       <x:c r="M11" t="s">
         <x:v>50</x:v>
       </x:c>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+      <x:c r="P11"/>
+      <x:c r="Q11"/>
+      <x:c r="R11"/>
+      <x:c r="S11"/>
+      <x:c r="T11"/>
+      <x:c r="U11"/>
+      <x:c r="V11"/>
     </x:row>
     <x:row r="12" ht="21" customHeight="1">
       <x:c r="A12" t="s">
@@ -3606,6 +3692,15 @@
       <x:c r="L12" t="s">
         <x:v>52</x:v>
       </x:c>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+      <x:c r="P12"/>
+      <x:c r="Q12"/>
+      <x:c r="R12"/>
+      <x:c r="S12"/>
+      <x:c r="T12"/>
+      <x:c r="U12"/>
+      <x:c r="V12"/>
     </x:row>
     <x:row r="13" ht="21" customHeight="1">
       <x:c r="A13" t="s">
@@ -3641,9 +3736,17 @@
       <x:c r="L13" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P13" t="s">
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+      <x:c r="P13"/>
+      <x:c r="Q13" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R13"/>
+      <x:c r="S13"/>
+      <x:c r="T13"/>
+      <x:c r="U13"/>
+      <x:c r="V13"/>
     </x:row>
     <x:row r="14" ht="21" customHeight="1">
       <x:c r="A14" t="s">
@@ -3664,6 +3767,15 @@
       <x:c r="L14" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
+      <x:c r="Q14"/>
+      <x:c r="R14"/>
+      <x:c r="S14"/>
+      <x:c r="T14"/>
+      <x:c r="U14"/>
+      <x:c r="V14"/>
     </x:row>
     <x:row r="15" ht="21" customHeight="1">
       <x:c r="A15" t="s">
@@ -3684,13 +3796,19 @@
       <x:c r="J15" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="O15" t="str">
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+      <x:c r="P15" t="str">
         <x:v>金属-3</x:v>
       </x:c>
-      <x:c r="S15" t="s">
+      <x:c r="Q15"/>
+      <x:c r="R15"/>
+      <x:c r="S15"/>
+      <x:c r="T15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="U15" t="s">
+      <x:c r="U15"/>
+      <x:c r="V15" t="s">
         <x:v>61</x:v>
       </x:c>
     </x:row>
@@ -3719,6 +3837,15 @@
       <x:c r="L16" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+      <x:c r="P16"/>
+      <x:c r="Q16"/>
+      <x:c r="R16"/>
+      <x:c r="S16"/>
+      <x:c r="T16"/>
+      <x:c r="U16"/>
+      <x:c r="V16"/>
     </x:row>
     <x:row r="17" ht="21" customHeight="1">
       <x:c r="A17" t="s">
@@ -3745,6 +3872,15 @@
       <x:c r="L17" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
+      <x:c r="Q17"/>
+      <x:c r="R17"/>
+      <x:c r="S17"/>
+      <x:c r="T17"/>
+      <x:c r="U17"/>
+      <x:c r="V17"/>
     </x:row>
     <x:row r="18" ht="21" customHeight="1">
       <x:c r="A18" t="s">
@@ -3768,10 +3904,17 @@
       <x:c r="L18" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N18"/>
       <x:c r="O18" t="str"/>
-      <x:c r="S18" t="s">
+      <x:c r="P18"/>
+      <x:c r="Q18"/>
+      <x:c r="R18"/>
+      <x:c r="S18"/>
+      <x:c r="T18" t="s">
         <x:v>68</x:v>
       </x:c>
+      <x:c r="U18"/>
+      <x:c r="V18"/>
     </x:row>
     <x:row r="19" ht="21" customHeight="1">
       <x:c r="A19" t="s">
@@ -3795,6 +3938,15 @@
       <x:c r="L19" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
+      <x:c r="Q19"/>
+      <x:c r="R19"/>
+      <x:c r="S19"/>
+      <x:c r="T19"/>
+      <x:c r="U19"/>
+      <x:c r="V19"/>
     </x:row>
     <x:row r="20" ht="21" customHeight="1">
       <x:c r="A20" t="s">
@@ -3818,6 +3970,15 @@
       <x:c r="L20" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
+      <x:c r="Q20"/>
+      <x:c r="R20"/>
+      <x:c r="S20"/>
+      <x:c r="T20"/>
+      <x:c r="U20"/>
+      <x:c r="V20"/>
     </x:row>
     <x:row r="21" ht="21" customHeight="1">
       <x:c r="A21" t="s">
@@ -3838,6 +3999,15 @@
       <x:c r="K21" t="s">
         <x:v>73</x:v>
       </x:c>
+      <x:c r="N21"/>
+      <x:c r="O21"/>
+      <x:c r="P21"/>
+      <x:c r="Q21"/>
+      <x:c r="R21"/>
+      <x:c r="S21"/>
+      <x:c r="T21"/>
+      <x:c r="U21"/>
+      <x:c r="V21"/>
     </x:row>
     <x:row r="22" ht="21" customHeight="1">
       <x:c r="A22" t="s">
@@ -3858,6 +4028,15 @@
       <x:c r="L22" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
+      <x:c r="Q22"/>
+      <x:c r="R22"/>
+      <x:c r="S22"/>
+      <x:c r="T22"/>
+      <x:c r="U22"/>
+      <x:c r="V22"/>
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
       <x:c r="A23" t="s">
@@ -3884,12 +4063,19 @@
       <x:c r="L23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O23" t="str">
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+      <x:c r="P23" t="str">
         <x:v>金属-6</x:v>
       </x:c>
-      <x:c r="Q23" t="str">
+      <x:c r="Q23"/>
+      <x:c r="R23" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S23"/>
+      <x:c r="T23"/>
+      <x:c r="U23"/>
+      <x:c r="V23"/>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
       <x:c r="A24" t="s">
@@ -3913,9 +4099,17 @@
       <x:c r="L24" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P24" t="s">
+      <x:c r="N24"/>
+      <x:c r="O24"/>
+      <x:c r="P24"/>
+      <x:c r="Q24" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R24"/>
+      <x:c r="S24"/>
+      <x:c r="T24"/>
+      <x:c r="U24"/>
+      <x:c r="V24"/>
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
       <x:c r="A25" t="s">
@@ -3939,6 +4133,15 @@
       <x:c r="L25" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
+      <x:c r="Q25"/>
+      <x:c r="R25"/>
+      <x:c r="S25"/>
+      <x:c r="T25"/>
+      <x:c r="U25"/>
+      <x:c r="V25"/>
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
       <x:c r="A26" t="s">
@@ -3965,9 +4168,17 @@
       <x:c r="L26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P26" t="s">
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
+      <x:c r="Q26" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R26"/>
+      <x:c r="S26"/>
+      <x:c r="T26"/>
+      <x:c r="U26"/>
+      <x:c r="V26"/>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
       <x:c r="A27" t="s">
@@ -3997,6 +4208,15 @@
       <x:c r="L27" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
+      <x:c r="Q27"/>
+      <x:c r="R27"/>
+      <x:c r="S27"/>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
+      <x:c r="V27"/>
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
       <x:c r="A28" t="s">
@@ -4017,6 +4237,15 @@
       <x:c r="L28" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
+      <x:c r="Q28"/>
+      <x:c r="R28"/>
+      <x:c r="S28"/>
+      <x:c r="T28"/>
+      <x:c r="U28"/>
+      <x:c r="V28"/>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
       <x:c r="A29" t="s">
@@ -4053,17 +4282,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M29" t="str">
+        <x:v>内-3</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
         <x:v>段紙(土)-2</x:v>
       </x:c>
-      <x:c r="O29" t="str">
+      <x:c r="O29"/>
+      <x:c r="P29" t="str">
         <x:v>金属-5</x:v>
       </x:c>
-      <x:c r="P29" t="s">
+      <x:c r="Q29" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S29" t="s">
+      <x:c r="R29"/>
+      <x:c r="S29"/>
+      <x:c r="T29" t="s">
         <x:v>93</x:v>
       </x:c>
+      <x:c r="U29"/>
+      <x:c r="V29"/>
     </x:row>
     <x:row r="30" ht="21" customHeight="1">
       <x:c r="A30" t="s">
@@ -4084,6 +4321,15 @@
       <x:c r="L30" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
+      <x:c r="Q30"/>
+      <x:c r="R30"/>
+      <x:c r="S30"/>
+      <x:c r="T30"/>
+      <x:c r="U30"/>
+      <x:c r="V30"/>
     </x:row>
     <x:row r="31" ht="21" customHeight="1">
       <x:c r="A31" t="s">
@@ -4107,6 +4353,15 @@
       <x:c r="I31" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N31"/>
+      <x:c r="O31"/>
+      <x:c r="P31"/>
+      <x:c r="Q31"/>
+      <x:c r="R31"/>
+      <x:c r="S31"/>
+      <x:c r="T31"/>
+      <x:c r="U31"/>
+      <x:c r="V31"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
       <x:c r="A32" t="s">
@@ -4130,10 +4385,17 @@
       <x:c r="J32" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="O32" t="str">
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32" t="str">
         <x:v>金属-4</x:v>
       </x:c>
-      <x:c r="U32" t="s">
+      <x:c r="Q32"/>
+      <x:c r="R32"/>
+      <x:c r="S32"/>
+      <x:c r="T32"/>
+      <x:c r="U32"/>
+      <x:c r="V32" t="s">
         <x:v>99</x:v>
       </x:c>
     </x:row>
@@ -4159,10 +4421,17 @@
       <x:c r="K33" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="S33" t="s">
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+      <x:c r="P33"/>
+      <x:c r="Q33"/>
+      <x:c r="R33"/>
+      <x:c r="S33"/>
+      <x:c r="T33" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="U33" t="s">
+      <x:c r="U33"/>
+      <x:c r="V33" t="s">
         <x:v>104</x:v>
       </x:c>
     </x:row>
@@ -4200,7 +4469,15 @@
       <x:c r="L34" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N34"/>
       <x:c r="O34" t="str"/>
+      <x:c r="P34"/>
+      <x:c r="Q34"/>
+      <x:c r="R34"/>
+      <x:c r="S34"/>
+      <x:c r="T34"/>
+      <x:c r="U34"/>
+      <x:c r="V34"/>
     </x:row>
     <x:row r="35" ht="21" customHeight="1">
       <x:c r="A35" t="s">
@@ -4221,6 +4498,15 @@
       <x:c r="L35" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N35"/>
+      <x:c r="O35"/>
+      <x:c r="P35"/>
+      <x:c r="Q35"/>
+      <x:c r="R35"/>
+      <x:c r="S35"/>
+      <x:c r="T35"/>
+      <x:c r="U35"/>
+      <x:c r="V35"/>
     </x:row>
     <x:row r="36" ht="21" customHeight="1">
       <x:c r="A36" t="s">
@@ -4247,6 +4533,15 @@
       <x:c r="L36" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N36"/>
+      <x:c r="O36"/>
+      <x:c r="P36"/>
+      <x:c r="Q36"/>
+      <x:c r="R36"/>
+      <x:c r="S36"/>
+      <x:c r="T36"/>
+      <x:c r="U36"/>
+      <x:c r="V36"/>
     </x:row>
     <x:row r="37" ht="21" customHeight="1">
       <x:c r="A37" t="s">
@@ -4288,6 +4583,15 @@
       <x:c r="M37" t="str">
         <x:v>内-6</x:v>
       </x:c>
+      <x:c r="N37"/>
+      <x:c r="O37"/>
+      <x:c r="P37"/>
+      <x:c r="Q37"/>
+      <x:c r="R37"/>
+      <x:c r="S37"/>
+      <x:c r="T37"/>
+      <x:c r="U37"/>
+      <x:c r="V37"/>
     </x:row>
     <x:row r="38" ht="21" customHeight="1">
       <x:c r="A38" t="s">
@@ -4311,6 +4615,15 @@
       <x:c r="L38" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N38"/>
+      <x:c r="O38"/>
+      <x:c r="P38"/>
+      <x:c r="Q38"/>
+      <x:c r="R38"/>
+      <x:c r="S38"/>
+      <x:c r="T38"/>
+      <x:c r="U38"/>
+      <x:c r="V38"/>
     </x:row>
     <x:row r="39" ht="21" customHeight="1">
       <x:c r="A39" t="s">
@@ -4334,11 +4647,17 @@
       <x:c r="L39" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N39"/>
       <x:c r="O39" t="str"/>
-      <x:c r="S39" t="s">
+      <x:c r="P39"/>
+      <x:c r="Q39"/>
+      <x:c r="R39"/>
+      <x:c r="S39"/>
+      <x:c r="T39" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="U39" t="s">
+      <x:c r="U39"/>
+      <x:c r="V39" t="s">
         <x:v>120</x:v>
       </x:c>
     </x:row>
@@ -4364,10 +4683,17 @@
       <x:c r="K40" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="O40" t="str">
+      <x:c r="N40"/>
+      <x:c r="O40"/>
+      <x:c r="P40" t="str">
         <x:v>金属-19</x:v>
       </x:c>
-      <x:c r="U40" t="s">
+      <x:c r="Q40"/>
+      <x:c r="R40"/>
+      <x:c r="S40"/>
+      <x:c r="T40"/>
+      <x:c r="U40"/>
+      <x:c r="V40" t="s">
         <x:v>124</x:v>
       </x:c>
     </x:row>
@@ -4393,6 +4719,15 @@
       <x:c r="M41" t="str">
         <x:v>外-15</x:v>
       </x:c>
+      <x:c r="N41"/>
+      <x:c r="O41"/>
+      <x:c r="P41"/>
+      <x:c r="Q41"/>
+      <x:c r="R41"/>
+      <x:c r="S41"/>
+      <x:c r="T41"/>
+      <x:c r="U41"/>
+      <x:c r="V41"/>
     </x:row>
     <x:row r="42" ht="21" customHeight="1">
       <x:c r="A42" t="s">
@@ -4413,6 +4748,15 @@
       <x:c r="K42" t="s">
         <x:v>128</x:v>
       </x:c>
+      <x:c r="N42"/>
+      <x:c r="O42"/>
+      <x:c r="P42"/>
+      <x:c r="Q42"/>
+      <x:c r="R42"/>
+      <x:c r="S42"/>
+      <x:c r="T42"/>
+      <x:c r="U42"/>
+      <x:c r="V42"/>
     </x:row>
     <x:row r="43" ht="21" customHeight="1">
       <x:c r="A43" t="s">
@@ -4433,6 +4777,15 @@
       <x:c r="L43" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N43"/>
+      <x:c r="O43"/>
+      <x:c r="P43"/>
+      <x:c r="Q43"/>
+      <x:c r="R43"/>
+      <x:c r="S43"/>
+      <x:c r="T43"/>
+      <x:c r="U43"/>
+      <x:c r="V43"/>
     </x:row>
     <x:row r="44" ht="21" customHeight="1">
       <x:c r="A44" t="s">
@@ -4453,6 +4806,15 @@
       <x:c r="J44" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N44"/>
+      <x:c r="O44"/>
+      <x:c r="P44"/>
+      <x:c r="Q44"/>
+      <x:c r="R44"/>
+      <x:c r="S44"/>
+      <x:c r="T44"/>
+      <x:c r="U44"/>
+      <x:c r="V44"/>
     </x:row>
     <x:row r="45" ht="21" customHeight="1">
       <x:c r="A45" t="s">
@@ -4473,6 +4835,15 @@
       <x:c r="J45" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N45"/>
+      <x:c r="O45"/>
+      <x:c r="P45"/>
+      <x:c r="Q45"/>
+      <x:c r="R45"/>
+      <x:c r="S45"/>
+      <x:c r="T45"/>
+      <x:c r="U45"/>
+      <x:c r="V45"/>
     </x:row>
     <x:row r="46" ht="21" customHeight="1">
       <x:c r="A46" t="s">
@@ -4509,14 +4880,23 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M46" t="str">
+        <x:v>内-7</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
         <x:v>段紙(土)-6</x:v>
       </x:c>
-      <x:c r="O46" t="str">
+      <x:c r="O46"/>
+      <x:c r="P46" t="str">
         <x:v>金属-20</x:v>
       </x:c>
-      <x:c r="P46" t="s">
+      <x:c r="Q46" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R46"/>
+      <x:c r="S46"/>
+      <x:c r="T46"/>
+      <x:c r="U46"/>
+      <x:c r="V46"/>
     </x:row>
     <x:row r="47" ht="21" customHeight="1">
       <x:c r="A47" t="s">
@@ -4540,6 +4920,15 @@
       <x:c r="L47" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
+      <x:c r="P47"/>
+      <x:c r="Q47"/>
+      <x:c r="R47"/>
+      <x:c r="S47"/>
+      <x:c r="T47"/>
+      <x:c r="U47"/>
+      <x:c r="V47"/>
     </x:row>
     <x:row r="48" ht="21" customHeight="1">
       <x:c r="A48" t="s">
@@ -4560,6 +4949,15 @@
       <x:c r="L48" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
+      <x:c r="S48"/>
+      <x:c r="T48"/>
+      <x:c r="U48"/>
+      <x:c r="V48"/>
     </x:row>
     <x:row r="49" ht="21" customHeight="1">
       <x:c r="A49" t="s">
@@ -4586,7 +4984,15 @@
       <x:c r="K49" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="U49" t="s">
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+      <x:c r="P49"/>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
+      <x:c r="S49"/>
+      <x:c r="T49"/>
+      <x:c r="U49"/>
+      <x:c r="V49" t="s">
         <x:v>139</x:v>
       </x:c>
     </x:row>
@@ -4615,6 +5021,15 @@
       <x:c r="L50" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
+      <x:c r="P50"/>
+      <x:c r="Q50"/>
+      <x:c r="R50"/>
+      <x:c r="S50"/>
+      <x:c r="T50"/>
+      <x:c r="U50"/>
+      <x:c r="V50"/>
     </x:row>
     <x:row r="51" ht="21" customHeight="1">
       <x:c r="A51" t="s">
@@ -4638,6 +5053,15 @@
       <x:c r="K51" t="s">
         <x:v>142</x:v>
       </x:c>
+      <x:c r="N51"/>
+      <x:c r="O51"/>
+      <x:c r="P51"/>
+      <x:c r="Q51"/>
+      <x:c r="R51"/>
+      <x:c r="S51"/>
+      <x:c r="T51"/>
+      <x:c r="U51"/>
+      <x:c r="V51"/>
     </x:row>
     <x:row r="52" ht="21" customHeight="1">
       <x:c r="A52" t="s">
@@ -4667,6 +5091,15 @@
       <x:c r="L52" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52"/>
+      <x:c r="S52"/>
+      <x:c r="T52"/>
+      <x:c r="U52"/>
+      <x:c r="V52"/>
     </x:row>
     <x:row r="53" ht="21" customHeight="1">
       <x:c r="A53" t="s">
@@ -4690,9 +5123,17 @@
       <x:c r="L53" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="S53" t="s">
+      <x:c r="N53"/>
+      <x:c r="O53"/>
+      <x:c r="P53"/>
+      <x:c r="Q53"/>
+      <x:c r="R53"/>
+      <x:c r="S53"/>
+      <x:c r="T53" t="s">
         <x:v>146</x:v>
       </x:c>
+      <x:c r="U53"/>
+      <x:c r="V53"/>
     </x:row>
     <x:row r="54" ht="21" customHeight="1">
       <x:c r="A54" t="s">
@@ -4716,7 +5157,15 @@
       <x:c r="I54" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="U54" t="s">
+      <x:c r="N54"/>
+      <x:c r="O54"/>
+      <x:c r="P54"/>
+      <x:c r="Q54"/>
+      <x:c r="R54"/>
+      <x:c r="S54"/>
+      <x:c r="T54"/>
+      <x:c r="U54"/>
+      <x:c r="V54" t="s">
         <x:v>150</x:v>
       </x:c>
     </x:row>
@@ -4742,6 +5191,15 @@
       <x:c r="K55" t="s">
         <x:v>152</x:v>
       </x:c>
+      <x:c r="N55"/>
+      <x:c r="O55"/>
+      <x:c r="P55"/>
+      <x:c r="Q55"/>
+      <x:c r="R55"/>
+      <x:c r="S55"/>
+      <x:c r="T55"/>
+      <x:c r="U55"/>
+      <x:c r="V55"/>
     </x:row>
     <x:row r="56" ht="21" customHeight="1">
       <x:c r="A56" t="s">
@@ -4762,6 +5220,15 @@
       <x:c r="K56" t="s">
         <x:v>154</x:v>
       </x:c>
+      <x:c r="N56"/>
+      <x:c r="O56"/>
+      <x:c r="P56"/>
+      <x:c r="Q56"/>
+      <x:c r="R56"/>
+      <x:c r="S56"/>
+      <x:c r="T56"/>
+      <x:c r="U56"/>
+      <x:c r="V56"/>
     </x:row>
     <x:row r="57" ht="21" customHeight="1">
       <x:c r="A57" t="s">
@@ -4785,10 +5252,17 @@
       <x:c r="L57" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O57" t="str">
+      <x:c r="N57"/>
+      <x:c r="O57"/>
+      <x:c r="P57" t="str">
         <x:v>金属-22</x:v>
       </x:c>
-      <x:c r="U57" t="s">
+      <x:c r="Q57"/>
+      <x:c r="R57"/>
+      <x:c r="S57"/>
+      <x:c r="T57"/>
+      <x:c r="U57"/>
+      <x:c r="V57" t="s">
         <x:v>157</x:v>
       </x:c>
     </x:row>
@@ -4820,6 +5294,15 @@
       <x:c r="L58" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N58"/>
+      <x:c r="O58"/>
+      <x:c r="P58"/>
+      <x:c r="Q58"/>
+      <x:c r="R58"/>
+      <x:c r="S58"/>
+      <x:c r="T58"/>
+      <x:c r="U58"/>
+      <x:c r="V58"/>
     </x:row>
     <x:row r="59" ht="21" customHeight="1">
       <x:c r="A59" t="s">
@@ -4843,10 +5326,17 @@
       <x:c r="J59" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="O59" t="str">
+      <x:c r="N59"/>
+      <x:c r="O59"/>
+      <x:c r="P59" t="str">
         <x:v>金属-21</x:v>
       </x:c>
-      <x:c r="U59" t="s">
+      <x:c r="Q59"/>
+      <x:c r="R59"/>
+      <x:c r="S59"/>
+      <x:c r="T59"/>
+      <x:c r="U59"/>
+      <x:c r="V59" t="s">
         <x:v>157</x:v>
       </x:c>
     </x:row>
@@ -4878,6 +5368,15 @@
       <x:c r="L60" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N60"/>
+      <x:c r="O60"/>
+      <x:c r="P60"/>
+      <x:c r="Q60"/>
+      <x:c r="R60"/>
+      <x:c r="S60"/>
+      <x:c r="T60"/>
+      <x:c r="U60"/>
+      <x:c r="V60"/>
     </x:row>
     <x:row r="61" ht="21" customHeight="1">
       <x:c r="A61" t="s">
@@ -4901,6 +5400,15 @@
       <x:c r="L61" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N61"/>
+      <x:c r="O61"/>
+      <x:c r="P61"/>
+      <x:c r="Q61"/>
+      <x:c r="R61"/>
+      <x:c r="S61"/>
+      <x:c r="T61"/>
+      <x:c r="U61"/>
+      <x:c r="V61"/>
     </x:row>
     <x:row r="62" ht="21" customHeight="1">
       <x:c r="A62" t="s">
@@ -4927,9 +5435,17 @@
       <x:c r="L62" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O62" t="str">
+      <x:c r="N62"/>
+      <x:c r="O62"/>
+      <x:c r="P62" t="str">
         <x:v>金属-23</x:v>
       </x:c>
+      <x:c r="Q62"/>
+      <x:c r="R62"/>
+      <x:c r="S62"/>
+      <x:c r="T62"/>
+      <x:c r="U62"/>
+      <x:c r="V62"/>
     </x:row>
     <x:row r="63" ht="21" customHeight="1">
       <x:c r="A63" t="s">
@@ -4956,6 +5472,15 @@
       <x:c r="L63" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N63"/>
+      <x:c r="O63"/>
+      <x:c r="P63"/>
+      <x:c r="Q63"/>
+      <x:c r="R63"/>
+      <x:c r="S63"/>
+      <x:c r="T63"/>
+      <x:c r="U63"/>
+      <x:c r="V63"/>
     </x:row>
     <x:row r="64" ht="21" customHeight="1">
       <x:c r="A64" t="s">
@@ -4976,6 +5501,15 @@
       <x:c r="J64" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N64"/>
+      <x:c r="O64"/>
+      <x:c r="P64"/>
+      <x:c r="Q64"/>
+      <x:c r="R64"/>
+      <x:c r="S64"/>
+      <x:c r="T64"/>
+      <x:c r="U64"/>
+      <x:c r="V64"/>
     </x:row>
     <x:row r="65" ht="21" customHeight="1">
       <x:c r="A65" t="s">
@@ -5017,9 +5551,17 @@
       <x:c r="M65" t="str">
         <x:v>内-8</x:v>
       </x:c>
-      <x:c r="Q65" t="str">
+      <x:c r="N65"/>
+      <x:c r="O65"/>
+      <x:c r="P65"/>
+      <x:c r="Q65"/>
+      <x:c r="R65" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S65"/>
+      <x:c r="T65"/>
+      <x:c r="U65"/>
+      <x:c r="V65"/>
     </x:row>
     <x:row r="66" ht="21" customHeight="1">
       <x:c r="A66" t="s">
@@ -5040,6 +5582,15 @@
       <x:c r="I66" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
+      <x:c r="P66"/>
+      <x:c r="Q66"/>
+      <x:c r="R66"/>
+      <x:c r="S66"/>
+      <x:c r="T66"/>
+      <x:c r="U66"/>
+      <x:c r="V66"/>
     </x:row>
     <x:row r="67" ht="21" customHeight="1">
       <x:c r="A67" t="s">
@@ -5063,7 +5614,15 @@
       <x:c r="J67" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="U67" t="s">
+      <x:c r="N67"/>
+      <x:c r="O67"/>
+      <x:c r="P67"/>
+      <x:c r="Q67"/>
+      <x:c r="R67"/>
+      <x:c r="S67"/>
+      <x:c r="T67"/>
+      <x:c r="U67"/>
+      <x:c r="V67" t="s">
         <x:v>178</x:v>
       </x:c>
     </x:row>
@@ -5086,6 +5645,15 @@
       <x:c r="K68" t="s">
         <x:v>180</x:v>
       </x:c>
+      <x:c r="N68"/>
+      <x:c r="O68"/>
+      <x:c r="P68"/>
+      <x:c r="Q68"/>
+      <x:c r="R68"/>
+      <x:c r="S68"/>
+      <x:c r="T68"/>
+      <x:c r="U68"/>
+      <x:c r="V68"/>
     </x:row>
     <x:row r="69" ht="21" customHeight="1">
       <x:c r="A69" t="s">
@@ -5106,6 +5674,15 @@
       <x:c r="J69" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N69"/>
+      <x:c r="O69"/>
+      <x:c r="P69"/>
+      <x:c r="Q69"/>
+      <x:c r="R69"/>
+      <x:c r="S69"/>
+      <x:c r="T69"/>
+      <x:c r="U69"/>
+      <x:c r="V69"/>
     </x:row>
     <x:row r="70" ht="21" customHeight="1">
       <x:c r="A70" t="s">
@@ -5129,7 +5706,15 @@
       <x:c r="L70" t="s">
         <x:v>183</x:v>
       </x:c>
+      <x:c r="N70"/>
       <x:c r="O70" t="str"/>
+      <x:c r="P70"/>
+      <x:c r="Q70"/>
+      <x:c r="R70"/>
+      <x:c r="S70"/>
+      <x:c r="T70"/>
+      <x:c r="U70"/>
+      <x:c r="V70"/>
     </x:row>
     <x:row r="71" ht="21" customHeight="1">
       <x:c r="A71" t="s">
@@ -5156,12 +5741,19 @@
       <x:c r="L71" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="O71" t="str">
+      <x:c r="N71"/>
+      <x:c r="O71"/>
+      <x:c r="P71" t="str">
         <x:v>金属-24</x:v>
       </x:c>
-      <x:c r="Q71" t="str">
+      <x:c r="Q71"/>
+      <x:c r="R71" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S71"/>
+      <x:c r="T71"/>
+      <x:c r="U71"/>
+      <x:c r="V71"/>
     </x:row>
     <x:row r="72" ht="21" customHeight="1">
       <x:c r="A72" t="s">
@@ -5188,12 +5780,19 @@
       <x:c r="L72" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="O72" t="str">
+      <x:c r="N72"/>
+      <x:c r="O72"/>
+      <x:c r="P72" t="str">
         <x:v>金属-25</x:v>
       </x:c>
-      <x:c r="S72" t="s">
+      <x:c r="Q72"/>
+      <x:c r="R72"/>
+      <x:c r="S72"/>
+      <x:c r="T72" t="s">
         <x:v>189</x:v>
       </x:c>
+      <x:c r="U72"/>
+      <x:c r="V72"/>
     </x:row>
     <x:row r="73" ht="21" customHeight="1">
       <x:c r="A73" t="s">
@@ -5220,10 +5819,17 @@
       <x:c r="L73" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="S73" t="s">
+      <x:c r="N73"/>
+      <x:c r="O73"/>
+      <x:c r="P73"/>
+      <x:c r="Q73"/>
+      <x:c r="R73"/>
+      <x:c r="S73"/>
+      <x:c r="T73" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="U73" t="s">
+      <x:c r="U73"/>
+      <x:c r="V73" t="s">
         <x:v>139</x:v>
       </x:c>
     </x:row>
@@ -5252,7 +5858,15 @@
       <x:c r="L74" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="U74" t="s">
+      <x:c r="N74"/>
+      <x:c r="O74"/>
+      <x:c r="P74"/>
+      <x:c r="Q74"/>
+      <x:c r="R74"/>
+      <x:c r="S74"/>
+      <x:c r="T74"/>
+      <x:c r="U74"/>
+      <x:c r="V74" t="s">
         <x:v>124</x:v>
       </x:c>
     </x:row>
@@ -5281,6 +5895,15 @@
       <x:c r="L75" t="s">
         <x:v>196</x:v>
       </x:c>
+      <x:c r="N75"/>
+      <x:c r="O75"/>
+      <x:c r="P75"/>
+      <x:c r="Q75"/>
+      <x:c r="R75"/>
+      <x:c r="S75"/>
+      <x:c r="T75"/>
+      <x:c r="U75"/>
+      <x:c r="V75"/>
     </x:row>
     <x:row r="76" ht="21" customHeight="1">
       <x:c r="A76" t="s">
@@ -5301,9 +5924,17 @@
       <x:c r="M76" t="str">
         <x:v>内-17</x:v>
       </x:c>
-      <x:c r="S76" t="s">
+      <x:c r="N76"/>
+      <x:c r="O76"/>
+      <x:c r="P76"/>
+      <x:c r="Q76"/>
+      <x:c r="R76"/>
+      <x:c r="S76"/>
+      <x:c r="T76" t="s">
         <x:v>202</x:v>
       </x:c>
+      <x:c r="U76"/>
+      <x:c r="V76"/>
     </x:row>
     <x:row r="77" ht="21" customHeight="1">
       <x:c r="A77" t="s">
@@ -5330,10 +5961,17 @@
       <x:c r="L77" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="S77" t="s">
+      <x:c r="N77"/>
+      <x:c r="O77"/>
+      <x:c r="P77"/>
+      <x:c r="Q77"/>
+      <x:c r="R77"/>
+      <x:c r="S77"/>
+      <x:c r="T77" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="U77" t="s">
+      <x:c r="U77"/>
+      <x:c r="V77" t="s">
         <x:v>178</x:v>
       </x:c>
     </x:row>
@@ -5374,7 +6012,15 @@
       <x:c r="M78" t="str">
         <x:v>内-18</x:v>
       </x:c>
+      <x:c r="N78"/>
       <x:c r="O78" t="str"/>
+      <x:c r="P78"/>
+      <x:c r="Q78"/>
+      <x:c r="R78"/>
+      <x:c r="S78"/>
+      <x:c r="T78"/>
+      <x:c r="U78"/>
+      <x:c r="V78"/>
     </x:row>
     <x:row r="79" ht="21" customHeight="1">
       <x:c r="A79" t="s">
@@ -5401,6 +6047,15 @@
       <x:c r="L79" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N79"/>
+      <x:c r="O79"/>
+      <x:c r="P79"/>
+      <x:c r="Q79"/>
+      <x:c r="R79"/>
+      <x:c r="S79"/>
+      <x:c r="T79"/>
+      <x:c r="U79"/>
+      <x:c r="V79"/>
     </x:row>
     <x:row r="80" ht="21" customHeight="1">
       <x:c r="A80" t="s">
@@ -5424,6 +6079,15 @@
       <x:c r="L80" t="s">
         <x:v>73</x:v>
       </x:c>
+      <x:c r="N80"/>
+      <x:c r="O80"/>
+      <x:c r="P80"/>
+      <x:c r="Q80"/>
+      <x:c r="R80"/>
+      <x:c r="S80"/>
+      <x:c r="T80"/>
+      <x:c r="U80"/>
+      <x:c r="V80"/>
     </x:row>
     <x:row r="81" ht="21" customHeight="1">
       <x:c r="A81" t="s">
@@ -5447,6 +6111,15 @@
       <x:c r="L81" t="s">
         <x:v>199</x:v>
       </x:c>
+      <x:c r="N81"/>
+      <x:c r="O81"/>
+      <x:c r="P81"/>
+      <x:c r="Q81"/>
+      <x:c r="R81"/>
+      <x:c r="S81"/>
+      <x:c r="T81"/>
+      <x:c r="U81"/>
+      <x:c r="V81"/>
     </x:row>
     <x:row r="82" ht="21" customHeight="1">
       <x:c r="A82" t="s">
@@ -5488,6 +6161,15 @@
       <x:c r="M82" t="str">
         <x:v>内-16</x:v>
       </x:c>
+      <x:c r="N82"/>
+      <x:c r="O82"/>
+      <x:c r="P82"/>
+      <x:c r="Q82"/>
+      <x:c r="R82"/>
+      <x:c r="S82"/>
+      <x:c r="T82"/>
+      <x:c r="U82"/>
+      <x:c r="V82"/>
     </x:row>
     <x:row r="83" ht="21" customHeight="1">
       <x:c r="A83" t="s">
@@ -5523,6 +6205,15 @@
       <x:c r="M83" t="str">
         <x:v>内-14</x:v>
       </x:c>
+      <x:c r="N83"/>
+      <x:c r="O83"/>
+      <x:c r="P83"/>
+      <x:c r="Q83"/>
+      <x:c r="R83"/>
+      <x:c r="S83"/>
+      <x:c r="T83"/>
+      <x:c r="U83"/>
+      <x:c r="V83"/>
     </x:row>
     <x:row r="84" ht="21" customHeight="1">
       <x:c r="A84" t="s">
@@ -5561,6 +6252,15 @@
       <x:c r="M84" t="str">
         <x:v>内-15</x:v>
       </x:c>
+      <x:c r="N84"/>
+      <x:c r="O84"/>
+      <x:c r="P84"/>
+      <x:c r="Q84"/>
+      <x:c r="R84"/>
+      <x:c r="S84"/>
+      <x:c r="T84"/>
+      <x:c r="U84"/>
+      <x:c r="V84"/>
     </x:row>
     <x:row r="85" ht="21" customHeight="1">
       <x:c r="A85" t="s">
@@ -5587,7 +6287,15 @@
       <x:c r="L85" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="U85" t="s">
+      <x:c r="N85"/>
+      <x:c r="O85"/>
+      <x:c r="P85"/>
+      <x:c r="Q85"/>
+      <x:c r="R85"/>
+      <x:c r="S85"/>
+      <x:c r="T85"/>
+      <x:c r="U85"/>
+      <x:c r="V85" t="s">
         <x:v>224</x:v>
       </x:c>
     </x:row>
@@ -5619,10 +6327,17 @@
       <x:c r="L86" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N86"/>
       <x:c r="O86" t="str"/>
-      <x:c r="Q86" t="str">
+      <x:c r="P86"/>
+      <x:c r="Q86"/>
+      <x:c r="R86" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S86"/>
+      <x:c r="T86"/>
+      <x:c r="U86"/>
+      <x:c r="V86"/>
     </x:row>
     <x:row r="87" ht="21" customHeight="1">
       <x:c r="A87" t="s">
@@ -5661,6 +6376,15 @@
       <x:c r="M87" t="str">
         <x:v>内-13</x:v>
       </x:c>
+      <x:c r="N87"/>
+      <x:c r="O87"/>
+      <x:c r="P87"/>
+      <x:c r="Q87"/>
+      <x:c r="R87"/>
+      <x:c r="S87"/>
+      <x:c r="T87"/>
+      <x:c r="U87"/>
+      <x:c r="V87"/>
     </x:row>
     <x:row r="88" ht="21" customHeight="1">
       <x:c r="A88" t="s">
@@ -5696,12 +6420,19 @@
       <x:c r="L88" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O88" t="str">
+      <x:c r="N88"/>
+      <x:c r="O88"/>
+      <x:c r="P88" t="str">
         <x:v>金属-29</x:v>
       </x:c>
-      <x:c r="Q88" t="str">
+      <x:c r="Q88"/>
+      <x:c r="R88" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S88"/>
+      <x:c r="T88"/>
+      <x:c r="U88"/>
+      <x:c r="V88"/>
     </x:row>
     <x:row r="89" ht="21" customHeight="1">
       <x:c r="A89" t="s">
@@ -5734,6 +6465,15 @@
       <x:c r="L89" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N89"/>
+      <x:c r="O89"/>
+      <x:c r="P89"/>
+      <x:c r="Q89"/>
+      <x:c r="R89"/>
+      <x:c r="S89"/>
+      <x:c r="T89"/>
+      <x:c r="U89"/>
+      <x:c r="V89"/>
     </x:row>
     <x:row r="90" ht="21" customHeight="1">
       <x:c r="A90" t="s">
@@ -5766,6 +6506,15 @@
       <x:c r="L90" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N90"/>
+      <x:c r="O90"/>
+      <x:c r="P90"/>
+      <x:c r="Q90"/>
+      <x:c r="R90"/>
+      <x:c r="S90"/>
+      <x:c r="T90"/>
+      <x:c r="U90"/>
+      <x:c r="V90"/>
     </x:row>
     <x:row r="91" ht="21" customHeight="1">
       <x:c r="A91" t="s">
@@ -5801,12 +6550,19 @@
       <x:c r="L91" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O91" t="str">
+      <x:c r="N91"/>
+      <x:c r="O91"/>
+      <x:c r="P91" t="str">
         <x:v>金属-28</x:v>
       </x:c>
-      <x:c r="Q91" t="str">
+      <x:c r="Q91"/>
+      <x:c r="R91" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S91"/>
+      <x:c r="T91"/>
+      <x:c r="U91"/>
+      <x:c r="V91"/>
     </x:row>
     <x:row r="92" ht="21" customHeight="1">
       <x:c r="A92" t="s">
@@ -5833,9 +6589,17 @@
       <x:c r="L92" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O92" t="str">
+      <x:c r="N92"/>
+      <x:c r="O92"/>
+      <x:c r="P92" t="str">
         <x:v>金属-30</x:v>
       </x:c>
+      <x:c r="Q92"/>
+      <x:c r="R92"/>
+      <x:c r="S92"/>
+      <x:c r="T92"/>
+      <x:c r="U92"/>
+      <x:c r="V92"/>
     </x:row>
     <x:row r="93" ht="21" customHeight="1">
       <x:c r="A93" t="s">
@@ -5862,9 +6626,17 @@
       <x:c r="L93" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="S93" t="s">
+      <x:c r="N93"/>
+      <x:c r="O93"/>
+      <x:c r="P93"/>
+      <x:c r="Q93"/>
+      <x:c r="R93"/>
+      <x:c r="S93"/>
+      <x:c r="T93" t="s">
         <x:v>245</x:v>
       </x:c>
+      <x:c r="U93"/>
+      <x:c r="V93"/>
     </x:row>
     <x:row r="94" ht="21" customHeight="1">
       <x:c r="A94" t="s">
@@ -5891,6 +6663,15 @@
       <x:c r="L94" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N94"/>
+      <x:c r="O94"/>
+      <x:c r="P94"/>
+      <x:c r="Q94"/>
+      <x:c r="R94"/>
+      <x:c r="S94"/>
+      <x:c r="T94"/>
+      <x:c r="U94"/>
+      <x:c r="V94"/>
     </x:row>
     <x:row r="95" ht="21" customHeight="1">
       <x:c r="A95" t="s">
@@ -5914,6 +6695,15 @@
       <x:c r="K95" t="s">
         <x:v>248</x:v>
       </x:c>
+      <x:c r="N95"/>
+      <x:c r="O95"/>
+      <x:c r="P95"/>
+      <x:c r="Q95"/>
+      <x:c r="R95"/>
+      <x:c r="S95"/>
+      <x:c r="T95"/>
+      <x:c r="U95"/>
+      <x:c r="V95"/>
     </x:row>
     <x:row r="96" ht="21" customHeight="1">
       <x:c r="A96" t="s">
@@ -5937,6 +6727,15 @@
       <x:c r="K96" t="s">
         <x:v>250</x:v>
       </x:c>
+      <x:c r="N96"/>
+      <x:c r="O96"/>
+      <x:c r="P96"/>
+      <x:c r="Q96"/>
+      <x:c r="R96"/>
+      <x:c r="S96"/>
+      <x:c r="T96"/>
+      <x:c r="U96"/>
+      <x:c r="V96"/>
     </x:row>
     <x:row r="97" ht="21" customHeight="1">
       <x:c r="A97" t="s">
@@ -5960,6 +6759,15 @@
       <x:c r="L97" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N97"/>
+      <x:c r="O97"/>
+      <x:c r="P97"/>
+      <x:c r="Q97"/>
+      <x:c r="R97"/>
+      <x:c r="S97"/>
+      <x:c r="T97"/>
+      <x:c r="U97"/>
+      <x:c r="V97"/>
     </x:row>
     <x:row r="98" ht="21" customHeight="1">
       <x:c r="A98" t="s">
@@ -5986,6 +6794,15 @@
       <x:c r="K98" t="s">
         <x:v>254</x:v>
       </x:c>
+      <x:c r="N98"/>
+      <x:c r="O98"/>
+      <x:c r="P98"/>
+      <x:c r="Q98"/>
+      <x:c r="R98"/>
+      <x:c r="S98"/>
+      <x:c r="T98"/>
+      <x:c r="U98"/>
+      <x:c r="V98"/>
     </x:row>
     <x:row r="99" ht="21" customHeight="1">
       <x:c r="A99" t="s">
@@ -6009,6 +6826,15 @@
       <x:c r="L99" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N99"/>
+      <x:c r="O99"/>
+      <x:c r="P99"/>
+      <x:c r="Q99"/>
+      <x:c r="R99"/>
+      <x:c r="S99"/>
+      <x:c r="T99"/>
+      <x:c r="U99"/>
+      <x:c r="V99"/>
     </x:row>
     <x:row r="100" ht="21" customHeight="1">
       <x:c r="A100" t="s">
@@ -6035,6 +6861,15 @@
       <x:c r="L100" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N100"/>
+      <x:c r="O100"/>
+      <x:c r="P100"/>
+      <x:c r="Q100"/>
+      <x:c r="R100"/>
+      <x:c r="S100"/>
+      <x:c r="T100"/>
+      <x:c r="U100"/>
+      <x:c r="V100"/>
     </x:row>
     <x:row r="101" ht="21" customHeight="1">
       <x:c r="A101" t="s">
@@ -6074,14 +6909,23 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="M101" t="str">
+        <x:v>内-12</x:v>
+      </x:c>
+      <x:c r="N101" t="str">
         <x:v>段紙(土)-7</x:v>
       </x:c>
-      <x:c r="O101" t="str">
+      <x:c r="O101"/>
+      <x:c r="P101" t="str">
         <x:v>金属-27</x:v>
       </x:c>
-      <x:c r="P101" t="s">
+      <x:c r="Q101" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R101"/>
+      <x:c r="S101"/>
+      <x:c r="T101"/>
+      <x:c r="U101"/>
+      <x:c r="V101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="s">
@@ -6105,9 +6949,17 @@
       <x:c r="K102" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="S102" t="s">
+      <x:c r="N102"/>
+      <x:c r="O102"/>
+      <x:c r="P102"/>
+      <x:c r="Q102"/>
+      <x:c r="R102"/>
+      <x:c r="S102"/>
+      <x:c r="T102" t="s">
         <x:v>263</x:v>
       </x:c>
+      <x:c r="U102"/>
+      <x:c r="V102"/>
     </x:row>
     <x:row r="103" ht="21" customHeight="1">
       <x:c r="A103" t="s">
@@ -6131,9 +6983,17 @@
       <x:c r="K103" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="S103" t="s">
+      <x:c r="N103"/>
+      <x:c r="O103"/>
+      <x:c r="P103"/>
+      <x:c r="Q103"/>
+      <x:c r="R103"/>
+      <x:c r="S103"/>
+      <x:c r="T103" t="s">
         <x:v>266</x:v>
       </x:c>
+      <x:c r="U103"/>
+      <x:c r="V103"/>
     </x:row>
     <x:row r="104" ht="21" customHeight="1">
       <x:c r="A104" t="s">
@@ -6160,12 +7020,19 @@
       <x:c r="K104" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="O104" t="str">
+      <x:c r="N104"/>
+      <x:c r="O104"/>
+      <x:c r="P104" t="str">
         <x:v>金属-26</x:v>
       </x:c>
-      <x:c r="S104" t="s">
+      <x:c r="Q104"/>
+      <x:c r="R104"/>
+      <x:c r="S104"/>
+      <x:c r="T104" t="s">
         <x:v>269</x:v>
       </x:c>
+      <x:c r="U104"/>
+      <x:c r="V104"/>
     </x:row>
     <x:row r="105" ht="21" customHeight="1">
       <x:c r="A105" t="s">
@@ -6189,6 +7056,15 @@
       <x:c r="K105" t="s">
         <x:v>271</x:v>
       </x:c>
+      <x:c r="N105"/>
+      <x:c r="O105"/>
+      <x:c r="P105"/>
+      <x:c r="Q105"/>
+      <x:c r="R105"/>
+      <x:c r="S105"/>
+      <x:c r="T105"/>
+      <x:c r="U105"/>
+      <x:c r="V105"/>
     </x:row>
     <x:row r="106" ht="21" customHeight="1">
       <x:c r="A106" t="s">
@@ -6212,7 +7088,15 @@
       <x:c r="L106" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="U106" t="s">
+      <x:c r="N106"/>
+      <x:c r="O106"/>
+      <x:c r="P106"/>
+      <x:c r="Q106"/>
+      <x:c r="R106"/>
+      <x:c r="S106"/>
+      <x:c r="T106"/>
+      <x:c r="U106"/>
+      <x:c r="V106" t="s">
         <x:v>224</x:v>
       </x:c>
     </x:row>
@@ -6241,6 +7125,15 @@
       <x:c r="K107" t="s">
         <x:v>276</x:v>
       </x:c>
+      <x:c r="N107"/>
+      <x:c r="O107"/>
+      <x:c r="P107"/>
+      <x:c r="Q107"/>
+      <x:c r="R107"/>
+      <x:c r="S107"/>
+      <x:c r="T107"/>
+      <x:c r="U107"/>
+      <x:c r="V107"/>
     </x:row>
     <x:row r="108" ht="21" customHeight="1">
       <x:c r="A108" t="s">
@@ -6279,6 +7172,15 @@
       <x:c r="M108" t="str">
         <x:v>外-14</x:v>
       </x:c>
+      <x:c r="N108"/>
+      <x:c r="O108"/>
+      <x:c r="P108"/>
+      <x:c r="Q108"/>
+      <x:c r="R108"/>
+      <x:c r="S108"/>
+      <x:c r="T108"/>
+      <x:c r="U108"/>
+      <x:c r="V108"/>
     </x:row>
     <x:row r="109" ht="21" customHeight="1">
       <x:c r="A109" t="s">
@@ -6320,6 +7222,15 @@
       <x:c r="M109" t="str">
         <x:v>外-13</x:v>
       </x:c>
+      <x:c r="N109"/>
+      <x:c r="O109"/>
+      <x:c r="P109"/>
+      <x:c r="Q109"/>
+      <x:c r="R109"/>
+      <x:c r="S109"/>
+      <x:c r="T109"/>
+      <x:c r="U109"/>
+      <x:c r="V109"/>
     </x:row>
     <x:row r="110" ht="21" customHeight="1">
       <x:c r="A110" t="s">
@@ -6346,6 +7257,15 @@
       <x:c r="K110" t="s">
         <x:v>285</x:v>
       </x:c>
+      <x:c r="N110"/>
+      <x:c r="O110"/>
+      <x:c r="P110"/>
+      <x:c r="Q110"/>
+      <x:c r="R110"/>
+      <x:c r="S110"/>
+      <x:c r="T110"/>
+      <x:c r="U110"/>
+      <x:c r="V110"/>
     </x:row>
     <x:row r="111" ht="21" customHeight="1">
       <x:c r="A111" t="s">
@@ -6372,10 +7292,17 @@
       <x:c r="K111" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="O111" t="str">
+      <x:c r="N111"/>
+      <x:c r="O111"/>
+      <x:c r="P111" t="str">
         <x:v>金属-31</x:v>
       </x:c>
-      <x:c r="U111" t="s">
+      <x:c r="Q111"/>
+      <x:c r="R111"/>
+      <x:c r="S111"/>
+      <x:c r="T111"/>
+      <x:c r="U111"/>
+      <x:c r="V111" t="s">
         <x:v>124</x:v>
       </x:c>
     </x:row>
@@ -6401,6 +7328,15 @@
       <x:c r="K112" t="s">
         <x:v>290</x:v>
       </x:c>
+      <x:c r="N112"/>
+      <x:c r="O112"/>
+      <x:c r="P112"/>
+      <x:c r="Q112"/>
+      <x:c r="R112"/>
+      <x:c r="S112"/>
+      <x:c r="T112"/>
+      <x:c r="U112"/>
+      <x:c r="V112"/>
     </x:row>
     <x:row r="113" ht="21" customHeight="1">
       <x:c r="A113" t="s">
@@ -6442,15 +7378,21 @@
       <x:c r="M113" t="str">
         <x:v>内-11</x:v>
       </x:c>
-      <x:c r="O113" t="str">
+      <x:c r="N113"/>
+      <x:c r="O113"/>
+      <x:c r="P113" t="str">
         <x:v>金属-33</x:v>
       </x:c>
-      <x:c r="Q113" t="str">
+      <x:c r="Q113"/>
+      <x:c r="R113" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
-      <x:c r="S113" t="s">
+      <x:c r="S113"/>
+      <x:c r="T113" t="s">
         <x:v>295</x:v>
       </x:c>
+      <x:c r="U113"/>
+      <x:c r="V113"/>
     </x:row>
     <x:row r="114" ht="21" customHeight="1">
       <x:c r="A114" t="s">
@@ -6480,12 +7422,19 @@
       <x:c r="L114" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="O114" t="str">
+      <x:c r="N114"/>
+      <x:c r="O114"/>
+      <x:c r="P114" t="str">
         <x:v>金属-32</x:v>
       </x:c>
-      <x:c r="Q114" t="str">
+      <x:c r="Q114"/>
+      <x:c r="R114" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S114"/>
+      <x:c r="T114"/>
+      <x:c r="U114"/>
+      <x:c r="V114"/>
     </x:row>
     <x:row r="115" ht="21" customHeight="1">
       <x:c r="A115" t="s">
@@ -6524,12 +7473,19 @@
       <x:c r="L115" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="O115" t="str">
+      <x:c r="N115"/>
+      <x:c r="O115"/>
+      <x:c r="P115" t="str">
         <x:v>金属-34</x:v>
       </x:c>
-      <x:c r="Q115" t="str">
+      <x:c r="Q115"/>
+      <x:c r="R115" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S115"/>
+      <x:c r="T115"/>
+      <x:c r="U115"/>
+      <x:c r="V115"/>
     </x:row>
     <x:row r="116" ht="21" customHeight="1">
       <x:c r="A116" t="s">
@@ -6553,9 +7509,17 @@
       <x:c r="L116" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="O116" t="str">
+      <x:c r="N116"/>
+      <x:c r="O116"/>
+      <x:c r="P116" t="str">
         <x:v>金属-35</x:v>
       </x:c>
+      <x:c r="Q116"/>
+      <x:c r="R116"/>
+      <x:c r="S116"/>
+      <x:c r="T116"/>
+      <x:c r="U116"/>
+      <x:c r="V116"/>
     </x:row>
     <x:row r="117" ht="21" customHeight="1">
       <x:c r="A117" t="s">
@@ -6576,7 +7540,15 @@
       <x:c r="J117" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N117"/>
       <x:c r="O117" t="str"/>
+      <x:c r="P117"/>
+      <x:c r="Q117"/>
+      <x:c r="R117"/>
+      <x:c r="S117"/>
+      <x:c r="T117"/>
+      <x:c r="U117"/>
+      <x:c r="V117"/>
     </x:row>
     <x:row r="118" ht="21" customHeight="1">
       <x:c r="A118" t="s">
@@ -6603,6 +7575,15 @@
       <x:c r="L118" t="s">
         <x:v>114</x:v>
       </x:c>
+      <x:c r="N118"/>
+      <x:c r="O118"/>
+      <x:c r="P118"/>
+      <x:c r="Q118"/>
+      <x:c r="R118"/>
+      <x:c r="S118"/>
+      <x:c r="T118"/>
+      <x:c r="U118"/>
+      <x:c r="V118"/>
     </x:row>
     <x:row r="119" ht="21" customHeight="1">
       <x:c r="A119" t="s">
@@ -6626,6 +7607,15 @@
       <x:c r="L119" t="s">
         <x:v>108</x:v>
       </x:c>
+      <x:c r="N119"/>
+      <x:c r="O119"/>
+      <x:c r="P119"/>
+      <x:c r="Q119"/>
+      <x:c r="R119"/>
+      <x:c r="S119"/>
+      <x:c r="T119"/>
+      <x:c r="U119"/>
+      <x:c r="V119"/>
     </x:row>
     <x:row r="120" ht="21" customHeight="1">
       <x:c r="A120" t="s">
@@ -6649,6 +7639,15 @@
       <x:c r="L120" t="s">
         <x:v>123</x:v>
       </x:c>
+      <x:c r="N120"/>
+      <x:c r="O120"/>
+      <x:c r="P120"/>
+      <x:c r="Q120"/>
+      <x:c r="R120"/>
+      <x:c r="S120"/>
+      <x:c r="T120"/>
+      <x:c r="U120"/>
+      <x:c r="V120"/>
     </x:row>
     <x:row r="121" ht="21" customHeight="1">
       <x:c r="A121" t="s">
@@ -6678,9 +7677,17 @@
       <x:c r="L121" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="O121" t="str">
+      <x:c r="N121"/>
+      <x:c r="O121"/>
+      <x:c r="P121" t="str">
         <x:v>金属-36</x:v>
       </x:c>
+      <x:c r="Q121"/>
+      <x:c r="R121"/>
+      <x:c r="S121"/>
+      <x:c r="T121"/>
+      <x:c r="U121"/>
+      <x:c r="V121"/>
     </x:row>
     <x:row r="122" ht="21" customHeight="1">
       <x:c r="A122" t="s">
@@ -6710,7 +7717,15 @@
       <x:c r="L122" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="U122" t="s">
+      <x:c r="N122"/>
+      <x:c r="O122"/>
+      <x:c r="P122"/>
+      <x:c r="Q122"/>
+      <x:c r="R122"/>
+      <x:c r="S122"/>
+      <x:c r="T122"/>
+      <x:c r="U122"/>
+      <x:c r="V122" t="s">
         <x:v>313</x:v>
       </x:c>
     </x:row>
@@ -6739,6 +7754,15 @@
       <x:c r="L123" t="s">
         <x:v>154</x:v>
       </x:c>
+      <x:c r="N123"/>
+      <x:c r="O123"/>
+      <x:c r="P123"/>
+      <x:c r="Q123"/>
+      <x:c r="R123"/>
+      <x:c r="S123"/>
+      <x:c r="T123"/>
+      <x:c r="U123"/>
+      <x:c r="V123"/>
     </x:row>
     <x:row r="124" ht="21" customHeight="1">
       <x:c r="A124" t="s">
@@ -6762,6 +7786,15 @@
       <x:c r="L124" t="s">
         <x:v>152</x:v>
       </x:c>
+      <x:c r="N124"/>
+      <x:c r="O124"/>
+      <x:c r="P124"/>
+      <x:c r="Q124"/>
+      <x:c r="R124"/>
+      <x:c r="S124"/>
+      <x:c r="T124"/>
+      <x:c r="U124"/>
+      <x:c r="V124"/>
     </x:row>
     <x:row r="125" ht="21" customHeight="1">
       <x:c r="A125" t="s">
@@ -6785,6 +7818,15 @@
       <x:c r="L125" t="s">
         <x:v>138</x:v>
       </x:c>
+      <x:c r="N125"/>
+      <x:c r="O125"/>
+      <x:c r="P125"/>
+      <x:c r="Q125"/>
+      <x:c r="R125"/>
+      <x:c r="S125"/>
+      <x:c r="T125"/>
+      <x:c r="U125"/>
+      <x:c r="V125"/>
     </x:row>
     <x:row r="126" ht="21" customHeight="1">
       <x:c r="A126" t="s">
@@ -6814,12 +7856,19 @@
       <x:c r="L126" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="O126" t="str">
+      <x:c r="N126"/>
+      <x:c r="O126"/>
+      <x:c r="P126" t="str">
         <x:v>金属-37</x:v>
       </x:c>
-      <x:c r="Q126" t="str">
+      <x:c r="Q126"/>
+      <x:c r="R126" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S126"/>
+      <x:c r="T126"/>
+      <x:c r="U126"/>
+      <x:c r="V126"/>
     </x:row>
     <x:row r="127" ht="21" customHeight="1">
       <x:c r="A127" t="s">
@@ -6843,6 +7892,15 @@
       <x:c r="K127" t="s">
         <x:v>318</x:v>
       </x:c>
+      <x:c r="N127"/>
+      <x:c r="O127"/>
+      <x:c r="P127"/>
+      <x:c r="Q127"/>
+      <x:c r="R127"/>
+      <x:c r="S127"/>
+      <x:c r="T127"/>
+      <x:c r="U127"/>
+      <x:c r="V127"/>
     </x:row>
     <x:row r="128" ht="21" customHeight="1">
       <x:c r="A128" t="s">
@@ -6866,6 +7924,15 @@
       <x:c r="K128" t="s">
         <x:v>316</x:v>
       </x:c>
+      <x:c r="N128"/>
+      <x:c r="O128"/>
+      <x:c r="P128"/>
+      <x:c r="Q128"/>
+      <x:c r="R128"/>
+      <x:c r="S128"/>
+      <x:c r="T128"/>
+      <x:c r="U128"/>
+      <x:c r="V128"/>
     </x:row>
     <x:row r="129" ht="21" customHeight="1">
       <x:c r="A129" t="s">
@@ -6889,9 +7956,17 @@
       <x:c r="K129" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="S129" t="s">
+      <x:c r="N129"/>
+      <x:c r="O129"/>
+      <x:c r="P129"/>
+      <x:c r="Q129"/>
+      <x:c r="R129"/>
+      <x:c r="S129"/>
+      <x:c r="T129" t="s">
         <x:v>326</x:v>
       </x:c>
+      <x:c r="U129"/>
+      <x:c r="V129"/>
     </x:row>
     <x:row r="130" ht="21" customHeight="1">
       <x:c r="A130" t="s">
@@ -6918,12 +7993,19 @@
       <x:c r="K130" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="O130" t="str">
+      <x:c r="N130"/>
+      <x:c r="O130"/>
+      <x:c r="P130" t="str">
         <x:v>金属-38</x:v>
       </x:c>
-      <x:c r="S130" t="s">
+      <x:c r="Q130"/>
+      <x:c r="R130"/>
+      <x:c r="S130"/>
+      <x:c r="T130" t="s">
         <x:v>189</x:v>
       </x:c>
+      <x:c r="U130"/>
+      <x:c r="V130"/>
     </x:row>
     <x:row r="131" ht="21" customHeight="1">
       <x:c r="A131" t="s">
@@ -6965,6 +8047,15 @@
       <x:c r="M131" t="str">
         <x:v>内-10</x:v>
       </x:c>
+      <x:c r="N131"/>
+      <x:c r="O131"/>
+      <x:c r="P131"/>
+      <x:c r="Q131"/>
+      <x:c r="R131"/>
+      <x:c r="S131"/>
+      <x:c r="T131"/>
+      <x:c r="U131"/>
+      <x:c r="V131"/>
     </x:row>
     <x:row r="132" ht="21" customHeight="1">
       <x:c r="A132" t="s">
@@ -6988,6 +8079,15 @@
       <x:c r="K132" t="s">
         <x:v>332</x:v>
       </x:c>
+      <x:c r="N132"/>
+      <x:c r="O132"/>
+      <x:c r="P132"/>
+      <x:c r="Q132"/>
+      <x:c r="R132"/>
+      <x:c r="S132"/>
+      <x:c r="T132"/>
+      <x:c r="U132"/>
+      <x:c r="V132"/>
     </x:row>
     <x:row r="133" ht="21" customHeight="1">
       <x:c r="A133" t="s">
@@ -7011,6 +8111,15 @@
       <x:c r="K133" t="s">
         <x:v>335</x:v>
       </x:c>
+      <x:c r="N133"/>
+      <x:c r="O133"/>
+      <x:c r="P133"/>
+      <x:c r="Q133"/>
+      <x:c r="R133"/>
+      <x:c r="S133"/>
+      <x:c r="T133"/>
+      <x:c r="U133"/>
+      <x:c r="V133"/>
     </x:row>
     <x:row r="134" ht="21" customHeight="1">
       <x:c r="A134" t="s">
@@ -7031,6 +8140,15 @@
       <x:c r="K134" t="s">
         <x:v>337</x:v>
       </x:c>
+      <x:c r="N134"/>
+      <x:c r="O134"/>
+      <x:c r="P134"/>
+      <x:c r="Q134"/>
+      <x:c r="R134"/>
+      <x:c r="S134"/>
+      <x:c r="T134"/>
+      <x:c r="U134"/>
+      <x:c r="V134"/>
     </x:row>
     <x:row r="135" ht="21" customHeight="1">
       <x:c r="A135" t="s">
@@ -7064,14 +8182,23 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="M135" t="str">
+        <x:v>内-9</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
         <x:v>段紙(土)-8</x:v>
       </x:c>
-      <x:c r="O135" t="str">
+      <x:c r="O135"/>
+      <x:c r="P135" t="str">
         <x:v>金属-39</x:v>
       </x:c>
-      <x:c r="P135" t="s">
+      <x:c r="Q135" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R135"/>
+      <x:c r="S135"/>
+      <x:c r="T135"/>
+      <x:c r="U135"/>
+      <x:c r="V135"/>
     </x:row>
     <x:row r="136" ht="21" customHeight="1">
       <x:c r="A136" t="s">
@@ -7095,6 +8222,15 @@
       <x:c r="K136" t="s">
         <x:v>342</x:v>
       </x:c>
+      <x:c r="N136"/>
+      <x:c r="O136"/>
+      <x:c r="P136"/>
+      <x:c r="Q136"/>
+      <x:c r="R136"/>
+      <x:c r="S136"/>
+      <x:c r="T136"/>
+      <x:c r="U136"/>
+      <x:c r="V136"/>
     </x:row>
     <x:row r="137" ht="21" customHeight="1">
       <x:c r="A137" t="s">
@@ -7121,6 +8257,15 @@
       <x:c r="K137" t="s">
         <x:v>345</x:v>
       </x:c>
+      <x:c r="N137"/>
+      <x:c r="O137"/>
+      <x:c r="P137"/>
+      <x:c r="Q137"/>
+      <x:c r="R137"/>
+      <x:c r="S137"/>
+      <x:c r="T137"/>
+      <x:c r="U137"/>
+      <x:c r="V137"/>
     </x:row>
     <x:row r="138" ht="21" customHeight="1">
       <x:c r="A138" t="s">
@@ -7144,6 +8289,15 @@
       <x:c r="K138" t="s">
         <x:v>347</x:v>
       </x:c>
+      <x:c r="N138"/>
+      <x:c r="O138"/>
+      <x:c r="P138"/>
+      <x:c r="Q138"/>
+      <x:c r="R138"/>
+      <x:c r="S138"/>
+      <x:c r="T138"/>
+      <x:c r="U138"/>
+      <x:c r="V138"/>
     </x:row>
     <x:row r="139" ht="21" customHeight="1">
       <x:c r="A139" t="s">
@@ -7170,6 +8324,15 @@
       <x:c r="L139" t="s">
         <x:v>294</x:v>
       </x:c>
+      <x:c r="N139"/>
+      <x:c r="O139"/>
+      <x:c r="P139"/>
+      <x:c r="Q139"/>
+      <x:c r="R139"/>
+      <x:c r="S139"/>
+      <x:c r="T139"/>
+      <x:c r="U139"/>
+      <x:c r="V139"/>
     </x:row>
     <x:row r="140" ht="21" customHeight="1">
       <x:c r="A140" t="s">
@@ -7193,6 +8356,15 @@
       <x:c r="K140" t="s">
         <x:v>351</x:v>
       </x:c>
+      <x:c r="N140"/>
+      <x:c r="O140"/>
+      <x:c r="P140"/>
+      <x:c r="Q140"/>
+      <x:c r="R140"/>
+      <x:c r="S140"/>
+      <x:c r="T140"/>
+      <x:c r="U140"/>
+      <x:c r="V140"/>
     </x:row>
     <x:row r="141" ht="21" customHeight="1">
       <x:c r="A141" t="s">
@@ -7222,9 +8394,17 @@
       <x:c r="L141" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="O141" t="str">
+      <x:c r="N141"/>
+      <x:c r="O141"/>
+      <x:c r="P141" t="str">
         <x:v>金属-40</x:v>
       </x:c>
+      <x:c r="Q141"/>
+      <x:c r="R141"/>
+      <x:c r="S141"/>
+      <x:c r="T141"/>
+      <x:c r="U141"/>
+      <x:c r="V141"/>
     </x:row>
     <x:row r="142" ht="21" customHeight="1">
       <x:c r="A142" t="s">
@@ -7248,6 +8428,15 @@
       <x:c r="K142" t="s">
         <x:v>339</x:v>
       </x:c>
+      <x:c r="N142"/>
+      <x:c r="O142"/>
+      <x:c r="P142"/>
+      <x:c r="Q142"/>
+      <x:c r="R142"/>
+      <x:c r="S142"/>
+      <x:c r="T142"/>
+      <x:c r="U142"/>
+      <x:c r="V142"/>
     </x:row>
     <x:row r="143" ht="21" customHeight="1">
       <x:c r="A143" t="s">
@@ -7280,7 +8469,15 @@
       <x:c r="L143" t="s">
         <x:v>285</x:v>
       </x:c>
+      <x:c r="N143"/>
       <x:c r="O143" t="str"/>
+      <x:c r="P143"/>
+      <x:c r="Q143"/>
+      <x:c r="R143"/>
+      <x:c r="S143"/>
+      <x:c r="T143"/>
+      <x:c r="U143"/>
+      <x:c r="V143"/>
     </x:row>
     <x:row r="144" ht="21" customHeight="1">
       <x:c r="A144" t="s">
@@ -7304,10 +8501,17 @@
       <x:c r="K144" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="O144" t="str">
+      <x:c r="N144"/>
+      <x:c r="O144"/>
+      <x:c r="P144" t="str">
         <x:v>金属-41</x:v>
       </x:c>
-      <x:c r="U144" t="s">
+      <x:c r="Q144"/>
+      <x:c r="R144"/>
+      <x:c r="S144"/>
+      <x:c r="T144"/>
+      <x:c r="U144"/>
+      <x:c r="V144" t="s">
         <x:v>124</x:v>
       </x:c>
     </x:row>
@@ -7336,9 +8540,17 @@
       <x:c r="K145" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="O145" t="str">
+      <x:c r="N145"/>
+      <x:c r="O145"/>
+      <x:c r="P145" t="str">
         <x:v>金属-42</x:v>
       </x:c>
+      <x:c r="Q145"/>
+      <x:c r="R145"/>
+      <x:c r="S145"/>
+      <x:c r="T145"/>
+      <x:c r="U145"/>
+      <x:c r="V145"/>
     </x:row>
     <x:row r="146" ht="21" customHeight="1">
       <x:c r="A146" t="s">
@@ -7365,9 +8577,17 @@
       <x:c r="J146" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="S146" t="s">
+      <x:c r="N146"/>
+      <x:c r="O146"/>
+      <x:c r="P146"/>
+      <x:c r="Q146"/>
+      <x:c r="R146"/>
+      <x:c r="S146"/>
+      <x:c r="T146" t="s">
         <x:v>366</x:v>
       </x:c>
+      <x:c r="U146"/>
+      <x:c r="V146"/>
     </x:row>
     <x:row r="147" ht="21" customHeight="1">
       <x:c r="A147" t="s">
@@ -7391,6 +8611,15 @@
       <x:c r="L147" t="s">
         <x:v>308</x:v>
       </x:c>
+      <x:c r="N147"/>
+      <x:c r="O147"/>
+      <x:c r="P147"/>
+      <x:c r="Q147"/>
+      <x:c r="R147"/>
+      <x:c r="S147"/>
+      <x:c r="T147"/>
+      <x:c r="U147"/>
+      <x:c r="V147"/>
     </x:row>
     <x:row r="148" ht="21" customHeight="1">
       <x:c r="A148" t="s">
@@ -7411,6 +8640,15 @@
       <x:c r="L148" t="s">
         <x:v>316</x:v>
       </x:c>
+      <x:c r="N148"/>
+      <x:c r="O148"/>
+      <x:c r="P148"/>
+      <x:c r="Q148"/>
+      <x:c r="R148"/>
+      <x:c r="S148"/>
+      <x:c r="T148"/>
+      <x:c r="U148"/>
+      <x:c r="V148"/>
     </x:row>
     <x:row r="149" ht="21" customHeight="1">
       <x:c r="A149" t="s">
@@ -7437,9 +8675,17 @@
       <x:c r="K149" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="O149" t="str">
+      <x:c r="N149"/>
+      <x:c r="O149"/>
+      <x:c r="P149" t="str">
         <x:v>金属-43</x:v>
       </x:c>
+      <x:c r="Q149"/>
+      <x:c r="R149"/>
+      <x:c r="S149"/>
+      <x:c r="T149"/>
+      <x:c r="U149"/>
+      <x:c r="V149"/>
     </x:row>
     <x:row r="150" ht="21" customHeight="1">
       <x:c r="A150" t="s">
@@ -7466,6 +8712,15 @@
       <x:c r="L150" t="s">
         <x:v>339</x:v>
       </x:c>
+      <x:c r="N150"/>
+      <x:c r="O150"/>
+      <x:c r="P150"/>
+      <x:c r="Q150"/>
+      <x:c r="R150"/>
+      <x:c r="S150"/>
+      <x:c r="T150"/>
+      <x:c r="U150"/>
+      <x:c r="V150"/>
     </x:row>
     <x:row r="151" ht="21" customHeight="1">
       <x:c r="A151" t="s">
@@ -7489,6 +8744,15 @@
       <x:c r="I151" t="s">
         <x:v>351</x:v>
       </x:c>
+      <x:c r="N151"/>
+      <x:c r="O151"/>
+      <x:c r="P151"/>
+      <x:c r="Q151"/>
+      <x:c r="R151"/>
+      <x:c r="S151"/>
+      <x:c r="T151"/>
+      <x:c r="U151"/>
+      <x:c r="V151"/>
     </x:row>
     <x:row r="152" ht="21" customHeight="1">
       <x:c r="A152" t="s">
@@ -7515,6 +8779,15 @@
       <x:c r="L152" t="s">
         <x:v>330</x:v>
       </x:c>
+      <x:c r="N152"/>
+      <x:c r="O152"/>
+      <x:c r="P152"/>
+      <x:c r="Q152"/>
+      <x:c r="R152"/>
+      <x:c r="S152"/>
+      <x:c r="T152"/>
+      <x:c r="U152"/>
+      <x:c r="V152"/>
     </x:row>
     <x:row r="153" ht="21" customHeight="1">
       <x:c r="A153" t="s">
@@ -7538,6 +8811,15 @@
       <x:c r="K153" t="s">
         <x:v>380</x:v>
       </x:c>
+      <x:c r="N153"/>
+      <x:c r="O153"/>
+      <x:c r="P153"/>
+      <x:c r="Q153"/>
+      <x:c r="R153"/>
+      <x:c r="S153"/>
+      <x:c r="T153"/>
+      <x:c r="U153"/>
+      <x:c r="V153"/>
     </x:row>
     <x:row r="154" ht="21" customHeight="1">
       <x:c r="A154" t="s">
@@ -7579,6 +8861,15 @@
       <x:c r="M154" t="str">
         <x:v>外-12</x:v>
       </x:c>
+      <x:c r="N154"/>
+      <x:c r="O154"/>
+      <x:c r="P154"/>
+      <x:c r="Q154"/>
+      <x:c r="R154"/>
+      <x:c r="S154"/>
+      <x:c r="T154"/>
+      <x:c r="U154"/>
+      <x:c r="V154"/>
     </x:row>
     <x:row r="155" ht="21" customHeight="1">
       <x:c r="A155" t="s">
@@ -7599,6 +8890,15 @@
       <x:c r="I155" t="s">
         <x:v>332</x:v>
       </x:c>
+      <x:c r="N155"/>
+      <x:c r="O155"/>
+      <x:c r="P155"/>
+      <x:c r="Q155"/>
+      <x:c r="R155"/>
+      <x:c r="S155"/>
+      <x:c r="T155"/>
+      <x:c r="U155"/>
+      <x:c r="V155"/>
     </x:row>
     <x:row r="156" ht="21" customHeight="1">
       <x:c r="A156" t="s">
@@ -7628,6 +8928,15 @@
       <x:c r="L156" t="s">
         <x:v>318</x:v>
       </x:c>
+      <x:c r="N156"/>
+      <x:c r="O156"/>
+      <x:c r="P156"/>
+      <x:c r="Q156"/>
+      <x:c r="R156"/>
+      <x:c r="S156"/>
+      <x:c r="T156"/>
+      <x:c r="U156"/>
+      <x:c r="V156"/>
     </x:row>
     <x:row r="157" ht="21" customHeight="1">
       <x:c r="A157" t="s">
@@ -7648,12 +8957,19 @@
       <x:c r="K157" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="O157" t="str">
+      <x:c r="N157"/>
+      <x:c r="O157"/>
+      <x:c r="P157" t="str">
         <x:v>金属-44</x:v>
       </x:c>
-      <x:c r="Q157" t="str">
+      <x:c r="Q157"/>
+      <x:c r="R157" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S157"/>
+      <x:c r="T157"/>
+      <x:c r="U157"/>
+      <x:c r="V157"/>
     </x:row>
     <x:row r="158" ht="21" customHeight="1">
       <x:c r="A158" t="s">
@@ -7680,6 +8996,15 @@
       <x:c r="K158" t="s">
         <x:v>391</x:v>
       </x:c>
+      <x:c r="N158"/>
+      <x:c r="O158"/>
+      <x:c r="P158"/>
+      <x:c r="Q158"/>
+      <x:c r="R158"/>
+      <x:c r="S158"/>
+      <x:c r="T158"/>
+      <x:c r="U158"/>
+      <x:c r="V158"/>
     </x:row>
     <x:row r="159" ht="21" customHeight="1">
       <x:c r="A159" t="s">
@@ -7700,6 +9025,15 @@
       <x:c r="L159" t="s">
         <x:v>340</x:v>
       </x:c>
+      <x:c r="N159"/>
+      <x:c r="O159"/>
+      <x:c r="P159"/>
+      <x:c r="Q159"/>
+      <x:c r="R159"/>
+      <x:c r="S159"/>
+      <x:c r="T159"/>
+      <x:c r="U159"/>
+      <x:c r="V159"/>
     </x:row>
     <x:row r="160" ht="21" customHeight="1">
       <x:c r="A160" t="s">
@@ -7735,9 +9069,17 @@
       <x:c r="L160" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="O160" t="str">
+      <x:c r="N160"/>
+      <x:c r="O160"/>
+      <x:c r="P160" t="str">
         <x:v>金属-45</x:v>
       </x:c>
+      <x:c r="Q160"/>
+      <x:c r="R160"/>
+      <x:c r="S160"/>
+      <x:c r="T160"/>
+      <x:c r="U160"/>
+      <x:c r="V160"/>
     </x:row>
     <x:row r="161" ht="21" customHeight="1">
       <x:c r="A161" t="s">
@@ -7774,14 +9116,23 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="M161" t="str">
+        <x:v>外-11</x:v>
+      </x:c>
+      <x:c r="N161" t="str">
         <x:v>段紙(土)-9</x:v>
       </x:c>
-      <x:c r="O161" t="str">
+      <x:c r="O161"/>
+      <x:c r="P161" t="str">
         <x:v>金属-46</x:v>
       </x:c>
-      <x:c r="P161" t="s">
+      <x:c r="Q161" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="R161"/>
+      <x:c r="S161"/>
+      <x:c r="T161"/>
+      <x:c r="U161"/>
+      <x:c r="V161"/>
     </x:row>
     <x:row r="162" ht="21" customHeight="1">
       <x:c r="A162" t="s">
@@ -7805,7 +9156,15 @@
       <x:c r="K162" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="U162" t="s">
+      <x:c r="N162"/>
+      <x:c r="O162"/>
+      <x:c r="P162"/>
+      <x:c r="Q162"/>
+      <x:c r="R162"/>
+      <x:c r="S162"/>
+      <x:c r="T162"/>
+      <x:c r="U162"/>
+      <x:c r="V162" t="s">
         <x:v>400</x:v>
       </x:c>
     </x:row>
@@ -7834,9 +9193,17 @@
       <x:c r="L163" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="S163" t="s">
+      <x:c r="N163"/>
+      <x:c r="O163"/>
+      <x:c r="P163"/>
+      <x:c r="Q163"/>
+      <x:c r="R163"/>
+      <x:c r="S163"/>
+      <x:c r="T163" t="s">
         <x:v>403</x:v>
       </x:c>
+      <x:c r="U163"/>
+      <x:c r="V163"/>
     </x:row>
     <x:row r="164" ht="21" customHeight="1">
       <x:c r="A164" t="s">
@@ -7857,6 +9224,15 @@
       <x:c r="L164" t="s">
         <x:v>332</x:v>
       </x:c>
+      <x:c r="N164"/>
+      <x:c r="O164"/>
+      <x:c r="P164"/>
+      <x:c r="Q164"/>
+      <x:c r="R164"/>
+      <x:c r="S164"/>
+      <x:c r="T164"/>
+      <x:c r="U164"/>
+      <x:c r="V164"/>
     </x:row>
     <x:row r="165" ht="21" customHeight="1">
       <x:c r="A165" t="s">
@@ -7880,12 +9256,19 @@
       <x:c r="K165" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="O165" t="str">
+      <x:c r="N165"/>
+      <x:c r="O165"/>
+      <x:c r="P165" t="str">
         <x:v>金属-47</x:v>
       </x:c>
-      <x:c r="Q165" t="str">
+      <x:c r="Q165"/>
+      <x:c r="R165" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S165"/>
+      <x:c r="T165"/>
+      <x:c r="U165"/>
+      <x:c r="V165"/>
     </x:row>
     <x:row r="166" ht="21" customHeight="1">
       <x:c r="A166" t="s">
@@ -7909,6 +9292,15 @@
       <x:c r="L166" t="s">
         <x:v>335</x:v>
       </x:c>
+      <x:c r="N166"/>
+      <x:c r="O166"/>
+      <x:c r="P166"/>
+      <x:c r="Q166"/>
+      <x:c r="R166"/>
+      <x:c r="S166"/>
+      <x:c r="T166"/>
+      <x:c r="U166"/>
+      <x:c r="V166"/>
     </x:row>
     <x:row r="167" ht="21" customHeight="1">
       <x:c r="A167" t="s">
@@ -7932,6 +9324,15 @@
       <x:c r="L167" t="s">
         <x:v>342</x:v>
       </x:c>
+      <x:c r="N167"/>
+      <x:c r="O167"/>
+      <x:c r="P167"/>
+      <x:c r="Q167"/>
+      <x:c r="R167"/>
+      <x:c r="S167"/>
+      <x:c r="T167"/>
+      <x:c r="U167"/>
+      <x:c r="V167"/>
     </x:row>
     <x:row r="168" ht="21" customHeight="1">
       <x:c r="A168" t="s">
@@ -7952,6 +9353,15 @@
       <x:c r="L168" t="s">
         <x:v>351</x:v>
       </x:c>
+      <x:c r="N168"/>
+      <x:c r="O168"/>
+      <x:c r="P168"/>
+      <x:c r="Q168"/>
+      <x:c r="R168"/>
+      <x:c r="S168"/>
+      <x:c r="T168"/>
+      <x:c r="U168"/>
+      <x:c r="V168"/>
     </x:row>
     <x:row r="169" ht="21" customHeight="1">
       <x:c r="A169" t="s">
@@ -7975,7 +9385,15 @@
       <x:c r="M169" t="str">
         <x:v>外-10</x:v>
       </x:c>
-      <x:c r="U169" t="s">
+      <x:c r="N169"/>
+      <x:c r="O169"/>
+      <x:c r="P169"/>
+      <x:c r="Q169"/>
+      <x:c r="R169"/>
+      <x:c r="S169"/>
+      <x:c r="T169"/>
+      <x:c r="U169"/>
+      <x:c r="V169" t="s">
         <x:v>413</x:v>
       </x:c>
     </x:row>
@@ -8001,6 +9419,15 @@
       <x:c r="K170" t="s">
         <x:v>415</x:v>
       </x:c>
+      <x:c r="N170"/>
+      <x:c r="O170"/>
+      <x:c r="P170"/>
+      <x:c r="Q170"/>
+      <x:c r="R170"/>
+      <x:c r="S170"/>
+      <x:c r="T170"/>
+      <x:c r="U170"/>
+      <x:c r="V170"/>
     </x:row>
     <x:row r="171" ht="21" customHeight="1">
       <x:c r="A171" t="s">
@@ -8024,7 +9451,15 @@
       <x:c r="K171" t="s">
         <x:v>417</x:v>
       </x:c>
+      <x:c r="N171"/>
       <x:c r="O171" t="str"/>
+      <x:c r="P171"/>
+      <x:c r="Q171"/>
+      <x:c r="R171"/>
+      <x:c r="S171"/>
+      <x:c r="T171"/>
+      <x:c r="U171"/>
+      <x:c r="V171"/>
     </x:row>
     <x:row r="172" ht="21" customHeight="1">
       <x:c r="A172" t="s">
@@ -8048,6 +9483,15 @@
       <x:c r="K172" t="s">
         <x:v>420</x:v>
       </x:c>
+      <x:c r="N172"/>
+      <x:c r="O172"/>
+      <x:c r="P172"/>
+      <x:c r="Q172"/>
+      <x:c r="R172"/>
+      <x:c r="S172"/>
+      <x:c r="T172"/>
+      <x:c r="U172"/>
+      <x:c r="V172"/>
     </x:row>
     <x:row r="173" ht="21" customHeight="1">
       <x:c r="A173" t="s">
@@ -8074,6 +9518,15 @@
       <x:c r="L173" t="s">
         <x:v>360</x:v>
       </x:c>
+      <x:c r="N173"/>
+      <x:c r="O173"/>
+      <x:c r="P173"/>
+      <x:c r="Q173"/>
+      <x:c r="R173"/>
+      <x:c r="S173"/>
+      <x:c r="T173"/>
+      <x:c r="U173"/>
+      <x:c r="V173"/>
     </x:row>
     <x:row r="174" ht="21" customHeight="1">
       <x:c r="A174" t="s">
@@ -8103,9 +9556,17 @@
       <x:c r="L174" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="O174" t="str">
+      <x:c r="N174"/>
+      <x:c r="O174"/>
+      <x:c r="P174" t="str">
         <x:v>金属-49</x:v>
       </x:c>
+      <x:c r="Q174"/>
+      <x:c r="R174"/>
+      <x:c r="S174"/>
+      <x:c r="T174"/>
+      <x:c r="U174"/>
+      <x:c r="V174"/>
     </x:row>
     <x:row r="175" ht="21" customHeight="1">
       <x:c r="A175" t="s">
@@ -8126,6 +9587,15 @@
       <x:c r="K175" t="s">
         <x:v>426</x:v>
       </x:c>
+      <x:c r="N175"/>
+      <x:c r="O175"/>
+      <x:c r="P175"/>
+      <x:c r="Q175"/>
+      <x:c r="R175"/>
+      <x:c r="S175"/>
+      <x:c r="T175"/>
+      <x:c r="U175"/>
+      <x:c r="V175"/>
     </x:row>
     <x:row r="176" ht="21" customHeight="1">
       <x:c r="A176" t="s">
@@ -8149,6 +9619,15 @@
       <x:c r="J176" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N176"/>
+      <x:c r="O176"/>
+      <x:c r="P176"/>
+      <x:c r="Q176"/>
+      <x:c r="R176"/>
+      <x:c r="S176"/>
+      <x:c r="T176"/>
+      <x:c r="U176"/>
+      <x:c r="V176"/>
     </x:row>
     <x:row r="177" ht="21" customHeight="1">
       <x:c r="A177" t="s">
@@ -8190,12 +9669,19 @@
       <x:c r="M177" t="str">
         <x:v>外-9</x:v>
       </x:c>
-      <x:c r="O177" t="str">
+      <x:c r="N177"/>
+      <x:c r="O177"/>
+      <x:c r="P177" t="str">
         <x:v>金属-48</x:v>
       </x:c>
-      <x:c r="Q177" t="str">
+      <x:c r="Q177"/>
+      <x:c r="R177" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S177"/>
+      <x:c r="T177"/>
+      <x:c r="U177"/>
+      <x:c r="V177"/>
     </x:row>
     <x:row r="178" ht="21" customHeight="1">
       <x:c r="A178" t="s">
@@ -8216,6 +9702,15 @@
       <x:c r="I178" t="s">
         <x:v>387</x:v>
       </x:c>
+      <x:c r="N178"/>
+      <x:c r="O178"/>
+      <x:c r="P178"/>
+      <x:c r="Q178"/>
+      <x:c r="R178"/>
+      <x:c r="S178"/>
+      <x:c r="T178"/>
+      <x:c r="U178"/>
+      <x:c r="V178"/>
     </x:row>
     <x:row r="179" ht="21" customHeight="1">
       <x:c r="A179" t="s">
@@ -8239,6 +9734,15 @@
       <x:c r="L179" t="s">
         <x:v>391</x:v>
       </x:c>
+      <x:c r="N179"/>
+      <x:c r="O179"/>
+      <x:c r="P179"/>
+      <x:c r="Q179"/>
+      <x:c r="R179"/>
+      <x:c r="S179"/>
+      <x:c r="T179"/>
+      <x:c r="U179"/>
+      <x:c r="V179"/>
     </x:row>
     <x:row r="180" ht="21" customHeight="1">
       <x:c r="A180" t="s">
@@ -8268,6 +9772,15 @@
       <x:c r="L180" t="s">
         <x:v>383</x:v>
       </x:c>
+      <x:c r="N180"/>
+      <x:c r="O180"/>
+      <x:c r="P180"/>
+      <x:c r="Q180"/>
+      <x:c r="R180"/>
+      <x:c r="S180"/>
+      <x:c r="T180"/>
+      <x:c r="U180"/>
+      <x:c r="V180"/>
     </x:row>
     <x:row r="181" ht="21" customHeight="1">
       <x:c r="A181" t="s">
@@ -8288,6 +9801,15 @@
       <x:c r="J181" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N181"/>
+      <x:c r="O181"/>
+      <x:c r="P181"/>
+      <x:c r="Q181"/>
+      <x:c r="R181"/>
+      <x:c r="S181"/>
+      <x:c r="T181"/>
+      <x:c r="U181"/>
+      <x:c r="V181"/>
     </x:row>
     <x:row r="182" ht="21" customHeight="1">
       <x:c r="A182" t="s">
@@ -8311,9 +9833,17 @@
       <x:c r="L182" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="O182" t="str">
+      <x:c r="N182"/>
+      <x:c r="O182"/>
+      <x:c r="P182" t="str">
         <x:v>金属-50</x:v>
       </x:c>
+      <x:c r="Q182"/>
+      <x:c r="R182"/>
+      <x:c r="S182"/>
+      <x:c r="T182"/>
+      <x:c r="U182"/>
+      <x:c r="V182"/>
     </x:row>
     <x:row r="183" ht="21" customHeight="1">
       <x:c r="A183" t="s">
@@ -8337,9 +9867,17 @@
       <x:c r="L183" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="O183" t="str">
+      <x:c r="N183"/>
+      <x:c r="O183"/>
+      <x:c r="P183" t="str">
         <x:v>金属-51</x:v>
       </x:c>
+      <x:c r="Q183"/>
+      <x:c r="R183"/>
+      <x:c r="S183"/>
+      <x:c r="T183"/>
+      <x:c r="U183"/>
+      <x:c r="V183"/>
     </x:row>
     <x:row r="184" ht="21" customHeight="1">
       <x:c r="A184" t="s">
@@ -8360,9 +9898,17 @@
       <x:c r="J184" t="str">
         <x:v>M-</x:v>
       </x:c>
-      <x:c r="O184" t="str">
+      <x:c r="N184"/>
+      <x:c r="O184"/>
+      <x:c r="P184" t="str">
         <x:v>金属-52</x:v>
       </x:c>
+      <x:c r="Q184"/>
+      <x:c r="R184"/>
+      <x:c r="S184"/>
+      <x:c r="T184"/>
+      <x:c r="U184"/>
+      <x:c r="V184"/>
     </x:row>
     <x:row r="185" ht="21" customHeight="1">
       <x:c r="A185" t="s">
@@ -8386,6 +9932,15 @@
       <x:c r="L185" t="s">
         <x:v>380</x:v>
       </x:c>
+      <x:c r="N185"/>
+      <x:c r="O185"/>
+      <x:c r="P185"/>
+      <x:c r="Q185"/>
+      <x:c r="R185"/>
+      <x:c r="S185"/>
+      <x:c r="T185"/>
+      <x:c r="U185"/>
+      <x:c r="V185"/>
     </x:row>
     <x:row r="186" ht="21" customHeight="1">
       <x:c r="A186" t="s">
@@ -8415,6 +9970,15 @@
       <x:c r="M186" t="str">
         <x:v>外-8</x:v>
       </x:c>
+      <x:c r="N186"/>
+      <x:c r="O186"/>
+      <x:c r="P186"/>
+      <x:c r="Q186"/>
+      <x:c r="R186"/>
+      <x:c r="S186"/>
+      <x:c r="T186"/>
+      <x:c r="U186"/>
+      <x:c r="V186"/>
     </x:row>
     <x:row r="187" ht="21" customHeight="1">
       <x:c r="A187" t="s">
@@ -8441,7 +10005,15 @@
       <x:c r="M187" t="str">
         <x:v>外-7</x:v>
       </x:c>
-      <x:c r="U187" t="s">
+      <x:c r="N187"/>
+      <x:c r="O187"/>
+      <x:c r="P187"/>
+      <x:c r="Q187"/>
+      <x:c r="R187"/>
+      <x:c r="S187"/>
+      <x:c r="T187"/>
+      <x:c r="U187"/>
+      <x:c r="V187" t="s">
         <x:v>413</x:v>
       </x:c>
     </x:row>
@@ -8470,6 +10042,15 @@
       <x:c r="M188" t="str">
         <x:v>外-6</x:v>
       </x:c>
+      <x:c r="N188"/>
+      <x:c r="O188"/>
+      <x:c r="P188"/>
+      <x:c r="Q188"/>
+      <x:c r="R188"/>
+      <x:c r="S188"/>
+      <x:c r="T188"/>
+      <x:c r="U188"/>
+      <x:c r="V188"/>
     </x:row>
     <x:row r="189" ht="21" customHeight="1">
       <x:c r="A189" t="s">
@@ -8490,6 +10071,15 @@
       <x:c r="G189" t="s">
         <x:v>450</x:v>
       </x:c>
+      <x:c r="N189"/>
+      <x:c r="O189"/>
+      <x:c r="P189"/>
+      <x:c r="Q189"/>
+      <x:c r="R189"/>
+      <x:c r="S189"/>
+      <x:c r="T189"/>
+      <x:c r="U189"/>
+      <x:c r="V189"/>
     </x:row>
     <x:row r="190" ht="21" customHeight="1">
       <x:c r="A190" t="s">
@@ -8519,10 +10109,17 @@
       <x:c r="L190" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N190"/>
       <x:c r="O190" t="str"/>
-      <x:c r="Q190" t="str">
+      <x:c r="P190"/>
+      <x:c r="Q190"/>
+      <x:c r="R190" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S190"/>
+      <x:c r="T190"/>
+      <x:c r="U190"/>
+      <x:c r="V190"/>
     </x:row>
     <x:row r="191" ht="21" customHeight="1">
       <x:c r="A191" t="s">
@@ -8555,10 +10152,17 @@
       <x:c r="L191" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N191"/>
       <x:c r="O191" t="str"/>
-      <x:c r="Q191" t="str">
+      <x:c r="P191"/>
+      <x:c r="Q191"/>
+      <x:c r="R191" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S191"/>
+      <x:c r="T191"/>
+      <x:c r="U191"/>
+      <x:c r="V191"/>
     </x:row>
     <x:row r="192" ht="21" customHeight="1">
       <x:c r="A192" t="s">
@@ -8582,6 +10186,15 @@
       <x:c r="J192" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N192"/>
+      <x:c r="O192"/>
+      <x:c r="P192"/>
+      <x:c r="Q192"/>
+      <x:c r="R192"/>
+      <x:c r="S192"/>
+      <x:c r="T192"/>
+      <x:c r="U192"/>
+      <x:c r="V192"/>
     </x:row>
     <x:row r="193" ht="21" customHeight="1">
       <x:c r="A193" t="s">
@@ -8605,6 +10218,15 @@
       <x:c r="J193" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N193"/>
+      <x:c r="O193"/>
+      <x:c r="P193"/>
+      <x:c r="Q193"/>
+      <x:c r="R193"/>
+      <x:c r="S193"/>
+      <x:c r="T193"/>
+      <x:c r="U193"/>
+      <x:c r="V193"/>
     </x:row>
     <x:row r="194" ht="21" customHeight="1">
       <x:c r="A194" t="s">
@@ -8631,6 +10253,15 @@
       <x:c r="L194" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N194"/>
+      <x:c r="O194"/>
+      <x:c r="P194"/>
+      <x:c r="Q194"/>
+      <x:c r="R194"/>
+      <x:c r="S194"/>
+      <x:c r="T194"/>
+      <x:c r="U194"/>
+      <x:c r="V194"/>
     </x:row>
     <x:row r="195" ht="21" customHeight="1">
       <x:c r="A195" t="s">
@@ -8657,6 +10288,15 @@
       <x:c r="L195" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N195"/>
+      <x:c r="O195"/>
+      <x:c r="P195"/>
+      <x:c r="Q195"/>
+      <x:c r="R195"/>
+      <x:c r="S195"/>
+      <x:c r="T195"/>
+      <x:c r="U195"/>
+      <x:c r="V195"/>
     </x:row>
     <x:row r="196" ht="21" customHeight="1">
       <x:c r="A196" t="s">
@@ -8677,6 +10317,15 @@
       <x:c r="L196" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N196"/>
+      <x:c r="O196"/>
+      <x:c r="P196"/>
+      <x:c r="Q196"/>
+      <x:c r="R196"/>
+      <x:c r="S196"/>
+      <x:c r="T196"/>
+      <x:c r="U196"/>
+      <x:c r="V196"/>
     </x:row>
     <x:row r="197" ht="21" customHeight="1">
       <x:c r="A197" t="s">
@@ -8718,6 +10367,15 @@
       <x:c r="M197" t="str">
         <x:v>内-4</x:v>
       </x:c>
+      <x:c r="N197"/>
+      <x:c r="O197"/>
+      <x:c r="P197"/>
+      <x:c r="Q197"/>
+      <x:c r="R197"/>
+      <x:c r="S197"/>
+      <x:c r="T197"/>
+      <x:c r="U197"/>
+      <x:c r="V197"/>
     </x:row>
     <x:row r="198" ht="21" customHeight="1">
       <x:c r="A198" t="s">
@@ -8756,6 +10414,15 @@
       <x:c r="M198" t="str">
         <x:v>内-5</x:v>
       </x:c>
+      <x:c r="N198"/>
+      <x:c r="O198"/>
+      <x:c r="P198"/>
+      <x:c r="Q198"/>
+      <x:c r="R198"/>
+      <x:c r="S198"/>
+      <x:c r="T198"/>
+      <x:c r="U198"/>
+      <x:c r="V198"/>
     </x:row>
     <x:row r="199" ht="21" customHeight="1">
       <x:c r="A199" t="s">
@@ -8782,7 +10449,15 @@
       <x:c r="K199" t="s">
         <x:v>475</x:v>
       </x:c>
+      <x:c r="N199"/>
       <x:c r="O199" t="str"/>
+      <x:c r="P199"/>
+      <x:c r="Q199"/>
+      <x:c r="R199"/>
+      <x:c r="S199"/>
+      <x:c r="T199"/>
+      <x:c r="U199"/>
+      <x:c r="V199"/>
     </x:row>
     <x:row r="200" ht="21" customHeight="1">
       <x:c r="A200" t="s">
@@ -8812,7 +10487,15 @@
       <x:c r="L200" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N200"/>
       <x:c r="O200" t="str"/>
+      <x:c r="P200"/>
+      <x:c r="Q200"/>
+      <x:c r="R200"/>
+      <x:c r="S200"/>
+      <x:c r="T200"/>
+      <x:c r="U200"/>
+      <x:c r="V200"/>
     </x:row>
     <x:row r="201" ht="21" customHeight="1">
       <x:c r="A201" t="s">
@@ -8836,6 +10519,15 @@
       <x:c r="L201" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N201"/>
+      <x:c r="O201"/>
+      <x:c r="P201"/>
+      <x:c r="Q201"/>
+      <x:c r="R201"/>
+      <x:c r="S201"/>
+      <x:c r="T201"/>
+      <x:c r="U201"/>
+      <x:c r="V201"/>
     </x:row>
     <x:row r="202" ht="21" customHeight="1">
       <x:c r="A202" t="s">
@@ -8856,6 +10548,15 @@
       <x:c r="G202" t="s">
         <x:v>481</x:v>
       </x:c>
+      <x:c r="N202"/>
+      <x:c r="O202"/>
+      <x:c r="P202"/>
+      <x:c r="Q202"/>
+      <x:c r="R202"/>
+      <x:c r="S202"/>
+      <x:c r="T202"/>
+      <x:c r="U202"/>
+      <x:c r="V202"/>
     </x:row>
     <x:row r="203" ht="21" customHeight="1">
       <x:c r="A203" t="s">
@@ -8882,6 +10583,15 @@
       <x:c r="L203" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N203"/>
+      <x:c r="O203"/>
+      <x:c r="P203"/>
+      <x:c r="Q203"/>
+      <x:c r="R203"/>
+      <x:c r="S203"/>
+      <x:c r="T203"/>
+      <x:c r="U203"/>
+      <x:c r="V203"/>
     </x:row>
     <x:row r="204" ht="21" customHeight="1">
       <x:c r="A204" t="s">
@@ -8902,6 +10612,15 @@
       <x:c r="L204" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N204"/>
+      <x:c r="O204"/>
+      <x:c r="P204"/>
+      <x:c r="Q204"/>
+      <x:c r="R204"/>
+      <x:c r="S204"/>
+      <x:c r="T204"/>
+      <x:c r="U204"/>
+      <x:c r="V204"/>
     </x:row>
     <x:row r="205" ht="21" customHeight="1">
       <x:c r="A205" t="s">
@@ -8928,9 +10647,17 @@
       <x:c r="K205" t="s">
         <x:v>489</x:v>
       </x:c>
-      <x:c r="S205" t="s">
+      <x:c r="N205"/>
+      <x:c r="O205"/>
+      <x:c r="P205"/>
+      <x:c r="Q205"/>
+      <x:c r="R205"/>
+      <x:c r="S205"/>
+      <x:c r="T205" t="s">
         <x:v>490</x:v>
       </x:c>
+      <x:c r="U205"/>
+      <x:c r="V205"/>
     </x:row>
     <x:row r="206" ht="21" customHeight="1">
       <x:c r="A206" t="s">
@@ -8960,6 +10687,15 @@
       <x:c r="L206" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N206"/>
+      <x:c r="O206"/>
+      <x:c r="P206"/>
+      <x:c r="Q206"/>
+      <x:c r="R206"/>
+      <x:c r="S206"/>
+      <x:c r="T206"/>
+      <x:c r="U206"/>
+      <x:c r="V206"/>
     </x:row>
     <x:row r="207" ht="21" customHeight="1">
       <x:c r="A207" t="s">
@@ -8989,6 +10725,15 @@
       <x:c r="L207" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N207"/>
+      <x:c r="O207"/>
+      <x:c r="P207"/>
+      <x:c r="Q207"/>
+      <x:c r="R207"/>
+      <x:c r="S207"/>
+      <x:c r="T207"/>
+      <x:c r="U207"/>
+      <x:c r="V207"/>
     </x:row>
     <x:row r="208" ht="21" customHeight="1">
       <x:c r="A208" t="s">
@@ -9009,6 +10754,15 @@
       <x:c r="L208" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N208"/>
+      <x:c r="O208"/>
+      <x:c r="P208"/>
+      <x:c r="Q208"/>
+      <x:c r="R208"/>
+      <x:c r="S208"/>
+      <x:c r="T208"/>
+      <x:c r="U208"/>
+      <x:c r="V208"/>
     </x:row>
     <x:row r="209" ht="21" customHeight="1">
       <x:c r="A209" t="s">
@@ -9035,6 +10789,15 @@
       <x:c r="L209" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N209"/>
+      <x:c r="O209"/>
+      <x:c r="P209"/>
+      <x:c r="Q209"/>
+      <x:c r="R209"/>
+      <x:c r="S209"/>
+      <x:c r="T209"/>
+      <x:c r="U209"/>
+      <x:c r="V209"/>
     </x:row>
     <x:row r="210" ht="21" customHeight="1">
       <x:c r="A210" t="s">
@@ -9058,6 +10821,15 @@
       <x:c r="L210" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N210"/>
+      <x:c r="O210"/>
+      <x:c r="P210"/>
+      <x:c r="Q210"/>
+      <x:c r="R210"/>
+      <x:c r="S210"/>
+      <x:c r="T210"/>
+      <x:c r="U210"/>
+      <x:c r="V210"/>
     </x:row>
     <x:row r="211" ht="21" customHeight="1">
       <x:c r="A211" t="s">
@@ -9078,6 +10850,15 @@
       <x:c r="L211" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N211"/>
+      <x:c r="O211"/>
+      <x:c r="P211"/>
+      <x:c r="Q211"/>
+      <x:c r="R211"/>
+      <x:c r="S211"/>
+      <x:c r="T211"/>
+      <x:c r="U211"/>
+      <x:c r="V211"/>
     </x:row>
     <x:row r="212" ht="21" customHeight="1">
       <x:c r="A212" t="s">
@@ -9101,6 +10882,15 @@
       <x:c r="L212" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N212"/>
+      <x:c r="O212"/>
+      <x:c r="P212"/>
+      <x:c r="Q212"/>
+      <x:c r="R212"/>
+      <x:c r="S212"/>
+      <x:c r="T212"/>
+      <x:c r="U212"/>
+      <x:c r="V212"/>
     </x:row>
     <x:row r="213" ht="21" customHeight="1">
       <x:c r="A213" t="s">
@@ -9127,6 +10917,15 @@
       <x:c r="L213" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N213"/>
+      <x:c r="O213"/>
+      <x:c r="P213"/>
+      <x:c r="Q213"/>
+      <x:c r="R213"/>
+      <x:c r="S213"/>
+      <x:c r="T213"/>
+      <x:c r="U213"/>
+      <x:c r="V213"/>
     </x:row>
     <x:row r="214" ht="21" customHeight="1">
       <x:c r="A214" t="s">
@@ -9153,6 +10952,15 @@
       <x:c r="K214" t="s">
         <x:v>507</x:v>
       </x:c>
+      <x:c r="N214"/>
+      <x:c r="O214"/>
+      <x:c r="P214"/>
+      <x:c r="Q214"/>
+      <x:c r="R214"/>
+      <x:c r="S214"/>
+      <x:c r="T214"/>
+      <x:c r="U214"/>
+      <x:c r="V214"/>
     </x:row>
     <x:row r="215" ht="21" customHeight="1">
       <x:c r="A215" t="s">
@@ -9173,6 +10981,15 @@
       <x:c r="L215" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N215"/>
+      <x:c r="O215"/>
+      <x:c r="P215"/>
+      <x:c r="Q215"/>
+      <x:c r="R215"/>
+      <x:c r="S215"/>
+      <x:c r="T215"/>
+      <x:c r="U215"/>
+      <x:c r="V215"/>
     </x:row>
     <x:row r="216" ht="21" customHeight="1">
       <x:c r="A216" t="s">
@@ -9199,6 +11016,15 @@
       <x:c r="K216" t="s">
         <x:v>513</x:v>
       </x:c>
+      <x:c r="N216"/>
+      <x:c r="O216"/>
+      <x:c r="P216"/>
+      <x:c r="Q216"/>
+      <x:c r="R216"/>
+      <x:c r="S216"/>
+      <x:c r="T216"/>
+      <x:c r="U216"/>
+      <x:c r="V216"/>
     </x:row>
     <x:row r="217" ht="21" customHeight="1">
       <x:c r="A217" t="s">
@@ -9219,6 +11045,15 @@
       <x:c r="L217" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N217"/>
+      <x:c r="O217"/>
+      <x:c r="P217"/>
+      <x:c r="Q217"/>
+      <x:c r="R217"/>
+      <x:c r="S217"/>
+      <x:c r="T217"/>
+      <x:c r="U217"/>
+      <x:c r="V217"/>
     </x:row>
     <x:row r="218" ht="21" customHeight="1">
       <x:c r="A218" t="s">
@@ -9248,6 +11083,15 @@
       <x:c r="L218" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N218"/>
+      <x:c r="O218"/>
+      <x:c r="P218"/>
+      <x:c r="Q218"/>
+      <x:c r="R218"/>
+      <x:c r="S218"/>
+      <x:c r="T218"/>
+      <x:c r="U218"/>
+      <x:c r="V218"/>
     </x:row>
     <x:row r="219" ht="21" customHeight="1">
       <x:c r="A219" t="s">
@@ -9271,6 +11115,15 @@
       <x:c r="K219" t="s">
         <x:v>519</x:v>
       </x:c>
+      <x:c r="N219"/>
+      <x:c r="O219"/>
+      <x:c r="P219"/>
+      <x:c r="Q219"/>
+      <x:c r="R219"/>
+      <x:c r="S219"/>
+      <x:c r="T219"/>
+      <x:c r="U219"/>
+      <x:c r="V219"/>
     </x:row>
     <x:row r="220" ht="21" customHeight="1">
       <x:c r="A220" t="s">
@@ -9294,6 +11147,15 @@
       <x:c r="K220" t="s">
         <x:v>522</x:v>
       </x:c>
+      <x:c r="N220"/>
+      <x:c r="O220"/>
+      <x:c r="P220"/>
+      <x:c r="Q220"/>
+      <x:c r="R220"/>
+      <x:c r="S220"/>
+      <x:c r="T220"/>
+      <x:c r="U220"/>
+      <x:c r="V220"/>
     </x:row>
     <x:row r="221" ht="21" customHeight="1">
       <x:c r="A221" t="s">
@@ -9320,6 +11182,15 @@
       <x:c r="L221" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N221"/>
+      <x:c r="O221"/>
+      <x:c r="P221"/>
+      <x:c r="Q221"/>
+      <x:c r="R221"/>
+      <x:c r="S221"/>
+      <x:c r="T221"/>
+      <x:c r="U221"/>
+      <x:c r="V221"/>
     </x:row>
     <x:row r="222" ht="21" customHeight="1">
       <x:c r="A222" t="s">
@@ -9340,6 +11211,15 @@
       <x:c r="J222" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N222"/>
+      <x:c r="O222"/>
+      <x:c r="P222"/>
+      <x:c r="Q222"/>
+      <x:c r="R222"/>
+      <x:c r="S222"/>
+      <x:c r="T222"/>
+      <x:c r="U222"/>
+      <x:c r="V222"/>
     </x:row>
     <x:row r="223" ht="21" customHeight="1">
       <x:c r="A223" t="s">
@@ -9366,6 +11246,15 @@
       <x:c r="L223" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N223"/>
+      <x:c r="O223"/>
+      <x:c r="P223"/>
+      <x:c r="Q223"/>
+      <x:c r="R223"/>
+      <x:c r="S223"/>
+      <x:c r="T223"/>
+      <x:c r="U223"/>
+      <x:c r="V223"/>
     </x:row>
     <x:row r="224" ht="21" customHeight="1">
       <x:c r="A224" t="s">
@@ -9389,6 +11278,15 @@
       <x:c r="K224" t="s">
         <x:v>531</x:v>
       </x:c>
+      <x:c r="N224"/>
+      <x:c r="O224"/>
+      <x:c r="P224"/>
+      <x:c r="Q224"/>
+      <x:c r="R224"/>
+      <x:c r="S224"/>
+      <x:c r="T224"/>
+      <x:c r="U224"/>
+      <x:c r="V224"/>
     </x:row>
     <x:row r="225" ht="21" customHeight="1">
       <x:c r="A225" t="s">
@@ -9415,6 +11313,15 @@
       <x:c r="L225" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N225"/>
+      <x:c r="O225"/>
+      <x:c r="P225"/>
+      <x:c r="Q225"/>
+      <x:c r="R225"/>
+      <x:c r="S225"/>
+      <x:c r="T225"/>
+      <x:c r="U225"/>
+      <x:c r="V225"/>
     </x:row>
     <x:row r="226" ht="21" customHeight="1">
       <x:c r="A226" t="s">
@@ -9441,12 +11348,19 @@
       <x:c r="L226" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O226" t="str">
+      <x:c r="N226"/>
+      <x:c r="O226"/>
+      <x:c r="P226" t="str">
         <x:v>金属-61</x:v>
       </x:c>
-      <x:c r="Q226" t="str">
+      <x:c r="Q226"/>
+      <x:c r="R226" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S226"/>
+      <x:c r="T226"/>
+      <x:c r="U226"/>
+      <x:c r="V226"/>
     </x:row>
     <x:row r="227" ht="21" customHeight="1">
       <x:c r="A227" t="s">
@@ -9473,6 +11387,15 @@
       <x:c r="L227" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N227"/>
+      <x:c r="O227"/>
+      <x:c r="P227"/>
+      <x:c r="Q227"/>
+      <x:c r="R227"/>
+      <x:c r="S227"/>
+      <x:c r="T227"/>
+      <x:c r="U227"/>
+      <x:c r="V227"/>
     </x:row>
     <x:row r="228" ht="21" customHeight="1">
       <x:c r="A228" t="s">
@@ -9499,6 +11422,15 @@
       <x:c r="L228" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N228"/>
+      <x:c r="O228"/>
+      <x:c r="P228"/>
+      <x:c r="Q228"/>
+      <x:c r="R228"/>
+      <x:c r="S228"/>
+      <x:c r="T228"/>
+      <x:c r="U228"/>
+      <x:c r="V228"/>
     </x:row>
     <x:row r="229" ht="21" customHeight="1">
       <x:c r="A229" t="s">
@@ -9522,16 +11454,21 @@
       <x:c r="H229" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O229" t="str">
+      <x:c r="N229"/>
+      <x:c r="O229"/>
+      <x:c r="P229" t="str">
         <x:v>金属-60</x:v>
       </x:c>
-      <x:c r="Q229" t="str">
+      <x:c r="Q229"/>
+      <x:c r="R229" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
-      <x:c r="S229" t="s">
+      <x:c r="S229"/>
+      <x:c r="T229" t="s">
         <x:v>542</x:v>
       </x:c>
-      <x:c r="U229" t="s">
+      <x:c r="U229"/>
+      <x:c r="V229" t="s">
         <x:v>543</x:v>
       </x:c>
     </x:row>
@@ -9569,12 +11506,19 @@
       <x:c r="M230" t="str">
         <x:v>内-19</x:v>
       </x:c>
-      <x:c r="O230" t="str">
+      <x:c r="N230"/>
+      <x:c r="O230"/>
+      <x:c r="P230" t="str">
         <x:v>金属-59</x:v>
       </x:c>
-      <x:c r="Q230" t="str">
+      <x:c r="Q230"/>
+      <x:c r="R230" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S230"/>
+      <x:c r="T230"/>
+      <x:c r="U230"/>
+      <x:c r="V230"/>
     </x:row>
     <x:row r="231" ht="21" customHeight="1">
       <x:c r="A231" t="s">
@@ -9595,12 +11539,19 @@
       <x:c r="L231" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O231" t="str">
+      <x:c r="N231"/>
+      <x:c r="O231"/>
+      <x:c r="P231" t="str">
         <x:v>金属-62</x:v>
       </x:c>
-      <x:c r="S231" t="s">
+      <x:c r="Q231"/>
+      <x:c r="R231"/>
+      <x:c r="S231"/>
+      <x:c r="T231" t="s">
         <x:v>548</x:v>
       </x:c>
+      <x:c r="U231"/>
+      <x:c r="V231"/>
     </x:row>
     <x:row r="232" ht="21" customHeight="1">
       <x:c r="A232" t="s">
@@ -9627,6 +11578,15 @@
       <x:c r="L232" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N232"/>
+      <x:c r="O232"/>
+      <x:c r="P232"/>
+      <x:c r="Q232"/>
+      <x:c r="R232"/>
+      <x:c r="S232"/>
+      <x:c r="T232"/>
+      <x:c r="U232"/>
+      <x:c r="V232"/>
     </x:row>
     <x:row r="233" ht="21" customHeight="1">
       <x:c r="A233" t="s">
@@ -9653,9 +11613,17 @@
       <x:c r="L233" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="S233" t="s">
+      <x:c r="N233"/>
+      <x:c r="O233"/>
+      <x:c r="P233"/>
+      <x:c r="Q233"/>
+      <x:c r="R233"/>
+      <x:c r="S233"/>
+      <x:c r="T233" t="s">
         <x:v>553</x:v>
       </x:c>
+      <x:c r="U233"/>
+      <x:c r="V233"/>
     </x:row>
     <x:row r="234" ht="21" customHeight="1">
       <x:c r="A234" t="s">
@@ -9679,9 +11647,17 @@
       <x:c r="K234" t="s">
         <x:v>556</x:v>
       </x:c>
-      <x:c r="O234" t="str">
+      <x:c r="N234"/>
+      <x:c r="O234"/>
+      <x:c r="P234" t="str">
         <x:v>金属-55</x:v>
       </x:c>
+      <x:c r="Q234"/>
+      <x:c r="R234"/>
+      <x:c r="S234"/>
+      <x:c r="T234"/>
+      <x:c r="U234"/>
+      <x:c r="V234"/>
     </x:row>
     <x:row r="235" ht="21" customHeight="1">
       <x:c r="A235" t="s">
@@ -9708,6 +11684,15 @@
       <x:c r="L235" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N235"/>
+      <x:c r="O235"/>
+      <x:c r="P235"/>
+      <x:c r="Q235"/>
+      <x:c r="R235"/>
+      <x:c r="S235"/>
+      <x:c r="T235"/>
+      <x:c r="U235"/>
+      <x:c r="V235"/>
     </x:row>
     <x:row r="236" ht="21" customHeight="1">
       <x:c r="A236" t="s">
@@ -9731,12 +11716,19 @@
       <x:c r="K236" t="s">
         <x:v>559</x:v>
       </x:c>
-      <x:c r="O236" t="str">
+      <x:c r="N236"/>
+      <x:c r="O236"/>
+      <x:c r="P236" t="str">
         <x:v>金属-57</x:v>
       </x:c>
-      <x:c r="Q236" t="str">
+      <x:c r="Q236"/>
+      <x:c r="R236" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S236"/>
+      <x:c r="T236"/>
+      <x:c r="U236"/>
+      <x:c r="V236"/>
     </x:row>
     <x:row r="237" ht="21" customHeight="1">
       <x:c r="A237" t="s">
@@ -9763,12 +11755,19 @@
       <x:c r="K237" t="s">
         <x:v>562</x:v>
       </x:c>
-      <x:c r="O237" t="str">
+      <x:c r="N237"/>
+      <x:c r="O237"/>
+      <x:c r="P237" t="str">
         <x:v>金属-58</x:v>
       </x:c>
-      <x:c r="Q237" t="str">
+      <x:c r="Q237"/>
+      <x:c r="R237" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S237"/>
+      <x:c r="T237"/>
+      <x:c r="U237"/>
+      <x:c r="V237"/>
     </x:row>
     <x:row r="238" ht="21" customHeight="1">
       <x:c r="A238" t="s">
@@ -9792,12 +11791,19 @@
       <x:c r="K238" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="O238" t="str">
+      <x:c r="N238"/>
+      <x:c r="O238"/>
+      <x:c r="P238" t="str">
         <x:v>金属-56</x:v>
       </x:c>
-      <x:c r="Q238" t="str">
+      <x:c r="Q238"/>
+      <x:c r="R238" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S238"/>
+      <x:c r="T238"/>
+      <x:c r="U238"/>
+      <x:c r="V238"/>
     </x:row>
     <x:row r="239" ht="21" customHeight="1">
       <x:c r="A239" t="s">
@@ -9821,6 +11827,15 @@
       <x:c r="K239" t="s">
         <x:v>566</x:v>
       </x:c>
+      <x:c r="N239"/>
+      <x:c r="O239"/>
+      <x:c r="P239"/>
+      <x:c r="Q239"/>
+      <x:c r="R239"/>
+      <x:c r="S239"/>
+      <x:c r="T239"/>
+      <x:c r="U239"/>
+      <x:c r="V239"/>
     </x:row>
     <x:row r="240" ht="21" customHeight="1">
       <x:c r="A240" t="s">
@@ -9844,10 +11859,17 @@
       <x:c r="K240" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="O240" t="str">
+      <x:c r="N240"/>
+      <x:c r="O240"/>
+      <x:c r="P240" t="str">
         <x:v>金属-54</x:v>
       </x:c>
-      <x:c r="U240" t="s">
+      <x:c r="Q240"/>
+      <x:c r="R240"/>
+      <x:c r="S240"/>
+      <x:c r="T240"/>
+      <x:c r="U240"/>
+      <x:c r="V240" t="s">
         <x:v>124</x:v>
       </x:c>
     </x:row>
@@ -9873,10 +11895,17 @@
       <x:c r="K241" t="s">
         <x:v>572</x:v>
       </x:c>
-      <x:c r="O241" t="str">
+      <x:c r="N241"/>
+      <x:c r="O241"/>
+      <x:c r="P241" t="str">
         <x:v>金属-53</x:v>
       </x:c>
-      <x:c r="U241" t="s">
+      <x:c r="Q241"/>
+      <x:c r="R241"/>
+      <x:c r="S241"/>
+      <x:c r="T241"/>
+      <x:c r="U241"/>
+      <x:c r="V241" t="s">
         <x:v>124</x:v>
       </x:c>
     </x:row>
@@ -9902,6 +11931,15 @@
       <x:c r="H242" t="s">
         <x:v>101</x:v>
       </x:c>
+      <x:c r="N242"/>
+      <x:c r="O242"/>
+      <x:c r="P242"/>
+      <x:c r="Q242"/>
+      <x:c r="R242"/>
+      <x:c r="S242"/>
+      <x:c r="T242"/>
+      <x:c r="U242"/>
+      <x:c r="V242"/>
     </x:row>
     <x:row r="243" ht="21" customHeight="1">
       <x:c r="A243" t="s">
@@ -9931,6 +11969,15 @@
       <x:c r="L243" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N243"/>
+      <x:c r="O243"/>
+      <x:c r="P243"/>
+      <x:c r="Q243"/>
+      <x:c r="R243"/>
+      <x:c r="S243"/>
+      <x:c r="T243"/>
+      <x:c r="U243"/>
+      <x:c r="V243"/>
     </x:row>
     <x:row r="244" ht="21" customHeight="1">
       <x:c r="A244" t="s">
@@ -9951,6 +11998,15 @@
       <x:c r="I244" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N244"/>
+      <x:c r="O244"/>
+      <x:c r="P244"/>
+      <x:c r="Q244"/>
+      <x:c r="R244"/>
+      <x:c r="S244"/>
+      <x:c r="T244"/>
+      <x:c r="U244"/>
+      <x:c r="V244"/>
     </x:row>
     <x:row r="245" ht="21" customHeight="1">
       <x:c r="A245" t="s">
@@ -9974,6 +12030,15 @@
       <x:c r="I245" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N245"/>
+      <x:c r="O245"/>
+      <x:c r="P245"/>
+      <x:c r="Q245"/>
+      <x:c r="R245"/>
+      <x:c r="S245"/>
+      <x:c r="T245"/>
+      <x:c r="U245"/>
+      <x:c r="V245"/>
     </x:row>
     <x:row r="246" ht="21" customHeight="1">
       <x:c r="A246" t="s">
@@ -9994,6 +12059,15 @@
       <x:c r="I246" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N246"/>
+      <x:c r="O246"/>
+      <x:c r="P246"/>
+      <x:c r="Q246"/>
+      <x:c r="R246"/>
+      <x:c r="S246"/>
+      <x:c r="T246"/>
+      <x:c r="U246"/>
+      <x:c r="V246"/>
     </x:row>
     <x:row r="247" ht="21" customHeight="1">
       <x:c r="A247" t="s">
@@ -10033,17 +12107,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M247" t="str">
+        <x:v>外-5</x:v>
+      </x:c>
+      <x:c r="N247" t="str">
         <x:v>段紙(土)-3</x:v>
       </x:c>
-      <x:c r="O247" t="str">
+      <x:c r="O247"/>
+      <x:c r="P247" t="str">
         <x:v>金属-14</x:v>
       </x:c>
-      <x:c r="P247" t="s">
+      <x:c r="Q247" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S247" t="s">
+      <x:c r="R247"/>
+      <x:c r="S247"/>
+      <x:c r="T247" t="s">
         <x:v>585</x:v>
       </x:c>
+      <x:c r="U247"/>
+      <x:c r="V247"/>
     </x:row>
     <x:row r="248" ht="21" customHeight="1">
       <x:c r="A248" t="s">
@@ -10067,6 +12149,15 @@
       <x:c r="L248" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N248"/>
+      <x:c r="O248"/>
+      <x:c r="P248"/>
+      <x:c r="Q248"/>
+      <x:c r="R248"/>
+      <x:c r="S248"/>
+      <x:c r="T248"/>
+      <x:c r="U248"/>
+      <x:c r="V248"/>
     </x:row>
     <x:row r="249" ht="21" customHeight="1">
       <x:c r="A249" t="s">
@@ -10106,17 +12197,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M249" t="str">
+        <x:v>外-4</x:v>
+      </x:c>
+      <x:c r="N249" t="str">
         <x:v>段紙(土)-4</x:v>
       </x:c>
-      <x:c r="O249" t="str">
+      <x:c r="O249"/>
+      <x:c r="P249" t="str">
         <x:v>金属-15</x:v>
       </x:c>
-      <x:c r="P249" t="s">
+      <x:c r="Q249" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S249" t="s">
+      <x:c r="R249"/>
+      <x:c r="S249"/>
+      <x:c r="T249" t="s">
         <x:v>589</x:v>
       </x:c>
+      <x:c r="U249"/>
+      <x:c r="V249"/>
     </x:row>
     <x:row r="250" ht="21" customHeight="1">
       <x:c r="A250" t="s">
@@ -10137,6 +12236,15 @@
       <x:c r="J250" t="str">
         <x:v>M-</x:v>
       </x:c>
+      <x:c r="N250"/>
+      <x:c r="O250"/>
+      <x:c r="P250"/>
+      <x:c r="Q250"/>
+      <x:c r="R250"/>
+      <x:c r="S250"/>
+      <x:c r="T250"/>
+      <x:c r="U250"/>
+      <x:c r="V250"/>
     </x:row>
     <x:row r="251" ht="21" customHeight="1">
       <x:c r="A251" t="s">
@@ -10160,9 +12268,17 @@
       <x:c r="J251" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O251" t="str">
+      <x:c r="N251"/>
+      <x:c r="O251"/>
+      <x:c r="P251" t="str">
         <x:v>金属-17</x:v>
       </x:c>
+      <x:c r="Q251"/>
+      <x:c r="R251"/>
+      <x:c r="S251"/>
+      <x:c r="T251"/>
+      <x:c r="U251"/>
+      <x:c r="V251"/>
     </x:row>
     <x:row r="252" ht="21" customHeight="1">
       <x:c r="A252" t="s">
@@ -10186,9 +12302,17 @@
       <x:c r="J252" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O252" t="str">
+      <x:c r="N252"/>
+      <x:c r="O252"/>
+      <x:c r="P252" t="str">
         <x:v>金属-18</x:v>
       </x:c>
+      <x:c r="Q252"/>
+      <x:c r="R252"/>
+      <x:c r="S252"/>
+      <x:c r="T252"/>
+      <x:c r="U252"/>
+      <x:c r="V252"/>
     </x:row>
     <x:row r="253" ht="21" customHeight="1">
       <x:c r="A253" t="s">
@@ -10215,12 +12339,19 @@
       <x:c r="L253" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O253" t="str">
+      <x:c r="N253"/>
+      <x:c r="O253"/>
+      <x:c r="P253" t="str">
         <x:v>金属-16</x:v>
       </x:c>
-      <x:c r="Q253" t="str">
+      <x:c r="Q253"/>
+      <x:c r="R253" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S253"/>
+      <x:c r="T253"/>
+      <x:c r="U253"/>
+      <x:c r="V253"/>
     </x:row>
     <x:row r="254" ht="21" customHeight="1">
       <x:c r="A254" t="s">
@@ -10241,6 +12372,15 @@
       <x:c r="K254" t="s">
         <x:v>208</x:v>
       </x:c>
+      <x:c r="N254"/>
+      <x:c r="O254"/>
+      <x:c r="P254"/>
+      <x:c r="Q254"/>
+      <x:c r="R254"/>
+      <x:c r="S254"/>
+      <x:c r="T254"/>
+      <x:c r="U254"/>
+      <x:c r="V254"/>
     </x:row>
     <x:row r="255" ht="21" customHeight="1">
       <x:c r="A255" t="s">
@@ -10261,6 +12401,15 @@
       <x:c r="L255" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N255"/>
+      <x:c r="O255"/>
+      <x:c r="P255"/>
+      <x:c r="Q255"/>
+      <x:c r="R255"/>
+      <x:c r="S255"/>
+      <x:c r="T255"/>
+      <x:c r="U255"/>
+      <x:c r="V255"/>
     </x:row>
     <x:row r="256" ht="21" customHeight="1">
       <x:c r="A256" t="s">
@@ -10284,6 +12433,15 @@
       <x:c r="L256" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N256"/>
+      <x:c r="O256"/>
+      <x:c r="P256"/>
+      <x:c r="Q256"/>
+      <x:c r="R256"/>
+      <x:c r="S256"/>
+      <x:c r="T256"/>
+      <x:c r="U256"/>
+      <x:c r="V256"/>
     </x:row>
     <x:row r="257" ht="21" customHeight="1">
       <x:c r="A257" t="s">
@@ -10301,6 +12459,15 @@
       <x:c r="E257" t="s">
         <x:v>599</x:v>
       </x:c>
+      <x:c r="N257"/>
+      <x:c r="O257"/>
+      <x:c r="P257"/>
+      <x:c r="Q257"/>
+      <x:c r="R257"/>
+      <x:c r="S257"/>
+      <x:c r="T257"/>
+      <x:c r="U257"/>
+      <x:c r="V257"/>
     </x:row>
     <x:row r="258" ht="21" customHeight="1">
       <x:c r="A258" t="s">
@@ -10324,6 +12491,15 @@
       <x:c r="L258" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N258"/>
+      <x:c r="O258"/>
+      <x:c r="P258"/>
+      <x:c r="Q258"/>
+      <x:c r="R258"/>
+      <x:c r="S258"/>
+      <x:c r="T258"/>
+      <x:c r="U258"/>
+      <x:c r="V258"/>
     </x:row>
     <x:row r="259" ht="21" customHeight="1">
       <x:c r="A259" t="s">
@@ -10344,9 +12520,17 @@
       <x:c r="J259" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O259" t="str">
+      <x:c r="N259"/>
+      <x:c r="O259"/>
+      <x:c r="P259" t="str">
         <x:v>金属-13</x:v>
       </x:c>
+      <x:c r="Q259"/>
+      <x:c r="R259"/>
+      <x:c r="S259"/>
+      <x:c r="T259"/>
+      <x:c r="U259"/>
+      <x:c r="V259"/>
     </x:row>
     <x:row r="260" ht="21" customHeight="1">
       <x:c r="A260" t="s">
@@ -10367,7 +12551,15 @@
       <x:c r="J260" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="U260" t="s">
+      <x:c r="N260"/>
+      <x:c r="O260"/>
+      <x:c r="P260"/>
+      <x:c r="Q260"/>
+      <x:c r="R260"/>
+      <x:c r="S260"/>
+      <x:c r="T260"/>
+      <x:c r="U260"/>
+      <x:c r="V260" t="s">
         <x:v>604</x:v>
       </x:c>
     </x:row>
@@ -10390,10 +12582,17 @@
       <x:c r="J261" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O261" t="str">
+      <x:c r="N261"/>
+      <x:c r="O261"/>
+      <x:c r="P261" t="str">
         <x:v>金属-12</x:v>
       </x:c>
-      <x:c r="U261" t="s">
+      <x:c r="Q261"/>
+      <x:c r="R261"/>
+      <x:c r="S261"/>
+      <x:c r="T261"/>
+      <x:c r="U261"/>
+      <x:c r="V261" t="s">
         <x:v>604</x:v>
       </x:c>
     </x:row>
@@ -10419,6 +12618,15 @@
       <x:c r="L262" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N262"/>
+      <x:c r="O262"/>
+      <x:c r="P262"/>
+      <x:c r="Q262"/>
+      <x:c r="R262"/>
+      <x:c r="S262"/>
+      <x:c r="T262"/>
+      <x:c r="U262"/>
+      <x:c r="V262"/>
     </x:row>
     <x:row r="263" ht="21" customHeight="1">
       <x:c r="A263" t="s">
@@ -10445,10 +12653,17 @@
       <x:c r="K263" t="s">
         <x:v>196</x:v>
       </x:c>
+      <x:c r="N263"/>
       <x:c r="O263" t="str"/>
-      <x:c r="S263" t="s">
+      <x:c r="P263"/>
+      <x:c r="Q263"/>
+      <x:c r="R263"/>
+      <x:c r="S263"/>
+      <x:c r="T263" t="s">
         <x:v>609</x:v>
       </x:c>
+      <x:c r="U263"/>
+      <x:c r="V263"/>
     </x:row>
     <x:row r="264" ht="21" customHeight="1">
       <x:c r="A264" t="s">
@@ -10469,6 +12684,15 @@
       <x:c r="I264" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N264"/>
+      <x:c r="O264"/>
+      <x:c r="P264"/>
+      <x:c r="Q264"/>
+      <x:c r="R264"/>
+      <x:c r="S264"/>
+      <x:c r="T264"/>
+      <x:c r="U264"/>
+      <x:c r="V264"/>
     </x:row>
     <x:row r="265" ht="21" customHeight="1">
       <x:c r="A265" t="s">
@@ -10498,12 +12722,19 @@
       <x:c r="L265" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O265" t="str">
+      <x:c r="N265"/>
+      <x:c r="O265"/>
+      <x:c r="P265" t="str">
         <x:v>金属-11</x:v>
       </x:c>
-      <x:c r="Q265" t="str">
+      <x:c r="Q265"/>
+      <x:c r="R265" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S265"/>
+      <x:c r="T265"/>
+      <x:c r="U265"/>
+      <x:c r="V265"/>
     </x:row>
     <x:row r="266" ht="21" customHeight="1">
       <x:c r="A266" t="s">
@@ -10524,9 +12755,17 @@
       <x:c r="J266" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="S266" t="s">
+      <x:c r="N266"/>
+      <x:c r="O266"/>
+      <x:c r="P266"/>
+      <x:c r="Q266"/>
+      <x:c r="R266"/>
+      <x:c r="S266"/>
+      <x:c r="T266" t="s">
         <x:v>614</x:v>
       </x:c>
+      <x:c r="U266"/>
+      <x:c r="V266"/>
     </x:row>
     <x:row r="267" ht="21" customHeight="1">
       <x:c r="A267" t="s">
@@ -10556,12 +12795,19 @@
       <x:c r="L267" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O267" t="str">
+      <x:c r="N267"/>
+      <x:c r="O267"/>
+      <x:c r="P267" t="str">
         <x:v>金属-8</x:v>
       </x:c>
-      <x:c r="Q267" t="str">
+      <x:c r="Q267"/>
+      <x:c r="R267" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S267"/>
+      <x:c r="T267"/>
+      <x:c r="U267"/>
+      <x:c r="V267"/>
     </x:row>
     <x:row r="268" ht="21" customHeight="1">
       <x:c r="A268" t="s">
@@ -10591,7 +12837,15 @@
       <x:c r="L268" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N268"/>
       <x:c r="O268" t="str"/>
+      <x:c r="P268"/>
+      <x:c r="Q268"/>
+      <x:c r="R268"/>
+      <x:c r="S268"/>
+      <x:c r="T268"/>
+      <x:c r="U268"/>
+      <x:c r="V268"/>
     </x:row>
     <x:row r="269" ht="21" customHeight="1">
       <x:c r="A269" t="s">
@@ -10618,10 +12872,17 @@
       <x:c r="L269" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N269"/>
       <x:c r="O269" t="str"/>
-      <x:c r="Q269" t="str">
+      <x:c r="P269"/>
+      <x:c r="Q269"/>
+      <x:c r="R269" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S269"/>
+      <x:c r="T269"/>
+      <x:c r="U269"/>
+      <x:c r="V269"/>
     </x:row>
     <x:row r="270" ht="21" customHeight="1">
       <x:c r="A270" t="s">
@@ -10645,6 +12906,15 @@
       <x:c r="L270" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N270"/>
+      <x:c r="O270"/>
+      <x:c r="P270"/>
+      <x:c r="Q270"/>
+      <x:c r="R270"/>
+      <x:c r="S270"/>
+      <x:c r="T270"/>
+      <x:c r="U270"/>
+      <x:c r="V270"/>
     </x:row>
     <x:row r="271" ht="21" customHeight="1">
       <x:c r="A271" t="s">
@@ -10668,9 +12938,17 @@
       <x:c r="L271" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="S271" t="s">
+      <x:c r="N271"/>
+      <x:c r="O271"/>
+      <x:c r="P271"/>
+      <x:c r="Q271"/>
+      <x:c r="R271"/>
+      <x:c r="S271"/>
+      <x:c r="T271" t="s">
         <x:v>623</x:v>
       </x:c>
+      <x:c r="U271"/>
+      <x:c r="V271"/>
     </x:row>
     <x:row r="272" ht="21" customHeight="1">
       <x:c r="A272" t="s">
@@ -10694,6 +12972,15 @@
       <x:c r="L272" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N272"/>
+      <x:c r="O272"/>
+      <x:c r="P272"/>
+      <x:c r="Q272"/>
+      <x:c r="R272"/>
+      <x:c r="S272"/>
+      <x:c r="T272"/>
+      <x:c r="U272"/>
+      <x:c r="V272"/>
     </x:row>
     <x:row r="273" ht="21" customHeight="1">
       <x:c r="A273" t="s">
@@ -10711,6 +12998,15 @@
       <x:c r="E273" t="s">
         <x:v>626</x:v>
       </x:c>
+      <x:c r="N273"/>
+      <x:c r="O273"/>
+      <x:c r="P273"/>
+      <x:c r="Q273"/>
+      <x:c r="R273"/>
+      <x:c r="S273"/>
+      <x:c r="T273"/>
+      <x:c r="U273"/>
+      <x:c r="V273"/>
     </x:row>
     <x:row r="274" ht="21" customHeight="1">
       <x:c r="A274" t="s">
@@ -10747,14 +13043,23 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="M274" t="str">
+        <x:v>外-2</x:v>
+      </x:c>
+      <x:c r="N274" t="str">
         <x:v>段紙(土)-5</x:v>
       </x:c>
-      <x:c r="O274" t="str">
+      <x:c r="O274"/>
+      <x:c r="P274" t="str">
         <x:v>金属-7</x:v>
       </x:c>
-      <x:c r="Q274" t="str">
+      <x:c r="Q274"/>
+      <x:c r="R274" t="str">
         <x:v>ガラ-</x:v>
       </x:c>
+      <x:c r="S274"/>
+      <x:c r="T274"/>
+      <x:c r="U274"/>
+      <x:c r="V274"/>
     </x:row>
     <x:row r="275" ht="21" customHeight="1">
       <x:c r="A275" t="s">
@@ -10775,10 +13080,17 @@
       <x:c r="G275" t="s">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="S275" t="s">
+      <x:c r="N275"/>
+      <x:c r="O275"/>
+      <x:c r="P275"/>
+      <x:c r="Q275"/>
+      <x:c r="R275"/>
+      <x:c r="S275"/>
+      <x:c r="T275" t="s">
         <x:v>631</x:v>
       </x:c>
-      <x:c r="U275" t="s">
+      <x:c r="U275"/>
+      <x:c r="V275" t="s">
         <x:v>632</x:v>
       </x:c>
     </x:row>
@@ -10807,6 +13119,15 @@
       <x:c r="L276" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N276"/>
+      <x:c r="O276"/>
+      <x:c r="P276"/>
+      <x:c r="Q276"/>
+      <x:c r="R276"/>
+      <x:c r="S276"/>
+      <x:c r="T276"/>
+      <x:c r="U276"/>
+      <x:c r="V276"/>
     </x:row>
     <x:row r="277" ht="21" customHeight="1">
       <x:c r="A277" t="s">
@@ -10827,6 +13148,15 @@
       <x:c r="K277" t="s">
         <x:v>199</x:v>
       </x:c>
+      <x:c r="N277"/>
+      <x:c r="O277"/>
+      <x:c r="P277"/>
+      <x:c r="Q277"/>
+      <x:c r="R277"/>
+      <x:c r="S277"/>
+      <x:c r="T277"/>
+      <x:c r="U277"/>
+      <x:c r="V277"/>
     </x:row>
     <x:row r="278" ht="21" customHeight="1">
       <x:c r="A278" t="s">
@@ -10853,10 +13183,17 @@
       <x:c r="L278" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O278" t="str">
+      <x:c r="N278"/>
+      <x:c r="O278"/>
+      <x:c r="P278" t="str">
         <x:v>金属-10</x:v>
       </x:c>
-      <x:c r="U278" t="s">
+      <x:c r="Q278"/>
+      <x:c r="R278"/>
+      <x:c r="S278"/>
+      <x:c r="T278"/>
+      <x:c r="U278"/>
+      <x:c r="V278" t="s">
         <x:v>638</x:v>
       </x:c>
     </x:row>
@@ -10882,6 +13219,15 @@
       <x:c r="J279" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N279"/>
+      <x:c r="O279"/>
+      <x:c r="P279"/>
+      <x:c r="Q279"/>
+      <x:c r="R279"/>
+      <x:c r="S279"/>
+      <x:c r="T279"/>
+      <x:c r="U279"/>
+      <x:c r="V279"/>
     </x:row>
     <x:row r="280" ht="21" customHeight="1">
       <x:c r="A280" t="s">
@@ -10905,6 +13251,15 @@
       <x:c r="L280" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N280"/>
+      <x:c r="O280"/>
+      <x:c r="P280"/>
+      <x:c r="Q280"/>
+      <x:c r="R280"/>
+      <x:c r="S280"/>
+      <x:c r="T280"/>
+      <x:c r="U280"/>
+      <x:c r="V280"/>
     </x:row>
     <x:row r="281" ht="21" customHeight="1">
       <x:c r="A281" t="s">
@@ -10931,6 +13286,15 @@
       <x:c r="L281" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N281"/>
+      <x:c r="O281"/>
+      <x:c r="P281"/>
+      <x:c r="Q281"/>
+      <x:c r="R281"/>
+      <x:c r="S281"/>
+      <x:c r="T281"/>
+      <x:c r="U281"/>
+      <x:c r="V281"/>
     </x:row>
     <x:row r="282" ht="21" customHeight="1">
       <x:c r="A282" t="s">
@@ -10957,9 +13321,17 @@
       <x:c r="L282" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O282" t="str">
+      <x:c r="N282"/>
+      <x:c r="O282"/>
+      <x:c r="P282" t="str">
         <x:v>金属-9</x:v>
       </x:c>
+      <x:c r="Q282"/>
+      <x:c r="R282"/>
+      <x:c r="S282"/>
+      <x:c r="T282"/>
+      <x:c r="U282"/>
+      <x:c r="V282"/>
     </x:row>
     <x:row r="283" ht="21" customHeight="1">
       <x:c r="A283" t="s">
@@ -10986,6 +13358,15 @@
       <x:c r="L283" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N283"/>
+      <x:c r="O283"/>
+      <x:c r="P283"/>
+      <x:c r="Q283"/>
+      <x:c r="R283"/>
+      <x:c r="S283"/>
+      <x:c r="T283"/>
+      <x:c r="U283"/>
+      <x:c r="V283"/>
     </x:row>
     <x:row r="284" ht="21" customHeight="1">
       <x:c r="A284" t="s">
@@ -11012,6 +13393,15 @@
       <x:c r="L284" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N284"/>
+      <x:c r="O284"/>
+      <x:c r="P284"/>
+      <x:c r="Q284"/>
+      <x:c r="R284"/>
+      <x:c r="S284"/>
+      <x:c r="T284"/>
+      <x:c r="U284"/>
+      <x:c r="V284"/>
     </x:row>
     <x:row r="285" ht="21" customHeight="1">
       <x:c r="A285" t="s">
@@ -11035,6 +13425,15 @@
       <x:c r="M285" t="str">
         <x:v>外-3</x:v>
       </x:c>
+      <x:c r="N285"/>
+      <x:c r="O285"/>
+      <x:c r="P285"/>
+      <x:c r="Q285"/>
+      <x:c r="R285"/>
+      <x:c r="S285"/>
+      <x:c r="T285"/>
+      <x:c r="U285"/>
+      <x:c r="V285"/>
     </x:row>
     <x:row r="286" ht="21" customHeight="1">
       <x:c r="A286" t="s">
@@ -11058,6 +13457,15 @@
       <x:c r="I286" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N286"/>
+      <x:c r="O286"/>
+      <x:c r="P286"/>
+      <x:c r="Q286"/>
+      <x:c r="R286"/>
+      <x:c r="S286"/>
+      <x:c r="T286"/>
+      <x:c r="U286"/>
+      <x:c r="V286"/>
     </x:row>
     <x:row r="287" ht="21" customHeight="1">
       <x:c r="A287" t="s">
@@ -11078,6 +13486,15 @@
       <x:c r="I287" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N287"/>
+      <x:c r="O287"/>
+      <x:c r="P287"/>
+      <x:c r="Q287"/>
+      <x:c r="R287"/>
+      <x:c r="S287"/>
+      <x:c r="T287"/>
+      <x:c r="U287"/>
+      <x:c r="V287"/>
     </x:row>
     <x:row r="288" ht="21" customHeight="1">
       <x:c r="A288" t="s">
@@ -11101,6 +13518,15 @@
       <x:c r="L288" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="N288"/>
+      <x:c r="O288"/>
+      <x:c r="P288"/>
+      <x:c r="Q288"/>
+      <x:c r="R288"/>
+      <x:c r="S288"/>
+      <x:c r="T288"/>
+      <x:c r="U288"/>
+      <x:c r="V288"/>
     </x:row>
     <x:row r="289" ht="21" customHeight="1">
       <x:c r="A289" t="s">
@@ -11127,6 +13553,15 @@
       <x:c r="K289" t="s">
         <x:v>188</x:v>
       </x:c>
+      <x:c r="N289"/>
+      <x:c r="O289"/>
+      <x:c r="P289"/>
+      <x:c r="Q289"/>
+      <x:c r="R289"/>
+      <x:c r="S289"/>
+      <x:c r="T289"/>
+      <x:c r="U289"/>
+      <x:c r="V289"/>
     </x:row>
     <x:row r="290" ht="21" customHeight="1">
       <x:c r="A290" t="s">
@@ -11153,6 +13588,15 @@
       <x:c r="L290" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N290"/>
+      <x:c r="O290"/>
+      <x:c r="P290"/>
+      <x:c r="Q290"/>
+      <x:c r="R290"/>
+      <x:c r="S290"/>
+      <x:c r="T290"/>
+      <x:c r="U290"/>
+      <x:c r="V290"/>
     </x:row>
     <x:row r="291" ht="21" customHeight="1">
       <x:c r="A291" t="s">
@@ -11176,6 +13620,15 @@
       <x:c r="M291" t="str">
         <x:v>外-1</x:v>
       </x:c>
+      <x:c r="N291"/>
+      <x:c r="O291"/>
+      <x:c r="P291"/>
+      <x:c r="Q291"/>
+      <x:c r="R291"/>
+      <x:c r="S291"/>
+      <x:c r="T291"/>
+      <x:c r="U291"/>
+      <x:c r="V291"/>
     </x:row>
     <x:row r="292" ht="21" customHeight="1">
       <x:c r="A292" t="s">
@@ -11196,6 +13649,15 @@
       <x:c r="J292" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="N292"/>
+      <x:c r="O292"/>
+      <x:c r="P292"/>
+      <x:c r="Q292"/>
+      <x:c r="R292"/>
+      <x:c r="S292"/>
+      <x:c r="T292"/>
+      <x:c r="U292"/>
+      <x:c r="V292"/>
     </x:row>
     <x:row r="293" ht="22.5" customHeight="1">
       <x:c r="A293" t="s">
@@ -11222,7 +13684,15 @@
       <x:c r="K293" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="U293" t="s">
+      <x:c r="N293"/>
+      <x:c r="O293"/>
+      <x:c r="P293"/>
+      <x:c r="Q293"/>
+      <x:c r="R293"/>
+      <x:c r="S293"/>
+      <x:c r="T293"/>
+      <x:c r="U293"/>
+      <x:c r="V293" t="s">
         <x:v>662</x:v>
       </x:c>
     </x:row>
@@ -11248,7 +13718,15 @@
       <x:c r="K294" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="U294" t="s">
+      <x:c r="N294"/>
+      <x:c r="O294"/>
+      <x:c r="P294"/>
+      <x:c r="Q294"/>
+      <x:c r="R294"/>
+      <x:c r="S294"/>
+      <x:c r="T294"/>
+      <x:c r="U294"/>
+      <x:c r="V294" t="s">
         <x:v>666</x:v>
       </x:c>
     </x:row>
@@ -11277,7 +13755,15 @@
       <x:c r="L295" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="U295" t="s">
+      <x:c r="N295"/>
+      <x:c r="O295"/>
+      <x:c r="P295"/>
+      <x:c r="Q295"/>
+      <x:c r="R295"/>
+      <x:c r="S295"/>
+      <x:c r="T295"/>
+      <x:c r="U295"/>
+      <x:c r="V295" t="s">
         <x:v>670</x:v>
       </x:c>
     </x:row>
@@ -11304,10 +13790,10 @@
       <x:c r="J296"/>
       <x:c r="K296"/>
       <x:c r="L296"/>
-      <x:c r="M296" t="str">
+      <x:c r="M296"/>
+      <x:c r="N296" t="str">
         <x:v>段紙(土)-1</x:v>
       </x:c>
-      <x:c r="N296"/>
       <x:c r="O296"/>
       <x:c r="P296"/>
       <x:c r="Q296"/>
@@ -11315,6 +13801,7 @@
       <x:c r="S296"/>
       <x:c r="T296"/>
       <x:c r="U296"/>
+      <x:c r="V296"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" t="str">
@@ -11339,10 +13826,10 @@
       <x:c r="J297"/>
       <x:c r="K297"/>
       <x:c r="L297"/>
-      <x:c r="M297" t="str">
+      <x:c r="M297"/>
+      <x:c r="N297" t="str">
         <x:v>段紙(土)-11</x:v>
       </x:c>
-      <x:c r="N297"/>
       <x:c r="O297"/>
       <x:c r="P297"/>
       <x:c r="Q297"/>
@@ -11350,6 +13837,7 @@
       <x:c r="S297"/>
       <x:c r="T297"/>
       <x:c r="U297"/>
+      <x:c r="V297"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R09bdfd6011df473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rbbec8b3cd0584f2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R5b6e47a685534e54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Raa8f7a66d05442c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R1918551919394c0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rd251b1a586ce48cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R8357e9ebbcb9481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R3d5a5f4bad5d4681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R9158d87bae48495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rd522b4031dfa4a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R93820576eda44661"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R0d1471c88b514c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rb0510d1aab6b4c72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R8926dd20148546d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R5c4807a355e04947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R733a292d769949b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R0048c7950e164603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R964ad6d478f443b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R69bf6a779acc4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Rc80af685f2024f0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3616,7 +3616,9 @@
       <x:c r="N10"/>
       <x:c r="O10"/>
       <x:c r="P10"/>
-      <x:c r="Q10"/>
+      <x:c r="Q10" t="str">
+        <x:v>段紙-</x:v>
+      </x:c>
       <x:c r="R10"/>
       <x:c r="S10"/>
       <x:c r="T10"/>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R1ebe07936aa54058"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R9f355aa890144ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rdcbad7f4bb7044c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rf6c3a6095fcf4f09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R69b256997ea04d7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rf777381400084ad9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Re3612705d8924982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R1563a90e6a7546b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R40230da970b64ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R35b563b18dc44fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="Rc17de185a5a1410b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R709be1715feb4c49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Ra8e1bdaed46b4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rfe883c74167b4678"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R685791f530c94902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R24ba7273569c4285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R2c39fb8aab694a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R7bb5a1bd9f624151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="Rdebfabcf197e4ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R7bc802b2795a4f29"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -127,85 +127,85 @@
     <x:t xml:space="preserve">スターバックスコーヒー</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">イオンタウン可燃</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-7888</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">段紙・PET</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックスバリュ可燃</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22-1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">段紙・PET・アルミ・牛乳P</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">イオンタウン段紙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックス段紙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックスPETアルミ紙P</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PET アルミ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マックス発泡</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">発泡</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WE CARS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">22-8833</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">会社　商店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">関東電化ファインテック</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">マンション</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">フォーティーナイン</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">違反ゴミのみ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">第1第3水曜日</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">介護</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">みんなの家</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-4165</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">なごみの家</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">H-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ジャルディーノブリリオ（大和リビング）</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">K-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">イオンタウン可燃</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-7888</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">段紙・PET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックスバリュ可燃</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22-1555</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">段紙・PET・アルミ・牛乳P</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">イオンタウン段紙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックス段紙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックスPETアルミ紙P</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PET アルミ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マックス発泡</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">発泡</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WE CARS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">22-8833</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">会社　商店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">関東電化ファインテック</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">マンション</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">フォーティーナイン</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">違反ゴミのみ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">第1第3水曜日</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">介護</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">みんなの家</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-4165</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">なごみの家</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">H-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ジャルディーノブリリオ（大和リビング）</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">金属第4水曜日</x:t>
@@ -3275,8 +3275,8 @@
       <x:c r="H6" t="str">
         <x:v>K-1</x:v>
       </x:c>
-      <x:c r="I6" t="s">
-        <x:v>36</x:v>
+      <x:c r="I6" t="str">
+        <x:v>K-1</x:v>
       </x:c>
       <x:c r="J6" t="str">
         <x:v>M-</x:v>
@@ -3312,19 +3312,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="F7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G7" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="H7" t="str">
         <x:v>K-2</x:v>
       </x:c>
-      <x:c r="I7" t="s">
-        <x:v>36</x:v>
+      <x:c r="I7" t="str">
+        <x:v>K-2</x:v>
       </x:c>
       <x:c r="J7" t="str">
         <x:v>M-</x:v>
@@ -3349,7 +3349,7 @@
       </x:c>
       <x:c r="S7"/>
       <x:c r="T7" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="U7"/>
       <x:c r="V7"/>
@@ -3368,19 +3368,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E8" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="F8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="H8" t="str">
         <x:v>K-3</x:v>
       </x:c>
-      <x:c r="I8" t="s">
-        <x:v>36</x:v>
+      <x:c r="I8" t="str">
+        <x:v>K-3</x:v>
       </x:c>
       <x:c r="J8" t="str">
         <x:v>M-</x:v>
@@ -3405,7 +3405,7 @@
       </x:c>
       <x:c r="S8"/>
       <x:c r="T8" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="U8"/>
       <x:c r="V8"/>
@@ -3424,7 +3424,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F9" t="s">
         <x:v>5</x:v>
@@ -3467,7 +3467,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F10" t="s">
         <x:v>5</x:v>
@@ -3510,22 +3510,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H11" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H11" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="J11" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L11" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M11" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N11"/>
       <x:c r="O11"/>
@@ -3551,19 +3551,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E12" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H12" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F12" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H12" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="J12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N12"/>
       <x:c r="O12"/>
@@ -3589,16 +3589,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G13" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="G13" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>K-4</x:v>
       </x:c>
-      <x:c r="I13" t="s">
-        <x:v>36</x:v>
+      <x:c r="I13" t="str">
+        <x:v>K-4</x:v>
       </x:c>
       <x:c r="J13" t="str">
         <x:v>M-</x:v>
@@ -3626,7 +3626,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14">
         <x:v>13</x:v>
@@ -3635,7 +3635,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L14" t="s">
         <x:v>26</x:v>
@@ -3655,7 +3655,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C15">
         <x:v>14</x:v>
@@ -3664,7 +3664,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E15" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>M-</x:v>
@@ -3678,11 +3678,11 @@
       <x:c r="R15"/>
       <x:c r="S15"/>
       <x:c r="T15" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U15"/>
       <x:c r="V15" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="21" customHeight="1">
@@ -3690,7 +3690,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16">
         <x:v>15</x:v>
@@ -3699,13 +3699,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G16" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="I16" t="s">
-        <x:v>36</x:v>
+      <x:c r="I16" t="str">
+        <x:v>K-7</x:v>
       </x:c>
       <x:c r="L16" t="s">
         <x:v>26</x:v>
@@ -3725,7 +3725,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17">
         <x:v>16</x:v>
@@ -3734,10 +3734,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H17" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="H17" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>K-1</x:v>
@@ -3760,7 +3760,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18">
         <x:v>17</x:v>
@@ -3769,10 +3769,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="I18" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="I18" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="L18" t="s">
         <x:v>26</x:v>
@@ -3805,8 +3805,8 @@
       <x:c r="E19" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="I19" t="s">
-        <x:v>36</x:v>
+      <x:c r="I19" t="str">
+        <x:v>K-5</x:v>
       </x:c>
       <x:c r="L19" t="s">
         <x:v>26</x:v>
@@ -3826,7 +3826,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C20">
         <x:v>19</x:v>
@@ -3837,8 +3837,8 @@
       <x:c r="E20" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="I20" t="s">
-        <x:v>36</x:v>
+      <x:c r="I20" t="str">
+        <x:v>K-6</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>M-</x:v>
@@ -3858,7 +3858,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C21">
         <x:v>20</x:v>
@@ -3887,7 +3887,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C22">
         <x:v>21</x:v>
@@ -3916,7 +3916,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C23">
         <x:v>22</x:v>
@@ -3930,8 +3930,8 @@
       <x:c r="G23" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="I23" t="s">
-        <x:v>36</x:v>
+      <x:c r="I23" t="str">
+        <x:v>K-9</x:v>
       </x:c>
       <x:c r="L23" t="s">
         <x:v>26</x:v>
@@ -3955,7 +3955,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C24">
         <x:v>23</x:v>
@@ -3989,7 +3989,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C25">
         <x:v>24</x:v>
@@ -4035,8 +4035,8 @@
       <x:c r="G26" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="I26" t="s">
-        <x:v>36</x:v>
+      <x:c r="I26" t="str">
+        <x:v>K-8</x:v>
       </x:c>
       <x:c r="L26" t="s">
         <x:v>26</x:v>
@@ -4096,7 +4096,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C28">
         <x:v>27</x:v>
@@ -4142,8 +4142,8 @@
       <x:c r="H29" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="I29" t="s">
-        <x:v>36</x:v>
+      <x:c r="I29" t="str">
+        <x:v>K-10</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>K-2</x:v>
@@ -4180,7 +4180,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C30">
         <x:v>29</x:v>
@@ -4209,7 +4209,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C31">
         <x:v>30</x:v>
@@ -4223,8 +4223,8 @@
       <x:c r="G31" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="I31" t="s">
-        <x:v>36</x:v>
+      <x:c r="I31" t="str">
+        <x:v>K-11</x:v>
       </x:c>
       <x:c r="N31"/>
       <x:c r="O31"/>
@@ -4241,7 +4241,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C32">
         <x:v>31</x:v>
@@ -4252,9 +4252,7 @@
       <x:c r="E32" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="I32" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="I32"/>
       <x:c r="J32" t="str">
         <x:v>M-</x:v>
       </x:c>
@@ -4277,7 +4275,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C33">
         <x:v>32</x:v>
@@ -4330,8 +4328,8 @@
       <x:c r="H34" t="str">
         <x:v>K-5</x:v>
       </x:c>
-      <x:c r="I34" t="s">
-        <x:v>36</x:v>
+      <x:c r="I34" t="str">
+        <x:v>K-12</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>M-</x:v>
@@ -4357,7 +4355,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C35">
         <x:v>34</x:v>
@@ -4441,8 +4439,8 @@
       <x:c r="H37" t="str">
         <x:v>K-6</x:v>
       </x:c>
-      <x:c r="I37" t="s">
-        <x:v>36</x:v>
+      <x:c r="I37" t="str">
+        <x:v>K-14</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>M-</x:v>
@@ -4503,7 +4501,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C39">
         <x:v>38</x:v>
@@ -4514,8 +4512,8 @@
       <x:c r="E39" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="I39" t="s">
-        <x:v>36</x:v>
+      <x:c r="I39" t="str">
+        <x:v>K-15</x:v>
       </x:c>
       <x:c r="L39" t="s">
         <x:v>26</x:v>
@@ -4636,7 +4634,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C43">
         <x:v>42</x:v>
@@ -4665,7 +4663,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C44">
         <x:v>43</x:v>
@@ -4740,8 +4738,8 @@
       <x:c r="H46" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="I46" t="s">
-        <x:v>36</x:v>
+      <x:c r="I46" t="str">
+        <x:v>K-16</x:v>
       </x:c>
       <x:c r="J46" t="str">
         <x:v>M-</x:v>
@@ -4776,7 +4774,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C47">
         <x:v>46</x:v>
@@ -4874,7 +4872,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C50">
         <x:v>49</x:v>
@@ -4909,7 +4907,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C51">
         <x:v>50</x:v>
@@ -4941,7 +4939,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C52">
         <x:v>51</x:v>
@@ -4979,7 +4977,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C53">
         <x:v>52</x:v>
@@ -5027,9 +5025,10 @@
       <x:c r="G54" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="I54" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>K-</x:v>
+      </x:c>
+      <x:c r="J54"/>
       <x:c r="N54"/>
       <x:c r="O54"/>
       <x:c r="P54"/>
@@ -5360,7 +5359,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C64">
         <x:v>63</x:v>
@@ -5409,8 +5408,8 @@
       <x:c r="H65" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="I65" t="s">
-        <x:v>36</x:v>
+      <x:c r="I65" t="str">
+        <x:v>K-18</x:v>
       </x:c>
       <x:c r="J65" t="str">
         <x:v>M-</x:v>
@@ -5441,7 +5440,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C66">
         <x:v>65</x:v>
@@ -5452,8 +5451,8 @@
       <x:c r="E66" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="I66" t="s">
-        <x:v>36</x:v>
+      <x:c r="I66" t="str">
+        <x:v>K-17</x:v>
       </x:c>
       <x:c r="N66"/>
       <x:c r="O66"/>
@@ -5533,7 +5532,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C69">
         <x:v>68</x:v>
@@ -5562,7 +5561,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C70">
         <x:v>69</x:v>
@@ -5633,7 +5632,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C72">
         <x:v>71</x:v>
@@ -5711,7 +5710,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C74">
         <x:v>73</x:v>
@@ -5967,7 +5966,7 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="B81" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C81">
         <x:v>80</x:v>
@@ -6516,7 +6515,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B94" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C94">
         <x:v>93</x:v>
@@ -6583,7 +6582,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B96" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C96">
         <x:v>95</x:v>
@@ -6615,7 +6614,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C97">
         <x:v>96</x:v>
@@ -6647,7 +6646,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B98" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C98">
         <x:v>97</x:v>
@@ -6805,7 +6804,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B102" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C102">
         <x:v>101</x:v>
@@ -6839,7 +6838,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C103">
         <x:v>102</x:v>
@@ -6873,7 +6872,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C104">
         <x:v>103</x:v>
@@ -6912,7 +6911,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C105">
         <x:v>104</x:v>
@@ -7013,7 +7012,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B108" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C108">
         <x:v>107</x:v>
@@ -7030,8 +7029,8 @@
       <x:c r="H108" t="str">
         <x:v>K-32</x:v>
       </x:c>
-      <x:c r="I108" t="s">
-        <x:v>36</x:v>
+      <x:c r="I108" t="str">
+        <x:v>K-19</x:v>
       </x:c>
       <x:c r="J108" t="str">
         <x:v>M-</x:v>
@@ -7060,7 +7059,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B109" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C109">
         <x:v>108</x:v>
@@ -7080,8 +7079,8 @@
       <x:c r="H109" t="str">
         <x:v>K-33</x:v>
       </x:c>
-      <x:c r="I109" t="s">
-        <x:v>36</x:v>
+      <x:c r="I109" t="str">
+        <x:v>K-20</x:v>
       </x:c>
       <x:c r="J109" t="str">
         <x:v>M-</x:v>
@@ -7184,7 +7183,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B112" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C112">
         <x:v>111</x:v>
@@ -7365,7 +7364,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B116" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C116">
         <x:v>115</x:v>
@@ -7399,7 +7398,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B117" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C117">
         <x:v>116</x:v>
@@ -7428,7 +7427,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B118" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C118">
         <x:v>117</x:v>
@@ -7527,7 +7526,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B121" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C121">
         <x:v>120</x:v>
@@ -7642,7 +7641,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B124" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C124">
         <x:v>123</x:v>
@@ -7674,7 +7673,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B125" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C125">
         <x:v>124</x:v>
@@ -7748,7 +7747,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B127" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C127">
         <x:v>126</x:v>
@@ -7780,7 +7779,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B128" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C128">
         <x:v>127</x:v>
@@ -7812,7 +7811,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B129" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C129">
         <x:v>128</x:v>
@@ -7846,7 +7845,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B130" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C130">
         <x:v>129</x:v>
@@ -7935,7 +7934,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B132" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C132">
         <x:v>131</x:v>
@@ -8078,7 +8077,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B136" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C136">
         <x:v>135</x:v>
@@ -8110,7 +8109,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C137">
         <x:v>136</x:v>
@@ -8145,7 +8144,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C138">
         <x:v>137</x:v>
@@ -8212,7 +8211,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B140" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C140">
         <x:v>139</x:v>
@@ -8284,7 +8283,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B142" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C142">
         <x:v>141</x:v>
@@ -8430,7 +8429,7 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="B146" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C146">
         <x:v>145</x:v>
@@ -8467,7 +8466,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B147" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C147">
         <x:v>146</x:v>
@@ -8499,7 +8498,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B148" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C148">
         <x:v>147</x:v>
@@ -8528,7 +8527,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B149" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C149">
         <x:v>148</x:v>
@@ -8667,7 +8666,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B153" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C153">
         <x:v>152</x:v>
@@ -8749,7 +8748,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B155" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C155">
         <x:v>154</x:v>
@@ -8816,7 +8815,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B157" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C157">
         <x:v>156</x:v>
@@ -8849,7 +8848,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B158" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C158">
         <x:v>157</x:v>
@@ -8884,7 +8883,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B159" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C159">
         <x:v>158</x:v>
@@ -9012,7 +9011,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B162" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C162">
         <x:v>161</x:v>
@@ -9046,7 +9045,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B163" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C163">
         <x:v>162</x:v>
@@ -9083,7 +9082,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B164" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C164">
         <x:v>163</x:v>
@@ -9112,7 +9111,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B165" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C165">
         <x:v>164</x:v>
@@ -9180,7 +9179,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B167" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C167">
         <x:v>166</x:v>
@@ -9212,7 +9211,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B168" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C168">
         <x:v>167</x:v>
@@ -9275,7 +9274,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B170" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C170">
         <x:v>169</x:v>
@@ -9307,7 +9306,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B171" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C171">
         <x:v>170</x:v>
@@ -9339,7 +9338,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B172" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C172">
         <x:v>171</x:v>
@@ -9371,7 +9370,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B173" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C173">
         <x:v>172</x:v>
@@ -9446,7 +9445,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B175" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C175">
         <x:v>174</x:v>
@@ -9475,7 +9474,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B176" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C176">
         <x:v>175</x:v>
@@ -9561,7 +9560,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B178" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C178">
         <x:v>177</x:v>
@@ -9590,7 +9589,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B179" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C179">
         <x:v>178</x:v>
@@ -9660,7 +9659,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B181" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C181">
         <x:v>180</x:v>
@@ -9689,7 +9688,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="B182" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C182">
         <x:v>181</x:v>
@@ -9723,7 +9722,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="B183" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C183">
         <x:v>182</x:v>
@@ -9757,7 +9756,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="B184" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C184">
         <x:v>183</x:v>
@@ -9820,7 +9819,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="B186" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C186">
         <x:v>185</x:v>
@@ -9930,7 +9929,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="B189" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C189">
         <x:v>188</x:v>
@@ -9974,7 +9973,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="H190" t="s">
-        <x:v>36</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J190" t="str">
         <x:v>K-26</x:v>
@@ -9999,7 +9998,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B191" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C191">
         <x:v>190</x:v>
@@ -10017,7 +10016,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="H191" t="s">
-        <x:v>36</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J191" t="str">
         <x:v>K-25</x:v>
@@ -10074,7 +10073,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B193" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C193">
         <x:v>192</x:v>
@@ -10106,7 +10105,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B194" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C194">
         <x:v>193</x:v>
@@ -10120,8 +10119,8 @@
       <x:c r="G194" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="I194" t="s">
-        <x:v>36</x:v>
+      <x:c r="I194" t="str">
+        <x:v>K-51</x:v>
       </x:c>
       <x:c r="L194" t="str">
         <x:v>K-52</x:v>
@@ -10141,7 +10140,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B195" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C195">
         <x:v>194</x:v>
@@ -10155,8 +10154,8 @@
       <x:c r="G195" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="I195" t="s">
-        <x:v>36</x:v>
+      <x:c r="I195" t="str">
+        <x:v>K-52</x:v>
       </x:c>
       <x:c r="L195" t="str">
         <x:v>K-53</x:v>
@@ -10176,7 +10175,7 @@
         <x:v>438</x:v>
       </x:c>
       <x:c r="B196" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C196">
         <x:v>195</x:v>
@@ -10225,8 +10224,8 @@
       <x:c r="H197" t="str">
         <x:v>K-47</x:v>
       </x:c>
-      <x:c r="I197" t="s">
-        <x:v>36</x:v>
+      <x:c r="I197" t="str">
+        <x:v>K-54</x:v>
       </x:c>
       <x:c r="J197" t="str">
         <x:v>K-28</x:v>
@@ -10272,8 +10271,8 @@
       <x:c r="H198" t="str">
         <x:v>K-48</x:v>
       </x:c>
-      <x:c r="I198" t="s">
-        <x:v>36</x:v>
+      <x:c r="I198" t="str">
+        <x:v>K-55</x:v>
       </x:c>
       <x:c r="J198" t="str">
         <x:v>K-29</x:v>
@@ -10302,7 +10301,7 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B199" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C199">
         <x:v>198</x:v>
@@ -10375,7 +10374,7 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B201" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C201">
         <x:v>200</x:v>
@@ -10407,7 +10406,7 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B202" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C202">
         <x:v>201</x:v>
@@ -10436,7 +10435,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B203" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C203">
         <x:v>202</x:v>
@@ -10450,8 +10449,8 @@
       <x:c r="G203" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="I203" t="s">
-        <x:v>36</x:v>
+      <x:c r="I203" t="str">
+        <x:v>K-53</x:v>
       </x:c>
       <x:c r="L203" t="str">
         <x:v>K-51</x:v>
@@ -10471,7 +10470,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B204" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C204">
         <x:v>203</x:v>
@@ -10481,6 +10480,9 @@
       </x:c>
       <x:c r="E204" t="s">
         <x:v>457</x:v>
+      </x:c>
+      <x:c r="I204" t="str">
+        <x:v>K-37</x:v>
       </x:c>
       <x:c r="L204" t="str">
         <x:v>K-36</x:v>
@@ -10500,7 +10502,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B205" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C205">
         <x:v>204</x:v>
@@ -10537,7 +10539,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B206" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C206">
         <x:v>205</x:v>
@@ -10575,7 +10577,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B207" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C207">
         <x:v>206</x:v>
@@ -10592,8 +10594,8 @@
       <x:c r="G207" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="I207" t="s">
-        <x:v>36</x:v>
+      <x:c r="I207" t="str">
+        <x:v>K-39</x:v>
       </x:c>
       <x:c r="L207" t="str">
         <x:v>K-38</x:v>
@@ -10613,7 +10615,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B208" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C208">
         <x:v>207</x:v>
@@ -10642,7 +10644,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B209" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C209">
         <x:v>208</x:v>
@@ -10656,8 +10658,8 @@
       <x:c r="F209" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I209" t="s">
-        <x:v>36</x:v>
+      <x:c r="I209" t="str">
+        <x:v>K-38</x:v>
       </x:c>
       <x:c r="L209" t="str">
         <x:v>K-37</x:v>
@@ -10677,7 +10679,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B210" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C210">
         <x:v>209</x:v>
@@ -10709,7 +10711,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B211" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C211">
         <x:v>210</x:v>
@@ -10738,7 +10740,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B212" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C212">
         <x:v>211</x:v>
@@ -10770,7 +10772,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B213" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C213">
         <x:v>212</x:v>
@@ -10805,7 +10807,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B214" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C214">
         <x:v>213</x:v>
@@ -10840,7 +10842,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B215" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C215">
         <x:v>214</x:v>
@@ -10904,7 +10906,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B217" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C217">
         <x:v>216</x:v>
@@ -10916,7 +10918,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="I217" t="str">
-        <x:v>K-</x:v>
+        <x:v>K-40</x:v>
       </x:c>
       <x:c r="L217" t="str">
         <x:v>K-35</x:v>
@@ -10936,7 +10938,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B218" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C218">
         <x:v>217</x:v>
@@ -10974,7 +10976,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B219" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C219">
         <x:v>218</x:v>
@@ -11006,7 +11008,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B220" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C220">
         <x:v>219</x:v>
@@ -11038,7 +11040,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B221" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C221">
         <x:v>220</x:v>
@@ -11073,7 +11075,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B222" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C222">
         <x:v>221</x:v>
@@ -11102,7 +11104,7 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B223" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C223">
         <x:v>222</x:v>
@@ -11116,8 +11118,8 @@
       <x:c r="G223" t="s">
         <x:v>493</x:v>
       </x:c>
-      <x:c r="I223" t="s">
-        <x:v>36</x:v>
+      <x:c r="I223" t="str">
+        <x:v>K-46</x:v>
       </x:c>
       <x:c r="L223" t="str">
         <x:v>K-28</x:v>
@@ -11183,8 +11185,8 @@
       <x:c r="G225" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="I225" t="s">
-        <x:v>36</x:v>
+      <x:c r="I225" t="str">
+        <x:v>K-45</x:v>
       </x:c>
       <x:c r="L225" t="str">
         <x:v>K-29</x:v>
@@ -11218,8 +11220,8 @@
       <x:c r="G226" t="s">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="I226" t="s">
-        <x:v>36</x:v>
+      <x:c r="I226" t="str">
+        <x:v>K-41</x:v>
       </x:c>
       <x:c r="L226" t="str">
         <x:v>K-33</x:v>
@@ -11257,8 +11259,8 @@
       <x:c r="G227" t="s">
         <x:v>502</x:v>
       </x:c>
-      <x:c r="I227" t="s">
-        <x:v>36</x:v>
+      <x:c r="I227" t="str">
+        <x:v>K-43</x:v>
       </x:c>
       <x:c r="L227" t="str">
         <x:v>K-31</x:v>
@@ -11292,8 +11294,8 @@
       <x:c r="G228" t="s">
         <x:v>504</x:v>
       </x:c>
-      <x:c r="I228" t="s">
-        <x:v>36</x:v>
+      <x:c r="I228" t="str">
+        <x:v>K-42</x:v>
       </x:c>
       <x:c r="L228" t="str">
         <x:v>K-32</x:v>
@@ -11370,8 +11372,8 @@
       <x:c r="H230" t="str">
         <x:v>K-39</x:v>
       </x:c>
-      <x:c r="I230" t="s">
-        <x:v>36</x:v>
+      <x:c r="I230" t="str">
+        <x:v>K-44</x:v>
       </x:c>
       <x:c r="K230" t="str">
         <x:v>K-31</x:v>
@@ -11401,7 +11403,7 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B231" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C231">
         <x:v>230</x:v>
@@ -11434,7 +11436,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B232" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C232">
         <x:v>231</x:v>
@@ -11448,8 +11450,8 @@
       <x:c r="G232" t="s">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="I232" t="s">
-        <x:v>36</x:v>
+      <x:c r="I232" t="str">
+        <x:v>K-48</x:v>
       </x:c>
       <x:c r="L232" t="str">
         <x:v>K-26</x:v>
@@ -11469,7 +11471,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B233" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C233">
         <x:v>232</x:v>
@@ -11483,8 +11485,8 @@
       <x:c r="G233" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="I233" t="s">
-        <x:v>36</x:v>
+      <x:c r="I233" t="str">
+        <x:v>K-47</x:v>
       </x:c>
       <x:c r="L233" t="str">
         <x:v>K-27</x:v>
@@ -11506,7 +11508,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B234" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C234">
         <x:v>233</x:v>
@@ -11575,7 +11577,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B236" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C236">
         <x:v>235</x:v>
@@ -11611,7 +11613,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B237" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C237">
         <x:v>236</x:v>
@@ -11650,7 +11652,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B238" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C238">
         <x:v>237</x:v>
@@ -11686,7 +11688,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B239" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C239">
         <x:v>238</x:v>
@@ -11718,7 +11720,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B240" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C240">
         <x:v>239</x:v>
@@ -11860,7 +11862,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B244" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C244">
         <x:v>243</x:v>
@@ -11871,8 +11873,8 @@
       <x:c r="E244" t="s">
         <x:v>536</x:v>
       </x:c>
-      <x:c r="I244" t="s">
-        <x:v>36</x:v>
+      <x:c r="I244" t="str">
+        <x:v>K-25</x:v>
       </x:c>
       <x:c r="N244"/>
       <x:c r="O244"/>
@@ -11889,7 +11891,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B245" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C245">
         <x:v>244</x:v>
@@ -11903,8 +11905,8 @@
       <x:c r="G245" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="I245" t="s">
-        <x:v>36</x:v>
+      <x:c r="I245" t="str">
+        <x:v>K-26</x:v>
       </x:c>
       <x:c r="N245"/>
       <x:c r="O245"/>
@@ -11921,7 +11923,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B246" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C246">
         <x:v>245</x:v>
@@ -11932,8 +11934,8 @@
       <x:c r="E246" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="I246" t="s">
-        <x:v>36</x:v>
+      <x:c r="I246" t="str">
+        <x:v>K-27</x:v>
       </x:c>
       <x:c r="N246"/>
       <x:c r="O246"/>
@@ -11970,8 +11972,8 @@
       <x:c r="H247" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="I247" t="s">
-        <x:v>36</x:v>
+      <x:c r="I247" t="str">
+        <x:v>K-24</x:v>
       </x:c>
       <x:c r="J247" t="str">
         <x:v>K-7</x:v>
@@ -12019,8 +12021,8 @@
       <x:c r="E248" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="I248" t="s">
-        <x:v>36</x:v>
+      <x:c r="I248" t="str">
+        <x:v>K-23</x:v>
       </x:c>
       <x:c r="L248" t="s">
         <x:v>26</x:v>
@@ -12060,8 +12062,8 @@
       <x:c r="H249" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="I249" t="s">
-        <x:v>36</x:v>
+      <x:c r="I249" t="str">
+        <x:v>K-22</x:v>
       </x:c>
       <x:c r="J249" t="str">
         <x:v>K-6</x:v>
@@ -12098,7 +12100,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B250" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C250">
         <x:v>249</x:v>
@@ -12127,7 +12129,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B251" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C251">
         <x:v>250</x:v>
@@ -12161,7 +12163,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B252" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C252">
         <x:v>251</x:v>
@@ -12195,7 +12197,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B253" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C253">
         <x:v>252</x:v>
@@ -12209,8 +12211,8 @@
       <x:c r="G253" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="I253" t="s">
-        <x:v>36</x:v>
+      <x:c r="I253" t="str">
+        <x:v>K-21</x:v>
       </x:c>
       <x:c r="L253" t="s">
         <x:v>26</x:v>
@@ -12234,7 +12236,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B254" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C254">
         <x:v>253</x:v>
@@ -12263,7 +12265,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B255" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C255">
         <x:v>254</x:v>
@@ -12292,7 +12294,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B256" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C256">
         <x:v>255</x:v>
@@ -12382,7 +12384,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B259" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C259">
         <x:v>258</x:v>
@@ -12413,7 +12415,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B260" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C260">
         <x:v>259</x:v>
@@ -12444,7 +12446,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B261" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C261">
         <x:v>260</x:v>
@@ -12509,7 +12511,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B263" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C263">
         <x:v>262</x:v>
@@ -12523,9 +12525,7 @@
       <x:c r="H263" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="J263" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="J263"/>
       <x:c r="K263" t="s">
         <x:v>190</x:v>
       </x:c>
@@ -12546,7 +12546,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B264" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C264">
         <x:v>263</x:v>
@@ -12557,8 +12557,8 @@
       <x:c r="E264" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="I264" t="s">
-        <x:v>36</x:v>
+      <x:c r="I264" t="str">
+        <x:v>K-28</x:v>
       </x:c>
       <x:c r="N264"/>
       <x:c r="O264"/>
@@ -12575,7 +12575,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B265" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C265">
         <x:v>264</x:v>
@@ -12617,7 +12617,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B266" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C266">
         <x:v>265</x:v>
@@ -12648,7 +12648,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B267" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C267">
         <x:v>266</x:v>
@@ -12690,7 +12690,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B268" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C268">
         <x:v>267</x:v>
@@ -12728,7 +12728,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B269" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C269">
         <x:v>268</x:v>
@@ -12765,7 +12765,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B270" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C270">
         <x:v>269</x:v>
@@ -12776,8 +12776,8 @@
       <x:c r="E270" t="s">
         <x:v>577</x:v>
       </x:c>
-      <x:c r="I270" t="s">
-        <x:v>36</x:v>
+      <x:c r="I270" t="str">
+        <x:v>K-33</x:v>
       </x:c>
       <x:c r="L270" t="s">
         <x:v>26</x:v>
@@ -12831,7 +12831,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B272" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C272">
         <x:v>271</x:v>
@@ -12863,7 +12863,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B273" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C273">
         <x:v>272</x:v>
@@ -12906,8 +12906,8 @@
       <x:c r="H274" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="I274" t="s">
-        <x:v>36</x:v>
+      <x:c r="I274" t="str">
+        <x:v>K-36</x:v>
       </x:c>
       <x:c r="J274" t="str">
         <x:v>K-15</x:v>
@@ -12942,7 +12942,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B275" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C275">
         <x:v>274</x:v>
@@ -12957,7 +12957,7 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="I275" t="str">
-        <x:v>K-</x:v>
+        <x:v>K-13</x:v>
       </x:c>
       <x:c r="L275" t="str">
         <x:v>M-</x:v>
@@ -12995,8 +12995,8 @@
       <x:c r="G276" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="I276" t="s">
-        <x:v>36</x:v>
+      <x:c r="I276" t="str">
+        <x:v>K-29</x:v>
       </x:c>
       <x:c r="L276" t="s">
         <x:v>26</x:v>
@@ -13059,8 +13059,8 @@
       <x:c r="G278" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="I278" t="s">
-        <x:v>36</x:v>
+      <x:c r="I278" t="str">
+        <x:v>K-30</x:v>
       </x:c>
       <x:c r="L278" t="s">
         <x:v>26</x:v>
@@ -13084,7 +13084,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B279" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C279">
         <x:v>278</x:v>
@@ -13116,7 +13116,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B280" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C280">
         <x:v>279</x:v>
@@ -13127,9 +13127,7 @@
       <x:c r="E280" t="s">
         <x:v>598</x:v>
       </x:c>
-      <x:c r="I280" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="I280"/>
       <x:c r="L280" t="s">
         <x:v>26</x:v>
       </x:c>
@@ -13148,7 +13146,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B281" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C281">
         <x:v>280</x:v>
@@ -13162,9 +13160,7 @@
       <x:c r="G281" t="s">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="I281" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="I281"/>
       <x:c r="L281" t="s">
         <x:v>26</x:v>
       </x:c>
@@ -13183,7 +13179,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B282" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C282">
         <x:v>281</x:v>
@@ -13197,8 +13193,8 @@
       <x:c r="G282" t="s">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="I282" t="s">
-        <x:v>36</x:v>
+      <x:c r="I282" t="str">
+        <x:v>K-32</x:v>
       </x:c>
       <x:c r="L282" t="s">
         <x:v>26</x:v>
@@ -13220,7 +13216,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B283" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C283">
         <x:v>282</x:v>
@@ -13234,9 +13230,7 @@
       <x:c r="G283" t="s">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="I283" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="I283"/>
       <x:c r="L283" t="s">
         <x:v>26</x:v>
       </x:c>
@@ -13255,7 +13249,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B284" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C284">
         <x:v>283</x:v>
@@ -13269,9 +13263,7 @@
       <x:c r="G284" t="s">
         <x:v>604</x:v>
       </x:c>
-      <x:c r="I284" t="s">
-        <x:v>36</x:v>
-      </x:c>
+      <x:c r="I284"/>
       <x:c r="L284" t="s">
         <x:v>26</x:v>
       </x:c>
@@ -13336,8 +13328,8 @@
       <x:c r="G286" t="s">
         <x:v>607</x:v>
       </x:c>
-      <x:c r="I286" t="s">
-        <x:v>36</x:v>
+      <x:c r="I286" t="str">
+        <x:v>K-35</x:v>
       </x:c>
       <x:c r="N286"/>
       <x:c r="O286"/>
@@ -13354,7 +13346,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B287" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C287">
         <x:v>286</x:v>
@@ -13365,8 +13357,8 @@
       <x:c r="E287" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="I287" t="s">
-        <x:v>36</x:v>
+      <x:c r="I287" t="str">
+        <x:v>K-34</x:v>
       </x:c>
       <x:c r="N287"/>
       <x:c r="O287"/>
@@ -13383,7 +13375,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B288" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C288">
         <x:v>287</x:v>
@@ -13394,8 +13386,8 @@
       <x:c r="E288" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="I288" t="s">
-        <x:v>36</x:v>
+      <x:c r="I288" t="str">
+        <x:v>K-31</x:v>
       </x:c>
       <x:c r="L288" t="s">
         <x:v>26</x:v>
@@ -13415,7 +13407,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B289" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C289">
         <x:v>288</x:v>
@@ -13450,7 +13442,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B290" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C290">
         <x:v>289</x:v>
@@ -13517,7 +13509,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B292" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C292">
         <x:v>291</x:v>
@@ -13631,8 +13623,8 @@
       <x:c r="G295" t="s">
         <x:v>626</x:v>
       </x:c>
-      <x:c r="I295" t="s">
-        <x:v>36</x:v>
+      <x:c r="I295" t="str">
+        <x:v>K-50</x:v>
       </x:c>
       <x:c r="L295" t="str">
         <x:v>K-56</x:v>
@@ -14615,7 +14607,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C5">
         <x:v>1</x:v>
@@ -25998,16 +25990,16 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="I2" t="s">
-        <x:v>36</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>36</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K2" t="s">
         <x:v>272</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>36</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M2" t="s">
         <x:v>773</x:v>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="Rbfabbeee68574edc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R45865127cee047e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="Rc2f076d1e87b4b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R2a70bde4fdc34a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="Rfbc4f9ae3eaf40ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rd77a2ec100b54971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R01f51ab3c6ce4dce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R7330d8851b9b413b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R7bbec1230439427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R55712fdd92114931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="Rf9b1f7388bec4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rf8597274dd704f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R263685c45acd4bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R97a5f8839ab64a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R543c3443c7f34f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R0ac2467d28e348cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R08b504c8bed749e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R8c5b2e7db238484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R310b803da71c45b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Re2147025bc33451f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3441,9 +3441,7 @@
       <x:c r="M9" t="str">
         <x:v>段紙</x:v>
       </x:c>
-      <x:c r="N9" t="str">
-        <x:v>段紙(土)-10</x:v>
-      </x:c>
+      <x:c r="N9"/>
       <x:c r="O9"/>
       <x:c r="P9"/>
       <x:c r="Q9"/>
@@ -3484,7 +3482,9 @@
       <x:c r="M10" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="N10"/>
+      <x:c r="N10" t="str">
+        <x:v>段紙(土)-10</x:v>
+      </x:c>
       <x:c r="O10"/>
       <x:c r="P10"/>
       <x:c r="Q10" t="str">

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="Rf9b1f7388bec4aa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="Rf8597274dd704f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R263685c45acd4bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R97a5f8839ab64a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R543c3443c7f34f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R0ac2467d28e348cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R08b504c8bed749e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R8c5b2e7db238484e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R310b803da71c45b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="Re2147025bc33451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R0e953fae1e524d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R2c9988d34a084807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R67a226d5569042fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R8449c3798eff4ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R9c32bc79429342c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rd66261ec94f94368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rfcc2d9ecba854b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R34494238135d47b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R1adb1c3642124d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R5aaf8a00600f48a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5628,8 +5628,8 @@
       <x:c r="V71"/>
     </x:row>
     <x:row r="72" ht="21" customHeight="1">
-      <x:c r="A72" t="s">
-        <x:v>156</x:v>
+      <x:c r="A72" t="str">
+        <x:v>城北</x:v>
       </x:c>
       <x:c r="B72" t="s">
         <x:v>51</x:v>
@@ -5667,8 +5667,8 @@
       <x:c r="V72"/>
     </x:row>
     <x:row r="73" ht="21" customHeight="1">
-      <x:c r="A73" t="s">
-        <x:v>156</x:v>
+      <x:c r="A73" t="str">
+        <x:v>城北</x:v>
       </x:c>
       <x:c r="B73" t="s">
         <x:v>31</x:v>
@@ -5706,8 +5706,8 @@
       </x:c>
     </x:row>
     <x:row r="74" ht="21" customHeight="1">
-      <x:c r="A74" t="s">
-        <x:v>156</x:v>
+      <x:c r="A74" t="str">
+        <x:v>城北</x:v>
       </x:c>
       <x:c r="B74" t="s">
         <x:v>49</x:v>
@@ -5743,8 +5743,8 @@
       </x:c>
     </x:row>
     <x:row r="75" ht="21" customHeight="1">
-      <x:c r="A75" t="s">
-        <x:v>156</x:v>
+      <x:c r="A75" t="str">
+        <x:v>城北</x:v>
       </x:c>
       <x:c r="B75" t="s">
         <x:v>31</x:v>

--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="R0e953fae1e524d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R2c9988d34a084807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R67a226d5569042fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="R8449c3798eff4ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R9c32bc79429342c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="Rd66261ec94f94368"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="Rfcc2d9ecba854b59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R34494238135d47b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="R1adb1c3642124d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R5aaf8a00600f48a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="物件表" sheetId="1" r:id="Rbbcee19c82ad4183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" r:id="R46df4e3d21fe4d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" r:id="R2b3e4b34cb3e42f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" r:id="Rf1990432162a4b76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" r:id="R08d1db8a470f4565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" r:id="R6186684ba1d0466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" r:id="R14c3607202454f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" r:id="R6226204063d946a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非表示物件" sheetId="9" r:id="Raeccec5d4eba4044"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日許可物件表（休出用）" sheetId="10" r:id="R2b4cbf3aa5b64406"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9062,8 +9062,8 @@
       <x:c r="I163" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="L163" t="s">
-        <x:v>310</x:v>
+      <x:c r="L163" t="str">
+        <x:v>N-37</x:v>
       </x:c>
       <x:c r="N163"/>
       <x:c r="O163"/>
@@ -9093,8 +9093,8 @@
       <x:c r="E164" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="L164" t="s">
-        <x:v>305</x:v>
+      <x:c r="L164" t="str">
+        <x:v>N-36</x:v>
       </x:c>
       <x:c r="N164"/>
       <x:c r="O164"/>
